--- a/結合試験仕様書.xlsx
+++ b/結合試験仕様書.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="表示" sheetId="1" r:id="rId1"/>
+    <sheet name="表紙" sheetId="1" r:id="rId1"/>
     <sheet name="凡例・用語集" sheetId="2" r:id="rId2"/>
     <sheet name="イベント管理" sheetId="3" r:id="rId3"/>
     <sheet name="券種・申込フォーム項目" sheetId="4" r:id="rId4"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="460">
   <si>
     <t xml:space="preserve">ACTIO（イベント主催・管理サービス）</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">対象: index.html（単一ファイル・file:// 起動）</t>
   </si>
   <si>
-    <t xml:space="preserve">試験項目: 全80項目（大項目10）</t>
+    <t xml:space="preserve">試験項目: 全86項目（大項目10）</t>
   </si>
   <si>
     <t xml:space="preserve">動作保証: Google Chrome のみ</t>
@@ -193,7 +193,7 @@
     <t xml:space="preserve">目的</t>
   </si>
   <si>
-    <t xml:space="preserve">イベントの作成・編集・複製・削除と、5ステップのウィザードによる入力が正しく動作すること。公開時の必須チェックと日時の相関チェックが効くこと。</t>
+    <t xml:space="preserve">イベントの作成・編集・複製・削除と、5ステップのウィザードによる入力が正しく動作すること。公開時の必須チェックと日時の相関チェックが効くこと。一覧の絞り込みとページ送り、告知文の生成が動作すること。</t>
   </si>
   <si>
     <t xml:space="preserve">主催者としてログインしていること。特記なき場合、デモデータを投入した直後の状態から始める。</t>
@@ -247,7 +247,7 @@
     <t xml:space="preserve">「イベントを作成」→ 5ステップを順に入力 →「公開する」</t>
   </si>
   <si>
-    <t xml:space="preserve">イベントが作成され、イベント詳細（S-04）に遷移する。一覧にも表示される</t>
+    <t xml:space="preserve">イベントが作成され、イベント詳細（S-04）に遷移する。一覧にも表示される（F-01）</t>
   </si>
   <si>
     <t xml:space="preserve">ステップを行き来しても入力値が保持される</t>
@@ -349,6 +349,21 @@
     <t xml:space="preserve">サムネイルが表示され、公開ページのヘッダーと一覧カードの両方で崩れずに出る（D-15）</t>
   </si>
   <si>
+    <t xml:space="preserve">イベントを編集して保存できる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">公開中のイベントの詳細（S-04）を開いている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「編集」→ イベント名と説明文を変更 →「保存する」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">変更が保存され、イベント詳細と公開イベントページの双方に反映される（F-02）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">公開状態は変わらない</t>
+  </si>
+  <si>
     <t xml:space="preserve">イベントを複製するとシリーズが付き下書きになる</t>
   </si>
   <si>
@@ -361,6 +376,33 @@
     <t xml:space="preserve">「（複製）」が付いた下書きが作られ、複製元と複製先の両方に「シリーズ」が付く（F-05）</t>
   </si>
   <si>
+    <t xml:space="preserve">イベント詳細から告知文を生成できる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「告知文を生成」→ 文面を確認 →「コピーする」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベント名・日時・開催場所・説明文・申込締切・定員が差し込まれた文面が出る。コピーでき、送信履歴に「告知文」として記録される（F-29）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">テンプレート未設定時は既定の文面。設定・データ管理で変更できる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベント一覧を絞り込んでページを送れる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベントが21件以上ある</t>
+  </si>
+  <si>
+    <t xml:space="preserve">状態「公開中」・キーワード・カテゴリで絞り込み、ページ送りで2ページ目へ移動する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">条件に合うものだけが開始日時の降順で1ページ20件ずつ並ぶ。絞り込みを変更すると1ページ目に戻る（F-04 / D-36）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">デモデータだけでは21件に満たないため、複製で下書きを増やしてから実施する</t>
+  </si>
+  <si>
     <t xml:space="preserve">申込のあるイベントの削除で件数が示される</t>
   </si>
   <si>
@@ -487,7 +529,7 @@
     <t xml:space="preserve">項目を2件追加し、↑↓で入れ替え、片方を必須にして保存</t>
   </si>
   <si>
-    <t xml:space="preserve">申込フォームに設定した順序で表示され、必須項目は空のままだと申し込めない（D-28）</t>
+    <t xml:space="preserve">申込フォームに設定した順序で表示され、必須項目は空のままだと申し込めない（F-07 / D-28）</t>
   </si>
   <si>
     <t xml:space="preserve">・公開ページ・集客</t>
@@ -583,7 +625,7 @@
     <t xml:space="preserve">公開イベントページ（S-05）を開く</t>
   </si>
   <si>
-    <t xml:space="preserve">「残り○枚」が表示される。閾値を超える残席では表示されない（F-31）</t>
+    <t xml:space="preserve">公開イベントページにイベント名・日時・場所・説明文・券種が表示される。「残り○枚」が出る。閾値を超える残席では表示されない（F-08 / F-31）</t>
   </si>
   <si>
     <t xml:space="preserve">プレビューでは申込導線が出ない</t>
@@ -616,7 +658,7 @@
     <t xml:space="preserve">公開ページ →「申し込む」→ 券種選択・氏名・メール・パスワード入力 → 確認 → 申し込む</t>
   </si>
   <si>
-    <t xml:space="preserve">申込完了画面（S-07）に遷移し、受付コードが表示される（F-11 / F-24）</t>
+    <t xml:space="preserve">氏名とメールアドレスは必須で、未入力だと進めない。申込完了画面（S-07）に遷移し、受付コードが表示される（F-06 / F-11 / F-24）</t>
   </si>
   <si>
     <t xml:space="preserve">受付コードは英大文字と数字の8桁になる</t>
@@ -838,6 +880,21 @@
     <t xml:space="preserve">いずれでも該当する参加者だけに絞り込まれる（F-15）</t>
   </si>
   <si>
+    <t xml:space="preserve">参加者一覧のページを送れる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込が26件以上あるイベントの参加者一覧を開いている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ページ送りで2ページ目へ移動し、その後に受付状況の絞り込みを変更する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1ページ25件ずつ区切られ、2ページ目に26件目以降が出る。絞り込みを変更すると1ページ目に戻る（F-15）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">デモデータでは件数が足りないため、定員の大きいイベントに申込を追加してから実施する</t>
+  </si>
+  <si>
     <t xml:space="preserve">日本語入力で母音が落ちない</t>
   </si>
   <si>
@@ -877,6 +934,21 @@
     <t xml:space="preserve">状態が「申し込み済み」に戻り、受付日時が空になる</t>
   </si>
   <si>
+    <t xml:space="preserve">主催者が申込をキャンセルできる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">受付済み（参加確定）の参加者がいる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その行の「キャンセル」→ 確認ダイアログで OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">状態が「キャンセル済み」に変わり、券種の残席が1つ戻る。受付済みでも主催者はキャンセルできる（F-13 / D-10）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参加者側からのキャンセルは 4-9 の前提として実施する</t>
+  </si>
+  <si>
     <t xml:space="preserve">受付操作で集計とボタンの位置がずれない</t>
   </si>
   <si>
@@ -1133,6 +1205,21 @@
   </si>
   <si>
     <t xml:space="preserve">資料を含めるかは選択できる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">デモデータの投入と全データの初期化ができる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベントと申込が登録されている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「デモデータを投入」→ 確認 → 内容を確認。続けて「全データを初期化」→ 確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">投入では既存データが置き換わり、F節のデモデータが入る。初期化するとイベント・申込・資料・設定がすべて消え、ログアウトしてパスコード設定画面に戻る（F-21）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">初期化は元に戻せない。本シートの最後に実施する</t>
   </si>
   <si>
     <t xml:space="preserve">・資料・運営体制</t>
@@ -2132,7 +2219,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="5.9140625" style="17" customWidth="1"/>
@@ -2154,7 +2241,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>330</v>
+        <v>354</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2166,7 +2253,7 @@
         <v>56</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -2177,7 +2264,7 @@
         <v>50</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -2262,23 +2349,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>334</v>
+        <v>358</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>335</v>
+        <v>359</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>336</v>
+        <v>360</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="2"/>
@@ -2294,20 +2381,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="2"/>
@@ -2323,20 +2410,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>344</v>
+        <v>368</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="2"/>
@@ -2352,20 +2439,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>347</v>
+        <v>371</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>348</v>
+        <v>372</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>349</v>
+        <v>373</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="2"/>
@@ -2381,20 +2468,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="2"/>
@@ -2410,20 +2497,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="L13" s="13"/>
       <c r="M13" s="2"/>
@@ -2439,20 +2526,20 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="2"/>
@@ -2468,20 +2555,20 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="2"/>
@@ -2497,28 +2584,59 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="2"/>
       <c r="N16" s="13"/>
       <c r="O16" s="13" t="s">
-        <v>370</v>
+        <v>394</v>
       </c>
       <c r="P16" s="13"/>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="22">
+        <v>10</v>
+      </c>
+      <c r="E17" s="32"/>
+      <c r="F17" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="P17" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2527,9 +2645,9 @@
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="L6:P6"/>
-    <mergeCell ref="B8:B16"/>
-    <mergeCell ref="C8:C16"/>
-    <mergeCell ref="E8:E16"/>
+    <mergeCell ref="B8:B17"/>
+    <mergeCell ref="C8:C17"/>
+    <mergeCell ref="E8:E17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2559,7 +2677,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>371</v>
+        <v>400</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2571,7 +2689,7 @@
         <v>56</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>372</v>
+        <v>401</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -2582,7 +2700,7 @@
         <v>50</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>373</v>
+        <v>402</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -2667,23 +2785,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>374</v>
+        <v>403</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>375</v>
+        <v>404</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>376</v>
+        <v>405</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>378</v>
+        <v>407</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="2"/>
@@ -2699,20 +2817,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>379</v>
+        <v>408</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>380</v>
+        <v>409</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>381</v>
+        <v>410</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="2"/>
@@ -2728,20 +2846,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>382</v>
+        <v>411</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>383</v>
+        <v>412</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>384</v>
+        <v>413</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>385</v>
+        <v>414</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="2"/>
@@ -2757,20 +2875,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>386</v>
+        <v>415</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="2"/>
@@ -2786,20 +2904,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>390</v>
+        <v>419</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>391</v>
+        <v>420</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>393</v>
+        <v>422</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="2"/>
@@ -2846,7 +2964,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2858,7 +2976,7 @@
         <v>56</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -2869,7 +2987,7 @@
         <v>50</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>396</v>
+        <v>425</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -2954,23 +3072,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>335</v>
+        <v>359</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>399</v>
+        <v>428</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="2"/>
@@ -2986,26 +3104,26 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>403</v>
+        <v>432</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>404</v>
+        <v>433</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="2"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="s">
-        <v>405</v>
+        <v>434</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -3017,20 +3135,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>406</v>
+        <v>435</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>407</v>
+        <v>436</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>408</v>
+        <v>437</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>409</v>
+        <v>438</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="2"/>
@@ -3046,26 +3164,26 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>410</v>
+        <v>439</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>411</v>
+        <v>440</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>412</v>
+        <v>441</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>413</v>
+        <v>442</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="s">
-        <v>414</v>
+        <v>443</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -3077,20 +3195,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>415</v>
+        <v>444</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>416</v>
+        <v>445</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>417</v>
+        <v>446</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>418</v>
+        <v>447</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="2"/>
@@ -3106,20 +3224,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>419</v>
+        <v>448</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>420</v>
+        <v>449</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>421</v>
+        <v>450</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>422</v>
+        <v>451</v>
       </c>
       <c r="L13" s="13"/>
       <c r="M13" s="2"/>
@@ -3160,12 +3278,12 @@
   <sheetData>
     <row r="1" spans="1:12" ht="26.5">
       <c r="B1" s="24" t="s">
-        <v>423</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="B2" s="13" t="s">
-        <v>424</v>
+        <v>453</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -3173,16 +3291,16 @@
         <v>61</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>425</v>
+        <v>454</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>426</v>
+        <v>455</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>427</v>
+        <v>456</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>428</v>
+        <v>457</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>17</v>
@@ -3191,10 +3309,10 @@
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>429</v>
+        <v>458</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>430</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -3428,7 +3546,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="5.9140625" style="17" customWidth="1"/>
@@ -3832,7 +3950,7 @@
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>110</v>
@@ -3846,7 +3964,9 @@
       <c r="L17" s="13"/>
       <c r="M17" s="2"/>
       <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
+      <c r="O17" s="13" t="s">
+        <v>113</v>
+      </c>
       <c r="P17" s="13"/>
     </row>
     <row r="18" spans="1:16">
@@ -3857,26 +3977,117 @@
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L18" s="13"/>
       <c r="M18" s="2"/>
       <c r="N18" s="13"/>
       <c r="O18" s="13"/>
       <c r="P18" s="13"/>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="22">
+        <v>12</v>
+      </c>
+      <c r="E19" s="32"/>
+      <c r="F19" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="L19" s="13"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="P19" s="13"/>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="22">
+        <v>13</v>
+      </c>
+      <c r="E20" s="32"/>
+      <c r="F20" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="J20" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="L20" s="13"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="P20" s="13"/>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="22">
+        <v>14</v>
+      </c>
+      <c r="E21" s="32"/>
+      <c r="F21" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="L21" s="13"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3885,9 +4096,9 @@
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="L6:P6"/>
-    <mergeCell ref="B8:B18"/>
-    <mergeCell ref="C8:C18"/>
-    <mergeCell ref="E8:E18"/>
+    <mergeCell ref="B8:B21"/>
+    <mergeCell ref="C8:C21"/>
+    <mergeCell ref="E8:E21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3917,7 +4128,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -3929,7 +4140,7 @@
         <v>56</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -3940,7 +4151,7 @@
         <v>50</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -4025,23 +4236,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="2"/>
@@ -4057,20 +4268,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="2"/>
@@ -4086,26 +4297,26 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="2"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -4117,26 +4328,26 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -4148,20 +4359,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="2"/>
@@ -4177,20 +4388,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="L13" s="13"/>
       <c r="M13" s="2"/>
@@ -4206,26 +4417,26 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="2"/>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -4237,20 +4448,20 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="2"/>
@@ -4266,20 +4477,20 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="2"/>
@@ -4326,7 +4537,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -4338,7 +4549,7 @@
         <v>56</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -4349,7 +4560,7 @@
         <v>50</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -4434,23 +4645,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="2"/>
@@ -4466,20 +4677,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="2"/>
@@ -4495,20 +4706,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="2"/>
@@ -4524,20 +4735,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="2"/>
@@ -4553,20 +4764,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="2"/>
@@ -4582,20 +4793,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="L13" s="13"/>
       <c r="M13" s="2"/>
@@ -4611,20 +4822,20 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="2"/>
@@ -4640,20 +4851,20 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="2"/>
@@ -4700,7 +4911,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -4712,7 +4923,7 @@
         <v>56</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -4723,7 +4934,7 @@
         <v>50</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -4808,23 +5019,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="2"/>
@@ -4840,20 +5051,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="2"/>
@@ -4869,20 +5080,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="2"/>
@@ -4898,20 +5109,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="2"/>
@@ -4927,26 +5138,26 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="2"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -4958,20 +5169,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="L13" s="13"/>
       <c r="M13" s="2"/>
@@ -4987,20 +5198,20 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="2"/>
@@ -5016,20 +5227,20 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="2"/>
@@ -5045,20 +5256,20 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="2"/>
@@ -5074,20 +5285,20 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="2"/>
@@ -5134,7 +5345,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -5146,7 +5357,7 @@
         <v>56</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -5157,7 +5368,7 @@
         <v>50</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -5242,23 +5453,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="2"/>
@@ -5274,20 +5485,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="2"/>
@@ -5303,20 +5514,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="2"/>
@@ -5332,26 +5543,26 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -5363,20 +5574,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="2"/>
@@ -5392,20 +5603,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="L13" s="13"/>
       <c r="M13" s="2"/>
@@ -5430,7 +5641,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="5.9140625" style="17" customWidth="1"/>
@@ -5452,7 +5663,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -5464,7 +5675,7 @@
         <v>56</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -5475,7 +5686,7 @@
         <v>50</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -5560,23 +5771,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="2"/>
@@ -5592,20 +5803,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="2"/>
@@ -5621,26 +5832,26 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="2"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -5652,25 +5863,27 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
+      <c r="O11" s="13" t="s">
+        <v>295</v>
+      </c>
       <c r="P11" s="13"/>
     </row>
     <row r="12" spans="1:16">
@@ -5681,20 +5894,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="2"/>
@@ -5710,20 +5923,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="L13" s="13"/>
       <c r="M13" s="2"/>
@@ -5739,25 +5952,27 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="2"/>
       <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
+      <c r="O14" s="13" t="s">
+        <v>308</v>
+      </c>
       <c r="P14" s="13"/>
     </row>
     <row r="15" spans="1:16">
@@ -5768,20 +5983,20 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>269</v>
+        <v>310</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="2"/>
@@ -5797,20 +6012,20 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="2"/>
@@ -5826,20 +6041,20 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="2"/>
@@ -5855,26 +6070,84 @@
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="13" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="L18" s="13"/>
       <c r="M18" s="2"/>
       <c r="N18" s="13"/>
       <c r="O18" s="13"/>
       <c r="P18" s="13"/>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="22">
+        <v>12</v>
+      </c>
+      <c r="E19" s="32"/>
+      <c r="F19" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="L19" s="13"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="22">
+        <v>13</v>
+      </c>
+      <c r="E20" s="32"/>
+      <c r="F20" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="J20" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="L20" s="13"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -5883,9 +6156,9 @@
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="L6:P6"/>
-    <mergeCell ref="B8:B18"/>
-    <mergeCell ref="C8:C18"/>
-    <mergeCell ref="E8:E18"/>
+    <mergeCell ref="B8:B20"/>
+    <mergeCell ref="C8:C20"/>
+    <mergeCell ref="E8:E20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5915,7 +6188,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -5927,7 +6200,7 @@
         <v>56</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -5938,7 +6211,7 @@
         <v>50</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>309</v>
+        <v>333</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -6023,23 +6296,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>312</v>
+        <v>336</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="2"/>
@@ -6055,20 +6328,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>315</v>
+        <v>339</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="2"/>
@@ -6084,20 +6357,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>319</v>
+        <v>343</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="2"/>
@@ -6113,20 +6386,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>323</v>
+        <v>347</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="2"/>
@@ -6142,20 +6415,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>326</v>
+        <v>350</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>329</v>
+        <v>353</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="2"/>

--- a/結合試験仕様書.xlsx
+++ b/結合試験仕様書.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="525">
   <si>
     <t xml:space="preserve">ACTIO（イベント主催・管理サービス）</t>
   </si>
@@ -70,7 +70,7 @@
     <t xml:space="preserve">大項目 / 中項目 / 小項目</t>
   </si>
   <si>
-    <t xml:space="preserve">テスト対象の分類。大きな機能名→具体的な項目、の順に細かくなります。</t>
+    <t xml:space="preserve">テスト対象の分類。大項目＝機能のまとまり（シート名）、中項目＝1件ごとの試験項目です。小項目は本仕様書では使用しません。</t>
   </si>
   <si>
     <t xml:space="preserve">観点</t>
@@ -103,6 +103,12 @@
     <t xml:space="preserve">OK＝期待どおり動いた。NG＝期待どおりにならなかった（不具合）。</t>
   </si>
   <si>
+    <t xml:space="preserve">備考</t>
+  </si>
+  <si>
+    <t xml:space="preserve">補足。先頭の「ID:」は対応する機能ID・入力仕様IDで、続けてその仕様にした理由や、実施するうえでの注意を書いています。</t>
+  </si>
+  <si>
     <t xml:space="preserve">AI</t>
   </si>
   <si>
@@ -157,7 +163,37 @@
     <t xml:space="preserve">F-xx / S-xx / D-xx</t>
   </si>
   <si>
-    <t xml:space="preserve">機能ID・画面ID・入力仕様ID。機能一覧.md / 画面一覧.md / 仕様決定シート.md と対応します。</t>
+    <t xml:space="preserve">機能ID・画面ID・入力仕様ID。備考欄に「ID:」として記載しています。機能一覧.md / 画面一覧.md / 仕様決定シート.md と対応し、どの要件を確かめている項目かを追えます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">券種</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参加枠のこと（一般・学生 など）。券種ごとに定員を決められます。本サービスでは無料のものだけを扱います。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベントの状態</t>
+  </si>
+  <si>
+    <t xml:space="preserve">公開前（下書き）／公開中／終了。終了は、終了日時を過ぎると自動的に切り替わります。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込の状態</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申し込み済み／参加確定（当日の受付が済んだ状態）／キャンセル済み。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シリーズ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">第1回・第2回と続く連続開催のまとまり。回をまたいだ集客の変化を見るために使います。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マイチケット</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参加者が自分の申込を確認・キャンセルする画面。メールアドレスとパスワードで開きます。</t>
   </si>
   <si>
     <t xml:space="preserve">受付コード</t>
@@ -193,10 +229,10 @@
     <t xml:space="preserve">目的</t>
   </si>
   <si>
-    <t xml:space="preserve">イベントの作成・編集・複製・削除と、5ステップのウィザードによる入力が正しく動作すること。公開時の必須チェックと日時の相関チェックが効くこと。一覧の絞り込みとページ送り、告知文の生成が動作すること。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">主催者としてログインしていること。特記なき場合、デモデータを投入した直後の状態から始める。</t>
+    <t xml:space="preserve">イベントを作成・編集・複製・削除する一連の流れが正しく動くこと。公開に必要な項目がそろっているかの確認と、開始・終了・申込締切の前後関係の確認が働くこと。一覧の絞り込みとページ送り、告知文の作成ができること。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">主催者としてログインしていること。ことわりがない限り、デモデータを入れた直後の状態から始める。</t>
   </si>
   <si>
     <t xml:space="preserve">テスト内容</t>
@@ -232,160 +268,175 @@
     <t xml:space="preserve">結果</t>
   </si>
   <si>
-    <t xml:space="preserve">備考</t>
-  </si>
-  <si>
     <t xml:space="preserve">イベント管理</t>
   </si>
   <si>
-    <t xml:space="preserve">イベントを新規作成できる</t>
+    <t xml:space="preserve">イベントを新規に作成できる</t>
   </si>
   <si>
     <t xml:space="preserve">イベント一覧を開いている</t>
   </si>
   <si>
-    <t xml:space="preserve">「イベントを作成」→ 5ステップを順に入力 →「公開する」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">イベントが作成され、イベント詳細（S-04）に遷移する。一覧にも表示される（F-01）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ステップを行き来しても入力値が保持される</t>
-  </si>
-  <si>
-    <t xml:space="preserve">イベント作成画面でステップ1〜3に入力済み</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ステップ表示の番号を直接クリックして1→4→2と移動する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">各ステップの入力値が保持されている。移動時に検証エラーは出ない</t>
+    <t xml:space="preserve">「イベントを作成」を押し、5つのステップを順に入力して「公開する」を押す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベントが作成されて詳細の画面に切り替わる。イベント一覧にも「公開中」として並ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ステップを行き来しても入力内容が消えない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作成画面でステップ1〜3まで入力した状態</t>
+  </si>
+  <si>
+    <t xml:space="preserve">画面上部のステップ番号を押して 1→4→2 の順に移動する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">どのステップに戻っても入力した内容がそのまま残っている。移動しただけではエラーは出ない</t>
   </si>
   <si>
     <t xml:space="preserve">下書きはイベント名だけで保存できる</t>
   </si>
   <si>
-    <t xml:space="preserve">イベント作成画面を開いた直後</t>
-  </si>
-  <si>
-    <t xml:space="preserve">イベント名だけを入力し「下書きとして保存」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エラーなく保存され、一覧に「公開前」で表示される（D-01）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">他の必須項目は未入力のまま</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公開時に必須項目が不足するとエラー一覧が出る</t>
-  </si>
-  <si>
-    <t xml:space="preserve">何も入力せずに「公開する」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">赤いエラー要約が出て件数が示され、各入力欄の下にもメッセージが出る。保存されない（D-01）</t>
+    <t xml:space="preserve">作成画面を開いた直後</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベント名だけを入力して「下書きとして保存」を押す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エラーにならずに保存され、一覧に「公開前」として並ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-01 ／ 他の項目は空のままにする</t>
+  </si>
+  <si>
+    <t xml:space="preserve">公開しようとして未入力があると、足りない項目がまとめて示される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">何も入力せずに「公開する」を押す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">画面上部に赤色で不足の件数と項目名が並び、各入力欄の下にも同じ内容が出る。保存はされない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-01</t>
   </si>
   <si>
     <t xml:space="preserve">開催形式を切り替えると入力欄が入れ替わる</t>
   </si>
   <si>
-    <t xml:space="preserve">イベント作成のステップ1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">開催形式を「会場」→「オンライン」に切り替え、ステップ2を開く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">会場名・住所の欄が消え、視聴URLの欄が表示される（D-16〜D-18）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">終了日時が開始日時以前だとエラーになる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">イベント作成のステップ3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">開始日時より前の終了日時を入力して「公開する」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「終了日時は開始日時より後の日時を指定してください」が表示される</t>
-  </si>
-  <si>
-    <t xml:space="preserve">相関チェック1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">申込締切が開始日時より後だとエラーになる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">開始日時より後の申込締切を入力して「公開する」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「申込締切は開始日時以前の日時を指定してください」が表示される（D-26）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">相関チェック2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">開始日時を入れると申込締切が補完される</t>
-  </si>
-  <si>
-    <t xml:space="preserve">イベント作成のステップ3。申込締切が未入力</t>
+    <t xml:space="preserve">作成画面のステップ1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">開催形式を「会場」から「オンライン」に変え、ステップ2を開く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">会場名と住所の欄が消え、代わりに視聴用URLの欄が現れる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-16〜D-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">終了日時を開始日時より前にすると保存できない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作成画面のステップ3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">開始日時より前の終了日時を入力して「公開する」を押す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「終了日時は開始日時より後の日時を指定してください」と表示され、保存されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">日時の前後関係の確認（1／3）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込締切を開始日時より後にすると保存できない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">開始日時より後の申込締切を入力して「公開する」を押す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「申込締切は開始日時以前の日時を指定してください」と表示され、保存されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-26 ／ 日時の前後関係の確認（2／3）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">開始日時を入れると申込締切が自動で入る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作成画面のステップ3で、申込締切がまだ空の状態</t>
   </si>
   <si>
     <t xml:space="preserve">開始日時を入力する</t>
   </si>
   <si>
-    <t xml:space="preserve">申込締切に同じ日時が自動で入る。すでに入力済みの場合は上書きしない（D-26）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カバー画像が長辺1200pxへ縮小されて保存される</t>
-  </si>
-  <si>
-    <t xml:space="preserve">試験データ/画像/生成/試験_大きい_2400x1600.jpg を用意</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ステップ3でカバー画像に選択し、保存後にイベント詳細と公開ページを開く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">サムネイルが表示され、公開ページのヘッダーと一覧カードの両方で崩れずに出る（D-15）</t>
+    <t xml:space="preserve">申込締切に同じ日時が自動で入る。すでに申込締切を入れていた場合は上書きされない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-26 ／ 入力の手間を減らすための補助</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大きなカバー画像が自動で縮小されて保存される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験データ／画像／生成／試験_大きい_2400x1600.jpg を用意する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ステップ3でこの画像をカバー画像に選び、保存後にイベント詳細と公開ページを開く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">縮小されて登録され、公開ページの見出し部分と一覧のカードのどちらでも崩れずに表示される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-15 ／ 長辺1200ピクセルまで縮めて保存する</t>
   </si>
   <si>
     <t xml:space="preserve">イベントを編集して保存できる</t>
   </si>
   <si>
-    <t xml:space="preserve">公開中のイベントの詳細（S-04）を開いている</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「編集」→ イベント名と説明文を変更 →「保存する」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">変更が保存され、イベント詳細と公開イベントページの双方に反映される（F-02）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公開状態は変わらない</t>
-  </si>
-  <si>
-    <t xml:space="preserve">イベントを複製するとシリーズが付き下書きになる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">シリーズ未設定の公開イベントがある</t>
+    <t xml:space="preserve">公開中のイベントの詳細画面を開いている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「編集」からイベント名と説明文を書き換え、「保存する」を押す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">変更が保存され、主催者側の詳細画面と参加者向けの公開ページの両方に反映される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-02 ／ 公開中のままで変わらない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベントを複製すると下書きとして作られる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シリーズが設定されていない公開中のイベントがある</t>
   </si>
   <si>
     <t xml:space="preserve">イベント一覧で「複製」を押す</t>
   </si>
   <si>
-    <t xml:space="preserve">「（複製）」が付いた下書きが作られ、複製元と複製先の両方に「シリーズ」が付く（F-05）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">イベント詳細から告知文を生成できる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「告知文を生成」→ 文面を確認 →「コピーする」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">イベント名・日時・開催場所・説明文・申込締切・定員が差し込まれた文面が出る。コピーでき、送信履歴に「告知文」として記録される（F-29）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">テンプレート未設定時は既定の文面。設定・データ管理で変更できる</t>
+    <t xml:space="preserve">名前に「（複製）」が付いた下書きが作られる。複製元と複製先の両方が同じシリーズとして結び付く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-05 ／ シリーズ＝第1回・第2回と続く連続開催のまとまり</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベントの告知文を作成できる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「告知文を生成」を押し、文面を確認して「コピーする」を押す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベント名・日時・開催場所・説明文・申込締切・定員が入った文面が出てコピーできる。設定画面の送信履歴に「告知文」として残る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-29 ／ 社内SNSやメールに貼って使う。ひな形は設定画面で変えられる</t>
   </si>
   <si>
     <t xml:space="preserve">イベント一覧を絞り込んでページを送れる</t>
@@ -394,34 +445,37 @@
     <t xml:space="preserve">イベントが21件以上ある</t>
   </si>
   <si>
-    <t xml:space="preserve">状態「公開中」・キーワード・カテゴリで絞り込み、ページ送りで2ページ目へ移動する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">条件に合うものだけが開始日時の降順で1ページ20件ずつ並ぶ。絞り込みを変更すると1ページ目に戻る（F-04 / D-36）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">デモデータだけでは21件に満たないため、複製で下書きを増やしてから実施する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">申込のあるイベントの削除で件数が示される</t>
-  </si>
-  <si>
-    <t xml:space="preserve">申込が9件あるイベントがある</t>
+    <t xml:space="preserve">状態「公開中」・キーワード・カテゴリで絞り込み、下部のページ送りで2ページ目を開く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">条件に合うものだけが開催日の新しい順に並び、1ページ20件ずつ区切られる。絞り込みを変えると1ページ目に戻る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-04 / D-36 ／ デモデータだけでは件数が足りないため、複製で下書きを増やしてから行う</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込があるイベントを削除するときは件数が示される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込が9件入っているイベントがある</t>
   </si>
   <si>
     <t xml:space="preserve">イベント一覧で「削除」を押す</t>
   </si>
   <si>
-    <t xml:space="preserve">「9件の申込があります」と件数を示す確認が出る。承諾すると申込も連動削除される（D-04）</t>
+    <t xml:space="preserve">「9件の申込があります」と件数を示す確認が出る。承諾するとイベントと申込がまとめて削除される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-04 ／ 気づかずに申込ごと消してしまうことを防ぐため</t>
   </si>
   <si>
     <t xml:space="preserve">・券種・申込フォーム項目</t>
   </si>
   <si>
-    <t xml:space="preserve">券種の追加・編集・削除、定員と販売期間の制約、および申込フォームのカスタム項目の設定が正しく動作すること。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">主催者としてログインし、イベント作成／編集画面を開いていること。</t>
+    <t xml:space="preserve">券種（参加枠）の追加・変更・削除と、定員や販売期間の制限が正しく働くこと。申込フォームに独自の質問項目を足せること。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">主催者としてログインし、イベントの作成または編集の画面を開いていること。</t>
   </si>
   <si>
     <t xml:space="preserve">券種・申込フォーム項目</t>
@@ -430,280 +484,319 @@
     <t xml:space="preserve">券種を追加・削除できる</t>
   </si>
   <si>
-    <t xml:space="preserve">イベント作成のステップ4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「券種を追加」で2件目を追加し、片方を「削除」する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">券種が追加・削除され、公開ページの券種欄に反映される（F-23）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">定員に0を入力するとエラーになる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">定員に 0 を入力して「公開する」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「定員は1以上9999以下で入力してください」が表示される（D-22）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">定員に10000を入力するとエラーになる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">定員に 10000 を入力して「公開する」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同上のエラーが表示される（D-22）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">上限9999の外側</t>
-  </si>
-  <si>
-    <t xml:space="preserve">申込数と同数への定員縮小は許可される</t>
-  </si>
-  <si>
-    <t xml:space="preserve">券種に5件の申込があるイベント</t>
-  </si>
-  <si>
-    <t xml:space="preserve">その券種の定員を 5 に変更して保存</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エラーにならず保存できる（D-02）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">境界のちょうど</t>
-  </si>
-  <si>
-    <t xml:space="preserve">申込数未満への定員縮小はできない</t>
-  </si>
-  <si>
-    <t xml:space="preserve">その券種の定員を 4 に変更して保存</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「すでに5件の申込があるため、定員を5未満にはできません」が表示される（D-02）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">申込のある券種は削除できない</t>
-  </si>
-  <si>
-    <t xml:space="preserve">券種に申込があるイベント</t>
+    <t xml:space="preserve">作成画面のステップ4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「券種を追加」で2件目を足し、片方を「削除」する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">券種が増減し、参加者向けの公開ページの券種欄にも反映される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-23 ／ 券種＝参加枠。本サービスでは無料のものだけを扱う</t>
+  </si>
+  <si>
+    <t xml:space="preserve">定員に0を入れると保存できない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">定員に 0 を入力して「公開する」を押す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「定員は1以上9999以下で入力してください」と表示され、保存されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-22 ／ 下限1の1つ外側</t>
+  </si>
+  <si>
+    <t xml:space="preserve">定員に10000を入れると保存できない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">定員に 10000 を入力して「公開する」を押す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-22 ／ 上限9999の1つ外側</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込数と同じ数までは定員を減らせる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ある券種に5件の申込が入っているイベント</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その券種の定員を 5 に変えて保存する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エラーにならずに保存できる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-02 ／ 受け付けられる境界のちょうど</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込数より少ない定員には減らせない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その券種の定員を 4 に変えて保存する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「すでに5件の申込があるため、定員を5未満にはできません」と表示され、保存されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-02 ／ 定員より多くの人を受け付けた状態にしないため</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込が入っている券種は削除できない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込が入っている券種があるイベント</t>
   </si>
   <si>
     <t xml:space="preserve">その券種の「削除」を押す</t>
   </si>
   <si>
-    <t xml:space="preserve">「申込のある券種は削除できません」が表示され、削除されない（D-03）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">販売終了が申込締切より後だとエラーになる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">販売終了に申込締切より後の日時を入力して「公開する」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「販売終了は申込締切以前の日時を指定してください」が表示される（D-24）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">相関チェック3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">残席表示の閾値を0にすると残席が出ない</t>
-  </si>
-  <si>
-    <t xml:space="preserve">残席が少ない券種があるイベント</t>
-  </si>
-  <si>
-    <t xml:space="preserve">残席表示の閾値を 0 にして保存し、公開ページを開く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「残り○枚」が表示されない（D-25）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カスタム項目を追加・並べ替え・必須設定できる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">イベント作成のステップ5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">項目を2件追加し、↑↓で入れ替え、片方を必須にして保存</t>
-  </si>
-  <si>
-    <t xml:space="preserve">申込フォームに設定した順序で表示され、必須項目は空のままだと申し込めない（F-07 / D-28）</t>
+    <t xml:space="preserve">「申込のある券種は削除できません」と表示され、削除されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-03 ／ 申込の行き先がなくなることを防ぐため</t>
+  </si>
+  <si>
+    <t xml:space="preserve">販売終了を申込締切より後にすると保存できない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">販売終了に、申込締切より後の日時を入力して「公開する」を押す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「販売終了は申込締切以前の日時を指定してください」と表示され、保存されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-24 ／ 日時の前後関係の確認（3／3）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">残席の表示を止められる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">残りが少ない券種があるイベント</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その券種の「残席を表示し始める枚数」を 0 にして保存し、参加者向けの公開ページを開く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「残り○枚」が表示されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-25 ／ 設定した枚数以下になったときだけ残席を出す仕組み</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込フォームに独自の質問を追加できる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作成画面のステップ5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">質問項目を2件追加し、↑↓で順番を入れ替え、片方を「必須」にして保存する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参加者の申込フォームに設定した順番で並ぶ。必須にした項目は未記入だと申し込めない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-07 / D-28 ／ 例: 所属部署、参加のきっかけ</t>
   </si>
   <si>
     <t xml:space="preserve">・公開ページ・集客</t>
   </si>
   <si>
-    <t xml:space="preserve">参加者側の入口となる公開イベント一覧と公開イベントページが、検索・カルーセル・残席表示を含めて正しく表示されること。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">デモデータを投入していること。参加者としてログアウト状態で操作する。</t>
+    <t xml:space="preserve">参加者が最初に見る公開イベント一覧とイベントページが、検索・横送り・残席表示を含めて正しく表示されること。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">デモデータを入れた状態。主催者としてはログインせず、参加者の立場で操作する。</t>
   </si>
   <si>
     <t xml:space="preserve">公開ページ・集客</t>
   </si>
   <si>
-    <t xml:space="preserve">公開中のイベントだけが一覧に出る</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公開3件・終了1件・下書き1件がある</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公開イベント一覧（S-10）を開く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「公開中のイベント」に公開中の3件だけが出る。終了と下書きは出ない（F-03）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">検索バーの4条件で絞り込める</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公開イベント一覧を開いている</t>
-  </si>
-  <si>
-    <t xml:space="preserve">キーワード・開催形式・カテゴリ・開催日以降をそれぞれ指定する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">条件に一致するイベントだけが表示され、件数表示も連動する（F-26）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カテゴリから探すは終了分も表示する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">終了済みのイベントが1件ある（研修）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「カテゴリから探す」で「研修」を選ぶ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">終了したイベントも「終了」バッジ付きで表示される。上段の「公開中のイベント」は変化しない</t>
-  </si>
-  <si>
-    <t xml:space="preserve">件数が多いとき左右のボタンで送れる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公開中のイベントが画面幅に収まらない件数ある</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カードの左右に出るボタンをクリックする</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カード1枚ぶんずつ横に送られる。先頭では左、末尾では右のボタンが無効になる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">スクロールバーが表示されない</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同上</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カード列の下端を確認する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">横スクロールバーが表示されない</t>
-  </si>
-  <si>
-    <t xml:space="preserve">収まる件数のときはボタンが出ない</t>
+    <t xml:space="preserve">公開中のイベントだけが並ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">公開中3件・終了1件・下書き1件があるデータ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参加者向けの公開イベント一覧を開く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">上段の「公開中のイベント」に3件だけが並ぶ。終了したイベントと下書きは出ない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-03 ／ 終了したかどうかは終了日時を過ぎたかで自動的に決まる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4つの条件で検索できる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参加者向けの公開イベント一覧を開いている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">キーワード・開催形式・カテゴリ・開催日以降を、それぞれ指定する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">条件に合うイベントだけが表示され、件数の表示も一緒に変わる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「カテゴリから探す」では終了したイベントも見られる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「研修」のカテゴリに、終了したイベントが1件ある</t>
+  </si>
+  <si>
+    <t xml:space="preserve">下段の「カテゴリから探す」で「研修」を選ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">終了したイベントも「終了」の表示付きで並ぶ。上段の「公開中のイベント」は変わらない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">過去の開催実績を見せるための仕組み。「すべて」を選ぶと全件が並ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">件数が多いときは左右のボタンで横に送れる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">公開中のイベントが、画面の幅に収まらない件数ある</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一覧の左右に出るボタンを押す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベント1件ぶんずつ横に送られる。先頭では左、末尾では右のボタンが押せなくなる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">横スクロールバーが出ない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベントが並んでいる列の下端を見る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">横方向のスクロールバーが表示されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">左右のボタンで操作させるため、スクロールバーは隠している</t>
+  </si>
+  <si>
+    <t xml:space="preserve">件数が少ないときは送りボタンが出ない</t>
   </si>
   <si>
     <t xml:space="preserve">公開中のイベントが3件だけの状態</t>
   </si>
   <si>
-    <t xml:space="preserve">公開イベント一覧を開く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">左右のボタンが表示されない。カードが引き伸ばされず一定幅で並ぶ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">残席が閾値以下のとき残り枚数が出る</t>
-  </si>
-  <si>
-    <t xml:space="preserve">閾値10・残席が10以下の券種があるイベント</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公開イベントページ（S-05）を開く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公開イベントページにイベント名・日時・場所・説明文・券種が表示される。「残り○枚」が出る。閾値を超える残席では表示されない（F-08 / F-31）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プレビューでは申込導線が出ない</t>
+    <t xml:space="preserve">左右のボタンが出ない。イベントが横に引き伸ばされず、一定の幅で並ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベントページに内容が表示され、残りが少ないと枚数が出る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「残席を表示し始める枚数」が10で、残りが10以下の券種があるイベント</t>
+  </si>
+  <si>
+    <t xml:space="preserve">そのイベントの公開ページを開く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベント名・日時・開催場所・説明文・券種が表示される。残りが10以下の券種には「残り○枚」が出て、10を超える券種には出ない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-08 / F-31 ／ 残りが多いうちは出さない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プレビューでは申込ボタンが出ない</t>
   </si>
   <si>
     <t xml:space="preserve">主催者としてログインしている</t>
   </si>
   <si>
-    <t xml:space="preserve">イベント詳細（S-04）から「プレビュー」を開く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プレビューである旨の帯が出て、「申し込む」「申込を確認する」が表示されない（F-10）</t>
+    <t xml:space="preserve">イベント詳細の画面から「プレビュー」を開く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プレビューであることを示す帯が出る。「申し込む」「申込を確認する」は表示されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-10 ／ 公開前に見え方を確かめるための画面</t>
   </si>
   <si>
     <t xml:space="preserve">・申込フロー</t>
   </si>
   <si>
-    <t xml:space="preserve">参加者が券種を選んで申し込み、受付コードとQRコードを受け取るまでの流れと、定員・締切・重複の制御が正しく動作すること。</t>
+    <t xml:space="preserve">参加者が券種を選んで申し込み、受付コードとQRコードを受け取るまでの流れと、定員・締切・重複申込の制御が正しく働くこと。</t>
   </si>
   <si>
     <t xml:space="preserve">申込フロー</t>
   </si>
   <si>
-    <t xml:space="preserve">申込が完了して受付コードが発行される</t>
-  </si>
-  <si>
-    <t xml:space="preserve">空きのある公開イベントがある</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公開ページ →「申し込む」→ 券種選択・氏名・メール・パスワード入力 → 確認 → 申し込む</t>
-  </si>
-  <si>
-    <t xml:space="preserve">氏名とメールアドレスは必須で、未入力だと進めない。申込完了画面（S-07）に遷移し、受付コードが表示される（F-06 / F-11 / F-24）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">受付コードは英大文字と数字の8桁になる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">申込を完了した直後</t>
+    <t xml:space="preserve">申し込むと受付コードが発行される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">空きのある公開中のイベントがある</t>
+  </si>
+  <si>
+    <t xml:space="preserve">公開ページで「申し込む」→ 券種を選び氏名・メールアドレス・パスワードを入力 → 確認画面 →「申し込む」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">氏名とメールアドレスは未入力だと先に進めない。申込完了の画面に切り替わり、受付コードが表示される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-06 / F-11 / F-24 ／ パスワードは後から自分の申込を確認するために使う</t>
+  </si>
+  <si>
+    <t xml:space="preserve">受付コードは読み間違えにくい8桁になる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込を終えた直後</t>
   </si>
   <si>
     <t xml:space="preserve">表示された受付コードを確認する</t>
   </si>
   <si>
-    <t xml:space="preserve">8桁で、O・0・I・1 を含まない英大文字と数字のみ（D-32）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">申込完了にQRコードが表示される</t>
-  </si>
-  <si>
-    <t xml:space="preserve">申込完了画面を確認する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">受付コードの文字列とQRコードが併記される（F-24）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">確認画面から入力内容を修正できる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">申込内容確認（S-13）を表示している</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「入力内容を修正する」を押して値を変え、再度確認へ進む</t>
-  </si>
-  <si>
-    <t xml:space="preserve">申込フォームへ戻り、入力値が保持されている。修正が確認画面に反映される</t>
-  </si>
-  <si>
-    <t xml:space="preserve">締切時刻ちょうどは受け付ける</t>
-  </si>
-  <si>
-    <t xml:space="preserve">申込締切が現在時刻と同じイベント</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公開ページから申し込む</t>
-  </si>
-  <si>
-    <t xml:space="preserve">申し込める（D-06）</t>
+    <t xml:space="preserve">8桁で、英大文字と数字だけが使われている。見間違えやすい O・0・I・1 は含まれない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-32 ／ 当日、口頭や手書きで伝えても取り違えないようにするため</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込完了の画面にQRコードが出る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込完了の画面を確認する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">受付コードの文字と、同じ内容のQRコードが並んで表示される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">確認画面から入力内容を直せる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込内容の確認画面を表示している</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「入力内容を修正する」を押して値を変え、もう一度確認画面へ進む</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入力画面に戻り、先に入れた内容が残っている。直した内容が確認画面に反映される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">締切時刻ちょうどはまだ申し込める</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込締切が現在時刻とちょうど同じイベント</t>
+  </si>
+  <si>
+    <t xml:space="preserve">そのイベントの公開ページから申し込む</t>
+  </si>
+  <si>
+    <t xml:space="preserve">問題なく申し込める</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-06 ／ 受け付けられる境界のちょうど</t>
   </si>
   <si>
     <t xml:space="preserve">締切を過ぎると申し込めない</t>
@@ -712,172 +805,196 @@
     <t xml:space="preserve">申込締切を過ぎたイベント</t>
   </si>
   <si>
-    <t xml:space="preserve">公開ページを開く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「申込受付は終了しました」が表示され、「申し込む」が押せない（D-06）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">満席の券種は選択肢に出ない</t>
+    <t xml:space="preserve">「申込受付は終了しました」と表示され、「申し込む」が押せない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">満席の券種は選べない</t>
   </si>
   <si>
     <t xml:space="preserve">定員に達した券種があるイベント</t>
   </si>
   <si>
-    <t xml:space="preserve">公開ページで券種を確認し、申込フォームを開く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公開ページでは「この券種は満席です」と表示され、申込フォームの選択肢には出ない（F-12）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同じメールアドレスで重複申込できない</t>
+    <t xml:space="preserve">公開ページで券種の状態を見てから、申込フォームを開く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">公開ページには「この券種は満席です」と出る。申込フォームの選択肢にもその券種は出ない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同じイベントに同じメールアドレスで重ねて申し込めない</t>
   </si>
   <si>
     <t xml:space="preserve">すでに申込済みのメールアドレスがある</t>
   </si>
   <si>
-    <t xml:space="preserve">同じイベントに同じメールアドレスで申し込む</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「このメールアドレスはすでに申し込まれています」が表示される（F-12）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">キャンセル後は同じメールで再申込できる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">申込をキャンセル済みのメールアドレスがある</t>
-  </si>
-  <si>
-    <t xml:space="preserve">申し込める。新しい受付コードが発行される（D-09）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2回目以降は登録済みパスワードと照合される</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同じメールアドレスで一度申込済み</t>
-  </si>
-  <si>
-    <t xml:space="preserve">別のイベントに同じメールアドレス・違うパスワードで申し込む</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「このメールアドレスには別のパスワードが登録されています…」が表示される（D-43）</t>
+    <t xml:space="preserve">同じイベントに、同じメールアドレスで申し込む</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「このメールアドレスはすでに申し込まれています」と表示され、受け付けられない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-12 ／ 1件の申込につき1名のため</t>
+  </si>
+  <si>
+    <t xml:space="preserve">キャンセルした後は同じメールアドレスで申し込み直せる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">いったん申し込み、マイチケットからキャンセルしたメールアドレスがある</t>
+  </si>
+  <si>
+    <t xml:space="preserve">問題なく申し込める。新しい受付コードが発行される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-09 ／ 参加者側からのキャンセル操作も、この前提づくりで確認する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2回目以降は最初に決めたパスワードと一致しないと申し込めない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同じメールアドレスで一度申込を済ませてある</t>
+  </si>
+  <si>
+    <t xml:space="preserve">別のイベントに、同じメールアドレスと違うパスワードで申し込む</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「このメールアドレスには別のパスワードが登録されています」と表示され、受け付けられない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-43 ／ パスワードはメールアドレスごとに1つ</t>
   </si>
   <si>
     <t xml:space="preserve">・マイチケット</t>
   </si>
   <si>
-    <t xml:space="preserve">参加者がメールアドレスとパスワードでログインし、自分の申込を確認・キャンセルできること。QRコードの表示条件が正しいこと。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">デモデータを投入し、参加者として1件以上申し込んでいること。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">マイチケット</t>
-  </si>
-  <si>
-    <t xml:space="preserve">メールとパスワードでログインできる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">申込時にパスワードを設定済み</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ヘッダーの「マイチケット」→ メールアドレスとパスワードを入力してログイン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">そのメールアドレスの申込が全件表示される（F-25 / D-43）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">誤ったパスワードではログインできない</t>
-  </si>
-  <si>
-    <t xml:space="preserve">誤ったパスワードでログインする</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「メールアドレスまたはパスワードが正しくありません」が表示される</t>
-  </si>
-  <si>
-    <t xml:space="preserve">登録の有無を区別しない</t>
-  </si>
-  <si>
-    <t xml:space="preserve">未登録のメールアドレスを用意</t>
-  </si>
-  <si>
-    <t xml:space="preserve">未登録のメールアドレスでログインする</t>
-  </si>
-  <si>
-    <t xml:space="preserve">登録済みで誤パスワードの場合と同じ文言が出る。登録の有無が判別できない（D-43）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QRを読むと受付コードが表示される</t>
-  </si>
-  <si>
-    <t xml:space="preserve">参加確定かつ開催前の申込がある</t>
-  </si>
-  <si>
-    <t xml:space="preserve">マイチケットに表示されたQRコードをスマートフォンのカメラで読み取る</t>
-  </si>
-  <si>
-    <t xml:space="preserve">画面に表示されている受付コードと同一の8桁がスマートフォン上に表示される</t>
-  </si>
-  <si>
-    <t xml:space="preserve">スマートフォンでの確認</t>
-  </si>
-  <si>
-    <t xml:space="preserve">キャンセル済みはQRを表示しない</t>
+    <t xml:space="preserve">参加者がメールアドレスとパスワードで自分の申込を確認し、キャンセルできること。QRコードが出る条件が正しいこと。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">デモデータを入れ、参加者として1件以上申し込んである状態。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メールアドレスとパスワードで申込を確認できる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込のときにパスワードを決めてある</t>
+  </si>
+  <si>
+    <t xml:space="preserve">画面上部の「マイチケット」から、メールアドレスとパスワードを入力する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">そのメールアドレスで申し込んだものが、イベントをまたいで全件表示される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-25 / D-43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パスワードが違うと確認できない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">わざと違うパスワードを入力する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「メールアドレスまたはパスワードが正しくありません」と表示され、中身は見られない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">登録がないメールアドレスでも同じ文言が出る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一度も申し込んでいないメールアドレスを用意する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">そのメールアドレスで確認しようとする</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パスワードを間違えたときとまったく同じ文言が出る。そのメールアドレスが登録済みかどうかは分からない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-43 ／ 誰が申し込んでいるかを外部に知らせないため</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QRコードを読むと受付コードが表示される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">受付を済ませた（参加確定の）申込が、開催前のイベントにある</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マイチケットに出ているQRコードを、スマートフォンのカメラで読み取る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">画面に出ている受付コードと同じ8桁が、スマートフォンの側に表示される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スマートフォンを使って確認する項目</t>
+  </si>
+  <si>
+    <t xml:space="preserve">キャンセルした申込にはQRコードが出ない</t>
   </si>
   <si>
     <t xml:space="preserve">キャンセル済みの申込がある</t>
   </si>
   <si>
-    <t xml:space="preserve">マイチケットで該当の申込を確認する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QRコードが表示されない。状態は「キャンセル済み」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">終了済みは履歴表示のみでキャンセル不可</t>
+    <t xml:space="preserve">マイチケットでその申込を開く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QRコードが表示されない。状態は「キャンセル済み」と出る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">終了したイベントは記録の確認だけでキャンセルできない</t>
   </si>
   <si>
     <t xml:space="preserve">終了したイベントの申込がある</t>
   </si>
   <si>
-    <t xml:space="preserve">「終了」と表示され、QRもキャンセルボタンも出ない（D-10）</t>
+    <t xml:space="preserve">「終了」と表示され、QRコードもキャンセルのボタンも出ない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-10 ／ 終了後の取り消しは意味がないため</t>
   </si>
   <si>
     <t xml:space="preserve">・参加者管理・受付</t>
   </si>
   <si>
-    <t xml:space="preserve">主催者が参加者を検索・受付・編集・キャンセルでき、名簿をCSVで出力できること。受付操作で画面の要素がずれないこと。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">主催者としてログインし、申込のあるイベントの参加者一覧（S-08）を開いていること。</t>
+    <t xml:space="preserve">主催者が参加者を探し、当日の受付をし、内容を直し、キャンセルできること。名簿をCSVで取り出せること。操作しても画面の要素が動かないこと。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">主催者としてログインし、申込のあるイベントの参加者一覧を開いていること。</t>
   </si>
   <si>
     <t xml:space="preserve">参加者管理・受付</t>
   </si>
   <si>
-    <t xml:space="preserve">参加者が一覧に表示される</t>
+    <t xml:space="preserve">申込が一覧に表示される</t>
   </si>
   <si>
     <t xml:space="preserve">申込が9件あるイベント</t>
   </si>
   <si>
-    <t xml:space="preserve">参加者一覧を開く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9件が申込日時の昇順で表示され、上部の数値タイルと件数が一致する（F-15 / D-36）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">氏名・メール・受付コードで検索できる</t>
+    <t xml:space="preserve">そのイベントの参加者一覧を開く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9件が申し込んだ順に並び、画面上部の集計欄の件数と一致する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-15 / D-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">氏名・メールアドレス・受付コードで探せる</t>
   </si>
   <si>
     <t xml:space="preserve">参加者一覧を開いている</t>
   </si>
   <si>
-    <t xml:space="preserve">検索欄に氏名の一部、メールの一部、受付コードをそれぞれ入力する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">いずれでも該当する参加者だけに絞り込まれる（F-15）</t>
+    <t xml:space="preserve">検索欄に、氏名の一部・メールアドレスの一部・受付コードを、それぞれ入力する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">どれを入力しても、該当する参加者だけに絞られる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-15 ／ 当日の受付は、この検索に受付コードを入れて行う</t>
   </si>
   <si>
     <t xml:space="preserve">参加者一覧のページを送れる</t>
@@ -886,100 +1003,115 @@
     <t xml:space="preserve">申込が26件以上あるイベントの参加者一覧を開いている</t>
   </si>
   <si>
-    <t xml:space="preserve">ページ送りで2ページ目へ移動し、その後に受付状況の絞り込みを変更する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1ページ25件ずつ区切られ、2ページ目に26件目以降が出る。絞り込みを変更すると1ページ目に戻る（F-15）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">デモデータでは件数が足りないため、定員の大きいイベントに申込を追加してから実施する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">日本語入力で母音が落ちない</t>
+    <t xml:space="preserve">ページ送りで2ページ目を開き、そのあと受付状況の絞り込みを変える</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1ページ25件ずつ区切られ、2ページ目に26件目以降が出る。絞り込みを変えると1ページ目に戻る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-15 ／ デモデータでは件数が足りないため、定員の大きいイベントに申込を足してから行う</t>
+  </si>
+  <si>
+    <t xml:space="preserve">日本語入力の途中で文字が欠けない</t>
   </si>
   <si>
     <t xml:space="preserve">参加者一覧の検索欄</t>
   </si>
   <si>
-    <t xml:space="preserve">「やまだ」と入力して変換する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">入力した通りに表示される。子音だけが残る現象が起きない</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMEの確認</t>
-  </si>
-  <si>
-    <t xml:space="preserve">受付すると状態が参加確定に変わる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">未受付の参加者がいる</t>
+    <t xml:space="preserve">「やまだ」と入力して漢字に変換する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入力したとおりに表示される。変換の途中で文字が消えたり、一部だけが残ったりしない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">日本語入力（かな漢字変換）中の動作確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">受付をすると状態が「参加確定」に変わる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">まだ受付していない参加者がいる</t>
   </si>
   <si>
     <t xml:space="preserve">その行の「受付」を押す</t>
   </si>
   <si>
-    <t xml:space="preserve">状態が「申し込み済み」から「参加確定」に変わり、受付日時が入る（F-16）</t>
+    <t xml:space="preserve">状態が「申し込み済み」から「参加確定」に変わり、受付した日時が記録される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-16</t>
   </si>
   <si>
     <t xml:space="preserve">受付を取り消せる</t>
   </si>
   <si>
-    <t xml:space="preserve">受付済みの参加者がいる</t>
+    <t xml:space="preserve">すでに受付を済ませた参加者がいる</t>
   </si>
   <si>
     <t xml:space="preserve">その行の「受付取消」を押す</t>
   </si>
   <si>
-    <t xml:space="preserve">状態が「申し込み済み」に戻り、受付日時が空になる</t>
+    <t xml:space="preserve">状態が「申し込み済み」に戻り、受付日時の記録が消える</t>
+  </si>
+  <si>
+    <t xml:space="preserve">取り違えて受付したときのやり直しに使う</t>
   </si>
   <si>
     <t xml:space="preserve">主催者が申込をキャンセルできる</t>
   </si>
   <si>
-    <t xml:space="preserve">受付済み（参加確定）の参加者がいる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">その行の「キャンセル」→ 確認ダイアログで OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">状態が「キャンセル済み」に変わり、券種の残席が1つ戻る。受付済みでも主催者はキャンセルできる（F-13 / D-10）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">参加者側からのキャンセルは 4-9 の前提として実施する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">受付操作で集計とボタンの位置がずれない</t>
-  </si>
-  <si>
-    <t xml:space="preserve">未受付と受付済みが混在している</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「受付」「受付取消」を数回押す</t>
-  </si>
-  <si>
-    <t xml:space="preserve">上部の数値タイルと、各行の操作ボタンの位置が動かない</t>
-  </si>
-  <si>
-    <t xml:space="preserve">状態で絞り込んでも要素の位置がずれない</t>
-  </si>
-  <si>
-    <t xml:space="preserve">参加確定とキャンセル済みが混在している</t>
-  </si>
-  <si>
-    <t xml:space="preserve">状態の絞り込みを「すべての状態」と「申込あり」で切り替える</t>
-  </si>
-  <si>
-    <t xml:space="preserve">テキストとボタンの位置が動かない。最終行にも罫線が引かれている</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSVを出力してExcelで開ける</t>
+    <t xml:space="preserve">受付を済ませた（参加確定の）参加者がいる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その行の「キャンセル」を押し、確認に「OK」で答える</t>
+  </si>
+  <si>
+    <t xml:space="preserve">状態が「キャンセル済み」に変わり、その券種の残りが1つ戻る。受付済みでも主催者はキャンセルできる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-13 / D-10 ／ 当日の欠席連絡などを主催者側で反映するため</t>
+  </si>
+  <si>
+    <t xml:space="preserve">受付しても画面の要素が動かない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未受付と受付済みが混ざっている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「受付」「受付取消」を続けて数回押す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">画面上部の集計欄と、各行のボタンの位置が動かない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数字の桁数が変わっても幅が変わらないこと</t>
+  </si>
+  <si>
+    <t xml:space="preserve">絞り込んでも画面の要素が動かない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参加確定とキャンセル済みが混ざっている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">受付状況の絞り込みを「すべての状態」と「申込あり」で切り替える</t>
+  </si>
+  <si>
+    <t xml:space="preserve">文字とボタンの位置が横にずれない。一番下の行にも罫線が引かれている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">表示件数が変わってもレイアウトが動かないこと</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSVを取り出してExcelで開ける</t>
   </si>
   <si>
     <t xml:space="preserve">「CSVを出力」を押し、保存されたファイルをExcelで開く</t>
   </si>
   <si>
-    <t xml:space="preserve">文字化けせずに開ける（UTF-8 BOM付き）。カスタム項目も列として出力される（F-17）</t>
+    <t xml:space="preserve">文字化けせずに開ける。申込フォームに足した独自の質問も、列として出ている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-17</t>
   </si>
   <si>
     <t xml:space="preserve">CSVにキャンセル済みも含まれる</t>
@@ -988,223 +1120,265 @@
     <t xml:space="preserve">キャンセル済みの申込があるイベント</t>
   </si>
   <si>
-    <t xml:space="preserve">CSVを出力して内容を確認する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">参加確定とキャンセル済みの両方が出力される（F-17）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">参加者情報を編集できる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">行の「編集」からメールアドレスを修正して保存</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一覧に反映される。既存の他の申込と同じメールには変更できない（F-30）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">絞り込み結果へのメールが履歴に残る</t>
+    <t xml:space="preserve">CSVを取り出して中身を確認する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参加確定のものとキャンセル済みのものが、どちらも出力されている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-17 ／ 状態の列で見分けられる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参加者の申込内容を直せる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">行の「編集」からメールアドレスを直して保存する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一覧に反映される。同じイベントの他の申込と同じメールアドレスには変更できない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-30 ／ メールアドレスの打ち間違いに対応するため</t>
+  </si>
+  <si>
+    <t xml:space="preserve">絞り込んだ相手へのメールが履歴に残る</t>
   </si>
   <si>
     <t xml:space="preserve">参加者を絞り込んでいる</t>
   </si>
   <si>
-    <t xml:space="preserve">「絞り込み結果へメール」→ 件名と本文を確認して送信</t>
-  </si>
-  <si>
-    <t xml:space="preserve">既定のメールソフトが起動し、設定の「送信履歴」に件名と宛先数が記録される（F-19 / F-28）</t>
+    <t xml:space="preserve">「絞り込み結果へメール」を押し、件名と本文を確認して送信する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ふだん使っているメールソフトが立ち上がる。設定画面の「送信履歴」に件名と宛先の数が記録される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-19 / F-28 ／ 送信そのものはメールソフトが行う</t>
   </si>
   <si>
     <t xml:space="preserve">・ダッシュボード</t>
   </si>
   <si>
-    <t xml:space="preserve">全体の状況が数値タイル・円グラフ・棒グラフで正しく集計されて表示されること。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">主催者としてログインし、デモデータを投入していること。</t>
+    <t xml:space="preserve">全体の状況が、数値・円グラフ・棒グラフで正しく集計されて表示されること。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">主催者としてログインし、デモデータを入れた状態。</t>
   </si>
   <si>
     <t xml:space="preserve">ダッシュボード</t>
   </si>
   <si>
-    <t xml:space="preserve">数値タイルの集計が正しい</t>
-  </si>
-  <si>
-    <t xml:space="preserve">デモデータ投入直後</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ダッシュボード（S-01）を開き、4枚のタイルを確認する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公開中のイベント数・申込数・定員充足率・チェックイン率が実データと一致する（F-18）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カテゴリ別の円グラフが正しい</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「カテゴリ別の開催状況」を確認し、扇にマウスを重ねる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カテゴリごとの件数と割合が実データと一致する。凡例の合計が全イベント数になる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">開催予定に公開中のみ出る</t>
-  </si>
-  <si>
-    <t xml:space="preserve">終了・下書きを含むデータ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「開催予定」の一覧を確認する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公開中で未終了のイベントだけが開催日時の昇順で並ぶ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">シリーズ横断の棒グラフが第1回から並ぶ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同一シリーズのイベントが2件ある</t>
+    <t xml:space="preserve">上部の4つの数値が実際のデータと合っている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">デモデータを入れた直後</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ダッシュボードを開き、上部に並ぶ4つの数値を確認する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">公開中のイベント数・申込数・定員に対する充足率・受付を済ませた割合が、実際のデータと一致する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カテゴリ別の円グラフが実際のデータと合っている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「カテゴリ別の開催状況」を確認し、扇の部分にマウスを重ねる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カテゴリごとの件数と割合が実際のデータと一致する。凡例の合計が全イベント数と等しい</t>
+  </si>
+  <si>
+    <t xml:space="preserve">どの種類のイベントを多く開いているかを見るための表示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「開催予定」に公開中のものだけが並ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">終了したイベントと下書きを含むデータ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ダッシュボードの「開催予定」の一覧を確認する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">公開中でまだ終わっていないイベントだけが、開催日の近い順に並ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シリーズの棒グラフが第1回から順に並ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同じシリーズのイベントが2件ある</t>
   </si>
   <si>
     <t xml:space="preserve">「シリーズ横断の実績」を確認する</t>
   </si>
   <si>
-    <t xml:space="preserve">左端が第1回で、回ごとの申込数が棒の高さと数値で示される（改善⑤）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">下書きの回がグレーで表示される</t>
-  </si>
-  <si>
-    <t xml:space="preserve">シリーズの2回目が下書きのデータ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同上の棒グラフを確認する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">下書きの回の棒がグレーで描かれ、公開中の回と区別できる</t>
+    <t xml:space="preserve">左端が第1回で、回ごとの申込数が棒の高さと数値で示される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">回を重ねるごとの集客の変化を見るための表示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">下書きの回が灰色で区別される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シリーズの2回目が下書きになっているデータ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「シリーズ横断の実績」の棒グラフを確認する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">下書きの回の棒が灰色で描かれ、公開中の回と見分けられる</t>
   </si>
   <si>
     <t xml:space="preserve">・設定・データ管理</t>
   </si>
   <si>
-    <t xml:space="preserve">主催者ログイン、組織ブランディング、カテゴリ管理、メールテンプレート、JSONの入出力とデータ初期化が正しく動作すること。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">特記なき場合、主催者としてログインし設定・データ管理（S-09）を開いていること。</t>
+    <t xml:space="preserve">主催者のログイン、組織のロゴとヘッダー画像、カテゴリの管理、メールのひな形、データの書き出しと読み込み、初期化が正しく動くこと。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ことわりがない限り、主催者としてログインし、設定・データ管理の画面を開いていること。</t>
   </si>
   <si>
     <t xml:space="preserve">設定・データ管理</t>
   </si>
   <si>
-    <t xml:space="preserve">初回起動でパスコードを設定する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">全データ初期化の直後</t>
-  </si>
-  <si>
-    <t xml:space="preserve">index.html を開き、4〜16文字の英数字を入力して「設定して開始」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">パスコードが設定され、ダッシュボードに遷移する（F-27 / D-33）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">未認証では管理画面に入れない</t>
+    <t xml:space="preserve">初めて開いたときにパスコードを決める</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全データを初期化した直後</t>
+  </si>
+  <si>
+    <t xml:space="preserve">index.html を開き、4〜16文字の英数字を入力して「設定して開始」を押す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パスコードが登録され、ダッシュボードが開く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-27 / D-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ログインしていないと管理画面に入れない</t>
   </si>
   <si>
     <t xml:space="preserve">ログアウトしている</t>
   </si>
   <si>
-    <t xml:space="preserve">アドレスバーのハッシュを #/events に変更する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">主催者ログイン（S-12）へリダイレクトされる（F-27）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">再読込するとログアウトするがデータは残る</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ログインしてデータがある状態</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ページを再読込する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ログイン画面に戻るが、ログインし直すとイベント・申込がすべて残っている</t>
+    <t xml:space="preserve">ブラウザのアドレス欄の末尾を「#/events」に書き換えて開く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">管理画面は開かず、主催者ログインの画面に戻される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-27 ／ URLを直接指定しても入れないこと</t>
+  </si>
+  <si>
+    <t xml:space="preserve">開き直すとログアウトするが、データは残っている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ログインし、イベントと申込がある状態</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ブラウザで画面を再読み込みする</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ログイン画面に戻る。ログインし直すと、イベントも申込もすべて残っている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ログイン状態は意図的に保存していない（画面を閉じると解除される）</t>
   </si>
   <si>
     <t xml:space="preserve">パスコードを変更できる</t>
   </si>
   <si>
-    <t xml:space="preserve">「パスコード変更」タブを開いている</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現在のパスコードと新しいパスコードを入力して変更する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">変更され、次回から新しいパスコードでログインできる。現パスコードが違うとエラー（D-33）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">組織ロゴとヘッダー画像が公開側に反映される</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「一般設定」タブを開いている</t>
-  </si>
-  <si>
-    <t xml:space="preserve">組織ロゴとヘッダー画像を設定して保存し、公開イベント一覧を開く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ヘッダーにロゴ、トップにヘッダー画像が表示される（F-09 / D-37 / D-38）</t>
+    <t xml:space="preserve">「パスコード変更」のタブを開いている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">今のパスコードと新しいパスコードを入力して変更する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">変更され、次回から新しいパスコードで入れる。今のパスコードを間違えるとエラーになる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">組織のロゴとヘッダー画像が参加者側に出る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「一般設定」のタブを開いている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">組織ロゴとヘッダー画像を設定して保存し、参加者向けの公開イベント一覧を開く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">画面上部にロゴ、一覧の先頭にヘッダー画像が表示される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-09 / D-37 / D-38</t>
   </si>
   <si>
     <t xml:space="preserve">カテゴリを追加・削除・並べ替えできる</t>
   </si>
   <si>
-    <t xml:space="preserve">「カテゴリ管理」タブを開いている</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カテゴリを追加し、↑↓で並べ替え、未使用のものを削除する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">イベント作成の選択肢と公開側の絞り込みに反映される（D-12）</t>
+    <t xml:space="preserve">「カテゴリ管理」のタブを開いている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カテゴリを追加し、↑↓で順番を変え、どのイベントにも使っていないものを削除する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベント作成時の選択肢と、参加者側の絞り込みの選択肢に反映される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-12</t>
   </si>
   <si>
     <t xml:space="preserve">使用中のカテゴリは削除できない</t>
   </si>
   <si>
-    <t xml:space="preserve">イベントで使用中のカテゴリがある</t>
+    <t xml:space="preserve">イベントで使っているカテゴリがある</t>
   </si>
   <si>
     <t xml:space="preserve">そのカテゴリの「削除」を押す</t>
   </si>
   <si>
-    <t xml:space="preserve">「このカテゴリを使用しているイベントがあるため削除できません」が表示される（D-12）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">差し込み文字列をクリックで挿入できる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「メールテンプレート」タブを開いている</t>
-  </si>
-  <si>
-    <t xml:space="preserve">本文にカーソルを置き、下のチップ（例: {氏名}）をクリックする</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カーソル位置に差し込み文字列が挿入される（F-19）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JSONを書き出して読み込むと復元される</t>
+    <t xml:space="preserve">「このカテゴリを使用しているイベントがあるため削除できません」と表示され、削除されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-12 ／ 分類のないイベントが生まれることを防ぐため</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メール文面に差し込み項目をクリックで入れられる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「メールテンプレート」のタブを開いている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本文の入れたい位置にカーソルを置き、下に並ぶ「{氏名}」などのボタンを押す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カーソルのあった位置に、その差し込み項目が入る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-19 ／ 送信時にイベント名や氏名に置き換わる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">データを書き出して読み込むと元に戻る</t>
   </si>
   <si>
     <t xml:space="preserve">イベント・申込・画像があるデータ</t>
   </si>
   <si>
-    <t xml:space="preserve">「データ管理」でJSONを書き出し → 全データ初期化 → 書き出したJSONを読み込む</t>
-  </si>
-  <si>
-    <t xml:space="preserve">イベント・申込・カテゴリ・組織設定・画像がすべて復元される（F-20）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">資料を含めるかは選択できる</t>
+    <t xml:space="preserve">「データ管理」でファイルに書き出し、全データを初期化してから、書き出したファイルを読み込む</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベント・申込・カテゴリ・組織の設定・画像が、すべて元どおりになる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-20 ／ 唯一のバックアップ手段。資料を含めるかは選べる</t>
   </si>
   <si>
     <t xml:space="preserve">デモデータの投入と全データの初期化ができる</t>
@@ -1213,22 +1387,22 @@
     <t xml:space="preserve">イベントと申込が登録されている</t>
   </si>
   <si>
-    <t xml:space="preserve">「デモデータを投入」→ 確認 → 内容を確認。続けて「全データを初期化」→ 確認</t>
-  </si>
-  <si>
-    <t xml:space="preserve">投入では既存データが置き換わり、F節のデモデータが入る。初期化するとイベント・申込・資料・設定がすべて消え、ログアウトしてパスコード設定画面に戻る（F-21）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">初期化は元に戻せない。本シートの最後に実施する</t>
+    <t xml:space="preserve">「デモデータを投入」を押して確認し、内容を見る。続けて「全データを初期化」を押して確認する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">投入すると今のデータが置き換わり、動作確認用のイベントと申込が入る。初期化するとイベント・申込・資料・設定がすべて消え、ログアウトしてパスコードの設定画面に戻る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-21 ／ 初期化は元に戻せないため、このシートの最後に行う</t>
   </si>
   <si>
     <t xml:space="preserve">・資料・運営体制</t>
   </si>
   <si>
-    <t xml:space="preserve">運用資料をイベントに紐付けて管理でき、イベントごとの運営体制を記録できること。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">主催者としてログインしていること。試験データ/資料 のファイルを用意する。</t>
+    <t xml:space="preserve">進行台本や会場図などの資料をイベントごとに管理でき、当日の運営メンバーを記録できること。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">主催者としてログインしていること。試験データ／資料 のファイルを用意する。</t>
   </si>
   <si>
     <t xml:space="preserve">資料・運営体制</t>
@@ -1237,16 +1411,19 @@
     <t xml:space="preserve">資料をイベントに紐付けて登録できる</t>
   </si>
   <si>
-    <t xml:space="preserve">資料（S-16）を開いている</t>
-  </si>
-  <si>
-    <t xml:space="preserve">紐付け先イベントを選び、進行台本_サンプル.pdf を登録する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一覧に「イベント」列付きで表示される（F-34 / D-45）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">組織共通として登録できる</t>
+    <t xml:space="preserve">「資料」の画面を開いている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">紐付け先のイベントを選び、進行台本_サンプル.pdf を登録する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一覧に、どのイベントのものかが分かる形で表示される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-34 / D-45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">どのイベントにも属さない資料として登録できる</t>
   </si>
   <si>
     <t xml:space="preserve">紐付け先に「組織共通」を選んで登録する</t>
@@ -1255,13 +1432,16 @@
     <t xml:space="preserve">一覧に「組織共通」と表示される</t>
   </si>
   <si>
-    <t xml:space="preserve">イベントで絞り込める</t>
+    <t xml:space="preserve">受付マニュアルなど、毎回使う資料を想定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベントごとに絞り込める</t>
   </si>
   <si>
     <t xml:space="preserve">複数のイベントに資料が紐付いている</t>
   </si>
   <si>
-    <t xml:space="preserve">一覧上部の絞り込みでイベントを選ぶ</t>
+    <t xml:space="preserve">「資料」の画面の上部でイベントを選ぶ</t>
   </si>
   <si>
     <t xml:space="preserve">そのイベントの資料だけが表示される。「組織共通のみ」も選べる</t>
@@ -1270,112 +1450,127 @@
     <t xml:space="preserve">イベント詳細から紐付いた資料を開ける</t>
   </si>
   <si>
-    <t xml:space="preserve">イベントに資料を紐付け済み</t>
-  </si>
-  <si>
-    <t xml:space="preserve">イベント詳細（S-04）の「このイベントの資料」からダウンロードする</t>
-  </si>
-  <si>
-    <t xml:space="preserve">紐付けた資料が一覧され、原本のまま開ける</t>
-  </si>
-  <si>
-    <t xml:space="preserve">運営体制をパネル内で編集できる</t>
+    <t xml:space="preserve">イベントに資料を紐付けてある</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベント詳細の「このイベントの資料」からダウンロードする</t>
+  </si>
+  <si>
+    <t xml:space="preserve">紐付けた資料が並び、登録したときのまま開ける</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当日の進行で、その場から開くことを想定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">運営体制を編集できる</t>
   </si>
   <si>
     <t xml:space="preserve">イベント詳細を開いている</t>
   </si>
   <si>
-    <t xml:space="preserve">「運営体制」の「編集」から責任者とメンバーを追加・削除して保存</t>
-  </si>
-  <si>
-    <t xml:space="preserve">パネルに反映される。参加者側には表示されない（F-35 / D-44）</t>
+    <t xml:space="preserve">「運営体制」の「編集」から、責任者とメンバーを追加・削除して保存する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その場で表示に反映される。参加者側の画面には出ない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-35 / D-44 ／ 誰が何を担当するかを記録しておくため</t>
   </si>
   <si>
     <t xml:space="preserve">・境界値・異常系</t>
   </si>
   <si>
-    <t xml:space="preserve">0件・上限・不正入力・想定外のエラーに対して、アプリが落ちず、利用者に次の行動が分かる表示を出すこと。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">各項目の前提条件に応じてデータ状態を用意する。</t>
+    <t xml:space="preserve">データが1件もないとき、上限いっぱいのとき、誤った入力をしたときに、画面が止まらず、利用者が次に何をすればよいか分かる表示が出ること。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">項目ごとに、記載された状態のデータを用意する。</t>
   </si>
   <si>
     <t xml:space="preserve">境界値・異常系</t>
   </si>
   <si>
-    <t xml:space="preserve">データ0件でもエラーが出ない</t>
+    <t xml:space="preserve">データが1件もなくてもエラーにならない</t>
   </si>
   <si>
     <t xml:space="preserve">パスコードを設定し、各画面を順に開く</t>
   </si>
   <si>
-    <t xml:space="preserve">エラーが出ず、各一覧に次の操作を促す空状態の文言が表示される</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTML特殊文字がエスケープされる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">イベント名に &lt;script&gt;alert(1)&lt;/script&gt; を設定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">イベント一覧・イベント詳細・公開ページ・CSVで表示を確認する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">タグとして解釈されず、文字列のまま表示される</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XSS対策の確認</t>
-  </si>
-  <si>
-    <t xml:space="preserve">長いイベント名でレイアウトが崩れない</t>
-  </si>
-  <si>
-    <t xml:space="preserve">イベント名を100文字（上限）で設定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一覧・カード・ダッシュボードで表示を確認する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">はみ出さず、カードでは2行で省略される（D-11）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">既存データがある状態でスキーマが上がる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">旧バージョン（スキーマ1）のデータがある状態</t>
-  </si>
-  <si>
-    <t xml:space="preserve">このバージョンの index.html を開く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エラーなく既存のイベント・申込が読み込まれ、資料ストアが追加される</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IndexedDBの後方互換</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2MB超の画像を拒否する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">試験データ/画像/生成/試験_2MB超_900x900.png を用意</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カバー画像・組織ロゴ・ヘッダー画像のそれぞれで選択する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「画像は2MB以内のファイルを選択してください」が表示され、登録されない</t>
-  </si>
-  <si>
-    <t xml:space="preserve">資料の上限と対応外形式を拒否する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">試験_5MB超.pdf と 試験_対応外形式.txt を用意</t>
-  </si>
-  <si>
-    <t xml:space="preserve">資料（S-16）でそれぞれを登録しようとする</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「ファイルは5MB以内のものを選択してください」「対応していないファイル形式です」が出る（D-40）</t>
+    <t xml:space="preserve">エラーにならず、それぞれの一覧に「まだ登録がない」ことと、次にする操作の案内が出る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入力した文字が命令として動いてしまわない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベント名に &lt;script&gt;alert(1)&lt;/script&gt; を入れて保存する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベント一覧・イベント詳細・公開ページ・CSVで、それぞれ表示を確認する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">命令として動かず、入力した文字がそのまま文字として表示される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">悪意ある文字列を書き込まれても動作しないことの確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">長いイベント名でも表示が崩れない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベント名を上限の100文字にする</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベント一覧・一覧のカード・ダッシュボードで表示を確認する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">枠からはみ出さず、一覧のカードでは2行までで省略される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">以前に作ったデータが残っていても読み込める</t>
+  </si>
+  <si>
+    <t xml:space="preserve">前のバージョンで作ったデータが残っている状態</t>
+  </si>
+  <si>
+    <t xml:space="preserve">今回の index.html を開く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エラーにならず、以前のイベントと申込がそのまま読み込まれ、資料の保存先が追加される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">保存の仕組みを変えても、既存のデータが失われないことの確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2MBを超える画像は登録できない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験データ／画像／生成／試験_2MB超_900x900.png を用意する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カバー画像・組織ロゴ・ヘッダー画像のそれぞれで、この画像を選ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「画像は2MB以内のファイルを選択してください」と表示され、登録されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">データはブラウザ内に保存するため、容量に上限を設けている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大きすぎる資料と対応外の形式は登録できない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験_5MB超.pdf と 試験_対応外形式.txt を用意する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「資料」の画面で、それぞれを登録しようとする</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「ファイルは5MB以内のものを選択してください」「対応していないファイル形式です」と表示され、登録されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-40</t>
   </si>
   <si>
     <t xml:space="preserve">★ NG項目一覧（試験でNGだった点と対応）</t>
@@ -2241,7 +2436,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>354</v>
+        <v>404</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2250,10 +2445,10 @@
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>355</v>
+        <v>405</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -2261,10 +2456,10 @@
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>356</v>
+        <v>406</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -2272,7 +2467,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="34" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -2284,7 +2479,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="27"/>
       <c r="L6" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
@@ -2293,22 +2488,22 @@
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>17</v>
@@ -2323,19 +2518,19 @@
         <v>23</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2349,28 +2544,30 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>357</v>
+        <v>407</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>358</v>
+        <v>408</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>359</v>
+        <v>409</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>360</v>
+        <v>410</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>361</v>
+        <v>411</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="2"/>
       <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
+      <c r="O8" s="13" t="s">
+        <v>412</v>
+      </c>
       <c r="P8" s="13"/>
     </row>
     <row r="9" spans="1:16">
@@ -2381,25 +2578,27 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>362</v>
+        <v>413</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>363</v>
+        <v>414</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>364</v>
+        <v>415</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>365</v>
+        <v>416</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="2"/>
       <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
+      <c r="O9" s="13" t="s">
+        <v>417</v>
+      </c>
       <c r="P9" s="13"/>
     </row>
     <row r="10" spans="1:16">
@@ -2410,25 +2609,27 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>366</v>
+        <v>418</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>367</v>
+        <v>419</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>368</v>
+        <v>420</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>369</v>
+        <v>421</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="2"/>
       <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
+      <c r="O10" s="13" t="s">
+        <v>422</v>
+      </c>
       <c r="P10" s="13"/>
     </row>
     <row r="11" spans="1:16">
@@ -2439,25 +2640,27 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>370</v>
+        <v>423</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>371</v>
+        <v>424</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>372</v>
+        <v>425</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>373</v>
+        <v>426</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
+      <c r="O11" s="13" t="s">
+        <v>427</v>
+      </c>
       <c r="P11" s="13"/>
     </row>
     <row r="12" spans="1:16">
@@ -2468,25 +2671,27 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>374</v>
+        <v>428</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>375</v>
+        <v>429</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>376</v>
+        <v>430</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>377</v>
+        <v>431</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="2"/>
       <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
+      <c r="O12" s="13" t="s">
+        <v>432</v>
+      </c>
       <c r="P12" s="13"/>
     </row>
     <row r="13" spans="1:16">
@@ -2497,25 +2702,27 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>378</v>
+        <v>433</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>379</v>
+        <v>434</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>380</v>
+        <v>435</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>381</v>
+        <v>436</v>
       </c>
       <c r="L13" s="13"/>
       <c r="M13" s="2"/>
       <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
+      <c r="O13" s="13" t="s">
+        <v>437</v>
+      </c>
       <c r="P13" s="13"/>
     </row>
     <row r="14" spans="1:16">
@@ -2526,25 +2733,27 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>382</v>
+        <v>438</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>383</v>
+        <v>439</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>384</v>
+        <v>440</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>385</v>
+        <v>441</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="2"/>
       <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
+      <c r="O14" s="13" t="s">
+        <v>442</v>
+      </c>
       <c r="P14" s="13"/>
     </row>
     <row r="15" spans="1:16">
@@ -2555,25 +2764,27 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>386</v>
+        <v>443</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>387</v>
+        <v>444</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>388</v>
+        <v>445</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>389</v>
+        <v>446</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="2"/>
       <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
+      <c r="O15" s="13" t="s">
+        <v>447</v>
+      </c>
       <c r="P15" s="13"/>
     </row>
     <row r="16" spans="1:16">
@@ -2584,26 +2795,26 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>390</v>
+        <v>448</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>391</v>
+        <v>449</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>392</v>
+        <v>450</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>393</v>
+        <v>451</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="2"/>
       <c r="N16" s="13"/>
       <c r="O16" s="13" t="s">
-        <v>394</v>
+        <v>452</v>
       </c>
       <c r="P16" s="13"/>
     </row>
@@ -2615,26 +2826,26 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>395</v>
+        <v>453</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>396</v>
+        <v>454</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>397</v>
+        <v>455</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>398</v>
+        <v>456</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="2"/>
       <c r="N17" s="13"/>
       <c r="O17" s="13" t="s">
-        <v>399</v>
+        <v>457</v>
       </c>
       <c r="P17" s="13"/>
     </row>
@@ -2677,7 +2888,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>400</v>
+        <v>458</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2686,10 +2897,10 @@
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>401</v>
+        <v>459</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -2697,10 +2908,10 @@
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>402</v>
+        <v>460</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -2708,7 +2919,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="34" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -2720,7 +2931,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="27"/>
       <c r="L6" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
@@ -2729,22 +2940,22 @@
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>17</v>
@@ -2759,19 +2970,19 @@
         <v>23</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2785,28 +2996,30 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>403</v>
+        <v>461</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>404</v>
+        <v>462</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>405</v>
+        <v>463</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>406</v>
+        <v>464</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>407</v>
+        <v>465</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="2"/>
       <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
+      <c r="O8" s="13" t="s">
+        <v>466</v>
+      </c>
       <c r="P8" s="13"/>
     </row>
     <row r="9" spans="1:16">
@@ -2817,25 +3030,27 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>408</v>
+        <v>467</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>191</v>
+        <v>463</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>409</v>
+        <v>468</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>410</v>
+        <v>469</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="2"/>
       <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
+      <c r="O9" s="13" t="s">
+        <v>470</v>
+      </c>
       <c r="P9" s="13"/>
     </row>
     <row r="10" spans="1:16">
@@ -2846,20 +3061,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>411</v>
+        <v>471</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>412</v>
+        <v>472</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>413</v>
+        <v>473</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>414</v>
+        <v>474</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="2"/>
@@ -2875,25 +3090,27 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>415</v>
+        <v>475</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>416</v>
+        <v>476</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>417</v>
+        <v>477</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>418</v>
+        <v>478</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
+      <c r="O11" s="13" t="s">
+        <v>479</v>
+      </c>
       <c r="P11" s="13"/>
     </row>
     <row r="12" spans="1:16">
@@ -2904,25 +3121,27 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>419</v>
+        <v>480</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>420</v>
+        <v>481</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>421</v>
+        <v>482</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>422</v>
+        <v>483</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="2"/>
       <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
+      <c r="O12" s="13" t="s">
+        <v>484</v>
+      </c>
       <c r="P12" s="13"/>
     </row>
   </sheetData>
@@ -2964,7 +3183,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>423</v>
+        <v>485</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2973,10 +3192,10 @@
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -2984,10 +3203,10 @@
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>425</v>
+        <v>487</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -2995,7 +3214,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="34" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -3007,7 +3226,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="27"/>
       <c r="L6" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
@@ -3016,22 +3235,22 @@
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>17</v>
@@ -3046,19 +3265,19 @@
         <v>23</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -3072,23 +3291,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>426</v>
+        <v>488</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>427</v>
+        <v>489</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>359</v>
+        <v>409</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>428</v>
+        <v>490</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>429</v>
+        <v>491</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="2"/>
@@ -3104,26 +3323,26 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>430</v>
+        <v>492</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>431</v>
+        <v>493</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>432</v>
+        <v>494</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>433</v>
+        <v>495</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="2"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="s">
-        <v>434</v>
+        <v>496</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -3135,25 +3354,27 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>435</v>
+        <v>497</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>436</v>
+        <v>498</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>437</v>
+        <v>499</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>438</v>
+        <v>500</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="2"/>
       <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
+      <c r="O10" s="13" t="s">
+        <v>501</v>
+      </c>
       <c r="P10" s="13"/>
     </row>
     <row r="11" spans="1:16">
@@ -3164,26 +3385,26 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>440</v>
+        <v>503</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>441</v>
+        <v>504</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>442</v>
+        <v>505</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="s">
-        <v>443</v>
+        <v>506</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -3195,25 +3416,27 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>444</v>
+        <v>507</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>445</v>
+        <v>508</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>446</v>
+        <v>509</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>447</v>
+        <v>510</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="2"/>
       <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
+      <c r="O12" s="13" t="s">
+        <v>511</v>
+      </c>
       <c r="P12" s="13"/>
     </row>
     <row r="13" spans="1:16">
@@ -3224,25 +3447,27 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>448</v>
+        <v>512</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>449</v>
+        <v>513</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>450</v>
+        <v>514</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>451</v>
+        <v>515</v>
       </c>
       <c r="L13" s="13"/>
       <c r="M13" s="2"/>
       <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
+      <c r="O13" s="13" t="s">
+        <v>516</v>
+      </c>
       <c r="P13" s="13"/>
     </row>
   </sheetData>
@@ -3278,29 +3503,29 @@
   <sheetData>
     <row r="1" spans="1:12" ht="26.5">
       <c r="B1" s="24" t="s">
-        <v>452</v>
+        <v>517</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="B2" s="13" t="s">
-        <v>453</v>
+        <v>518</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>454</v>
+        <v>519</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>455</v>
+        <v>520</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>456</v>
+        <v>521</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>457</v>
+        <v>522</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>17</v>
@@ -3309,10 +3534,10 @@
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>458</v>
+        <v>523</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>459</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -3322,7 +3547,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="16" style="17" customWidth="1"/>
@@ -3426,9 +3651,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="B13" s="13" t="s">
-        <v>17</v>
-      </c>
+      <c r="B13" s="13"/>
       <c r="C13" s="13" t="s">
         <v>29</v>
       </c>
@@ -3437,7 +3660,9 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="B14" s="13"/>
+      <c r="B14" s="13" t="s">
+        <v>17</v>
+      </c>
       <c r="C14" s="13" t="s">
         <v>31</v>
       </c>
@@ -3491,18 +3716,18 @@
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="13"/>
+      <c r="C20" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="D20" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="13" t="s">
+    </row>
+    <row r="21" spans="1:12">
+      <c r="B21" s="13" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="B21" s="13"/>
       <c r="C21" s="13" t="s">
         <v>46</v>
       </c>
@@ -3520,23 +3745,77 @@
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="13"/>
+      <c r="C23" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="D23" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="B24" s="13"/>
       <c r="C24" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="13" t="s">
+    </row>
+    <row r="25" spans="1:12">
+      <c r="B25" s="13"/>
+      <c r="C25" s="13" t="s">
         <v>54</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="B26" s="13"/>
+      <c r="C26" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="B27" s="13"/>
+      <c r="C27" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="B28" s="13"/>
+      <c r="C28" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="B29" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="B30" s="13"/>
+      <c r="C30" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -3568,7 +3847,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -3577,10 +3856,10 @@
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -3588,10 +3867,10 @@
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -3599,7 +3878,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="34" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -3611,7 +3890,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="27"/>
       <c r="L6" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
@@ -3620,22 +3899,22 @@
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>17</v>
@@ -3650,19 +3929,19 @@
         <v>23</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -3676,28 +3955,30 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="2"/>
       <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
+      <c r="O8" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="P8" s="13"/>
     </row>
     <row r="9" spans="1:16">
@@ -3708,20 +3989,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="2"/>
@@ -3737,26 +4018,26 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="2"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -3768,25 +4049,27 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
+      <c r="O11" s="13" t="s">
+        <v>100</v>
+      </c>
       <c r="P11" s="13"/>
     </row>
     <row r="12" spans="1:16">
@@ -3797,25 +4080,27 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="2"/>
       <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
+      <c r="O12" s="13" t="s">
+        <v>105</v>
+      </c>
       <c r="P12" s="13"/>
     </row>
     <row r="13" spans="1:16">
@@ -3826,26 +4111,26 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="L13" s="13"/>
       <c r="M13" s="2"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -3857,26 +4142,26 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="2"/>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -3888,25 +4173,27 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="2"/>
       <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
+      <c r="O15" s="13" t="s">
+        <v>119</v>
+      </c>
       <c r="P15" s="13"/>
     </row>
     <row r="16" spans="1:16">
@@ -3917,25 +4204,27 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="2"/>
       <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
+      <c r="O16" s="13" t="s">
+        <v>124</v>
+      </c>
       <c r="P16" s="13"/>
     </row>
     <row r="17" spans="1:16">
@@ -3946,26 +4235,26 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="2"/>
       <c r="N17" s="13"/>
       <c r="O17" s="13" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="P17" s="13"/>
     </row>
@@ -3977,25 +4266,27 @@
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="13" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="L18" s="13"/>
       <c r="M18" s="2"/>
       <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
+      <c r="O18" s="13" t="s">
+        <v>134</v>
+      </c>
       <c r="P18" s="13"/>
     </row>
     <row r="19" spans="1:16">
@@ -4006,26 +4297,26 @@
       </c>
       <c r="E19" s="32"/>
       <c r="F19" s="13" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="L19" s="13"/>
       <c r="M19" s="2"/>
       <c r="N19" s="13"/>
       <c r="O19" s="13" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="P19" s="13"/>
     </row>
@@ -4037,26 +4328,26 @@
       </c>
       <c r="E20" s="32"/>
       <c r="F20" s="13" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="G20" s="13"/>
       <c r="H20" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="L20" s="13"/>
       <c r="M20" s="2"/>
       <c r="N20" s="13"/>
       <c r="O20" s="13" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="P20" s="13"/>
     </row>
@@ -4068,25 +4359,27 @@
       </c>
       <c r="E21" s="32"/>
       <c r="F21" s="13" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="L21" s="13"/>
       <c r="M21" s="2"/>
       <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
+      <c r="O21" s="13" t="s">
+        <v>148</v>
+      </c>
       <c r="P21" s="13"/>
     </row>
   </sheetData>
@@ -4128,7 +4421,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -4137,10 +4430,10 @@
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -4148,10 +4441,10 @@
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -4159,7 +4452,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="34" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -4171,7 +4464,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="27"/>
       <c r="L6" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
@@ -4180,22 +4473,22 @@
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>17</v>
@@ -4210,19 +4503,19 @@
         <v>23</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -4236,28 +4529,30 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="2"/>
       <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
+      <c r="O8" s="13" t="s">
+        <v>157</v>
+      </c>
       <c r="P8" s="13"/>
     </row>
     <row r="9" spans="1:16">
@@ -4268,25 +4563,27 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="2"/>
       <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
+      <c r="O9" s="13" t="s">
+        <v>161</v>
+      </c>
       <c r="P9" s="13"/>
     </row>
     <row r="10" spans="1:16">
@@ -4297,26 +4594,26 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="2"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -4328,26 +4625,26 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -4359,25 +4656,27 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="2"/>
       <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
+      <c r="O12" s="13" t="s">
+        <v>173</v>
+      </c>
       <c r="P12" s="13"/>
     </row>
     <row r="13" spans="1:16">
@@ -4388,25 +4687,27 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="L13" s="13"/>
       <c r="M13" s="2"/>
       <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
+      <c r="O13" s="13" t="s">
+        <v>178</v>
+      </c>
       <c r="P13" s="13"/>
     </row>
     <row r="14" spans="1:16">
@@ -4417,26 +4718,26 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="2"/>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -4448,25 +4749,27 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="2"/>
       <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
+      <c r="O15" s="13" t="s">
+        <v>187</v>
+      </c>
       <c r="P15" s="13"/>
     </row>
     <row r="16" spans="1:16">
@@ -4477,25 +4780,27 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="2"/>
       <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
+      <c r="O16" s="13" t="s">
+        <v>192</v>
+      </c>
       <c r="P16" s="13"/>
     </row>
   </sheetData>
@@ -4537,7 +4842,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -4546,10 +4851,10 @@
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -4557,10 +4862,10 @@
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -4568,7 +4873,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="34" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -4580,7 +4885,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="27"/>
       <c r="L6" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
@@ -4589,22 +4894,22 @@
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>17</v>
@@ -4619,19 +4924,19 @@
         <v>23</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -4645,28 +4950,30 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="2"/>
       <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
+      <c r="O8" s="13" t="s">
+        <v>201</v>
+      </c>
       <c r="P8" s="13"/>
     </row>
     <row r="9" spans="1:16">
@@ -4677,25 +4984,27 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="2"/>
       <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
+      <c r="O9" s="13" t="s">
+        <v>206</v>
+      </c>
       <c r="P9" s="13"/>
     </row>
     <row r="10" spans="1:16">
@@ -4706,25 +5015,27 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="2"/>
       <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
+      <c r="O10" s="13" t="s">
+        <v>211</v>
+      </c>
       <c r="P10" s="13"/>
     </row>
     <row r="11" spans="1:16">
@@ -4735,20 +5046,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="2"/>
@@ -4764,25 +5075,27 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="2"/>
       <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
+      <c r="O12" s="13" t="s">
+        <v>219</v>
+      </c>
       <c r="P12" s="13"/>
     </row>
     <row r="13" spans="1:16">
@@ -4793,20 +5106,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="L13" s="13"/>
       <c r="M13" s="2"/>
@@ -4822,25 +5135,27 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="2"/>
       <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
+      <c r="O14" s="13" t="s">
+        <v>227</v>
+      </c>
       <c r="P14" s="13"/>
     </row>
     <row r="15" spans="1:16">
@@ -4851,25 +5166,27 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="2"/>
       <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
+      <c r="O15" s="13" t="s">
+        <v>232</v>
+      </c>
       <c r="P15" s="13"/>
     </row>
   </sheetData>
@@ -4911,7 +5228,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -4920,10 +5237,10 @@
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -4931,10 +5248,10 @@
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -4942,7 +5259,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="34" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -4954,7 +5271,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="27"/>
       <c r="L6" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
@@ -4963,22 +5280,22 @@
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>17</v>
@@ -4993,19 +5310,19 @@
         <v>23</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -5019,28 +5336,30 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>208</v>
+        <v>235</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="2"/>
       <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
+      <c r="O8" s="13" t="s">
+        <v>240</v>
+      </c>
       <c r="P8" s="13"/>
     </row>
     <row r="9" spans="1:16">
@@ -5051,25 +5370,27 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="2"/>
       <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
+      <c r="O9" s="13" t="s">
+        <v>245</v>
+      </c>
       <c r="P9" s="13"/>
     </row>
     <row r="10" spans="1:16">
@@ -5080,25 +5401,27 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>218</v>
+        <v>247</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>219</v>
+        <v>248</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="2"/>
       <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
+      <c r="O10" s="13" t="s">
+        <v>249</v>
+      </c>
       <c r="P10" s="13"/>
     </row>
     <row r="11" spans="1:16">
@@ -5109,20 +5432,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="2"/>
@@ -5138,26 +5461,26 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="2"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="s">
-        <v>150</v>
+        <v>258</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -5169,25 +5492,27 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>228</v>
+        <v>259</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>229</v>
+        <v>260</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="L13" s="13"/>
       <c r="M13" s="2"/>
       <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
+      <c r="O13" s="13" t="s">
+        <v>262</v>
+      </c>
       <c r="P13" s="13"/>
     </row>
     <row r="14" spans="1:16">
@@ -5198,25 +5523,27 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>235</v>
+        <v>266</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="2"/>
       <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
+      <c r="O14" s="13" t="s">
+        <v>267</v>
+      </c>
       <c r="P14" s="13"/>
     </row>
     <row r="15" spans="1:16">
@@ -5227,25 +5554,27 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>237</v>
+        <v>269</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="2"/>
       <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
+      <c r="O15" s="13" t="s">
+        <v>272</v>
+      </c>
       <c r="P15" s="13"/>
     </row>
     <row r="16" spans="1:16">
@@ -5256,25 +5585,27 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>240</v>
+        <v>273</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>241</v>
+        <v>274</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>242</v>
+        <v>275</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="2"/>
       <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
+      <c r="O16" s="13" t="s">
+        <v>276</v>
+      </c>
       <c r="P16" s="13"/>
     </row>
     <row r="17" spans="1:16">
@@ -5285,25 +5616,27 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>244</v>
+        <v>278</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>245</v>
+        <v>279</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="2"/>
       <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
+      <c r="O17" s="13" t="s">
+        <v>281</v>
+      </c>
       <c r="P17" s="13"/>
     </row>
   </sheetData>
@@ -5345,7 +5678,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>247</v>
+        <v>282</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -5354,10 +5687,10 @@
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>248</v>
+        <v>283</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -5365,10 +5698,10 @@
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>249</v>
+        <v>284</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -5376,7 +5709,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="34" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -5388,7 +5721,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="27"/>
       <c r="L6" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
@@ -5397,22 +5730,22 @@
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>17</v>
@@ -5427,19 +5760,19 @@
         <v>23</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -5453,28 +5786,30 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>250</v>
+        <v>56</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>253</v>
+        <v>287</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>254</v>
+        <v>288</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="2"/>
       <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
+      <c r="O8" s="13" t="s">
+        <v>289</v>
+      </c>
       <c r="P8" s="13"/>
     </row>
     <row r="9" spans="1:16">
@@ -5485,20 +5820,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>255</v>
+        <v>290</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>191</v>
+        <v>286</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>256</v>
+        <v>291</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>257</v>
+        <v>292</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="2"/>
@@ -5514,25 +5849,27 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>258</v>
+        <v>293</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>259</v>
+        <v>294</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>260</v>
+        <v>295</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>261</v>
+        <v>296</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="2"/>
       <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
+      <c r="O10" s="13" t="s">
+        <v>297</v>
+      </c>
       <c r="P10" s="13"/>
     </row>
     <row r="11" spans="1:16">
@@ -5543,26 +5880,26 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>263</v>
+        <v>299</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>265</v>
+        <v>301</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="s">
-        <v>266</v>
+        <v>302</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -5574,20 +5911,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>268</v>
+        <v>304</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>270</v>
+        <v>306</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="2"/>
@@ -5603,25 +5940,27 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>271</v>
+        <v>307</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>273</v>
+        <v>309</v>
       </c>
       <c r="L13" s="13"/>
       <c r="M13" s="2"/>
       <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
+      <c r="O13" s="13" t="s">
+        <v>310</v>
+      </c>
       <c r="P13" s="13"/>
     </row>
   </sheetData>
@@ -5663,7 +6002,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -5672,10 +6011,10 @@
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>275</v>
+        <v>312</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -5683,10 +6022,10 @@
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>276</v>
+        <v>313</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -5694,7 +6033,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="34" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -5706,7 +6045,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="27"/>
       <c r="L6" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
@@ -5715,22 +6054,22 @@
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>17</v>
@@ -5745,19 +6084,19 @@
         <v>23</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -5771,28 +6110,30 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>277</v>
+        <v>314</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>278</v>
+        <v>315</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>279</v>
+        <v>316</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>280</v>
+        <v>317</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>281</v>
+        <v>318</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="2"/>
       <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
+      <c r="O8" s="13" t="s">
+        <v>319</v>
+      </c>
       <c r="P8" s="13"/>
     </row>
     <row r="9" spans="1:16">
@@ -5803,25 +6144,27 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>282</v>
+        <v>320</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>285</v>
+        <v>323</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="2"/>
       <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
+      <c r="O9" s="13" t="s">
+        <v>324</v>
+      </c>
       <c r="P9" s="13"/>
     </row>
     <row r="10" spans="1:16">
@@ -5832,26 +6175,26 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>286</v>
+        <v>325</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>287</v>
+        <v>326</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>288</v>
+        <v>327</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>289</v>
+        <v>328</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="2"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="s">
-        <v>290</v>
+        <v>329</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -5863,26 +6206,26 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>291</v>
+        <v>330</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>293</v>
+        <v>332</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>294</v>
+        <v>333</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="s">
-        <v>295</v>
+        <v>334</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -5894,25 +6237,27 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>296</v>
+        <v>335</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>297</v>
+        <v>336</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>298</v>
+        <v>337</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>299</v>
+        <v>338</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="2"/>
       <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
+      <c r="O12" s="13" t="s">
+        <v>339</v>
+      </c>
       <c r="P12" s="13"/>
     </row>
     <row r="13" spans="1:16">
@@ -5923,25 +6268,27 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>301</v>
+        <v>341</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>302</v>
+        <v>342</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>303</v>
+        <v>343</v>
       </c>
       <c r="L13" s="13"/>
       <c r="M13" s="2"/>
       <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
+      <c r="O13" s="13" t="s">
+        <v>344</v>
+      </c>
       <c r="P13" s="13"/>
     </row>
     <row r="14" spans="1:16">
@@ -5952,26 +6299,26 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>304</v>
+        <v>345</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>305</v>
+        <v>346</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>306</v>
+        <v>347</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>307</v>
+        <v>348</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="2"/>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -5983,25 +6330,27 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>309</v>
+        <v>350</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>310</v>
+        <v>351</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>311</v>
+        <v>352</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="2"/>
       <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
+      <c r="O15" s="13" t="s">
+        <v>354</v>
+      </c>
       <c r="P15" s="13"/>
     </row>
     <row r="16" spans="1:16">
@@ -6012,25 +6361,27 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>313</v>
+        <v>355</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>314</v>
+        <v>356</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>315</v>
+        <v>357</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>316</v>
+        <v>358</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="2"/>
       <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
+      <c r="O16" s="13" t="s">
+        <v>359</v>
+      </c>
       <c r="P16" s="13"/>
     </row>
     <row r="17" spans="1:16">
@@ -6041,25 +6392,27 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>317</v>
+        <v>360</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>318</v>
+        <v>361</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>319</v>
+        <v>362</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="2"/>
       <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
+      <c r="O17" s="13" t="s">
+        <v>363</v>
+      </c>
       <c r="P17" s="13"/>
     </row>
     <row r="18" spans="1:16">
@@ -6070,25 +6423,27 @@
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="13" t="s">
-        <v>320</v>
+        <v>364</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>321</v>
+        <v>365</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>322</v>
+        <v>366</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>323</v>
+        <v>367</v>
       </c>
       <c r="L18" s="13"/>
       <c r="M18" s="2"/>
       <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
+      <c r="O18" s="13" t="s">
+        <v>368</v>
+      </c>
       <c r="P18" s="13"/>
     </row>
     <row r="19" spans="1:16">
@@ -6099,25 +6454,27 @@
       </c>
       <c r="E19" s="32"/>
       <c r="F19" s="13" t="s">
-        <v>324</v>
+        <v>369</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>325</v>
+        <v>370</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>326</v>
+        <v>371</v>
       </c>
       <c r="L19" s="13"/>
       <c r="M19" s="2"/>
       <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
+      <c r="O19" s="13" t="s">
+        <v>372</v>
+      </c>
       <c r="P19" s="13"/>
     </row>
     <row r="20" spans="1:16">
@@ -6128,25 +6485,27 @@
       </c>
       <c r="E20" s="32"/>
       <c r="F20" s="13" t="s">
-        <v>327</v>
+        <v>373</v>
       </c>
       <c r="G20" s="13"/>
       <c r="H20" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>328</v>
+        <v>374</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>330</v>
+        <v>376</v>
       </c>
       <c r="L20" s="13"/>
       <c r="M20" s="2"/>
       <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
+      <c r="O20" s="13" t="s">
+        <v>377</v>
+      </c>
       <c r="P20" s="13"/>
     </row>
   </sheetData>
@@ -6188,7 +6547,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>331</v>
+        <v>378</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -6197,10 +6556,10 @@
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>332</v>
+        <v>379</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -6208,10 +6567,10 @@
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>333</v>
+        <v>380</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -6219,7 +6578,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="34" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -6231,7 +6590,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="27"/>
       <c r="L6" s="25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
@@ -6240,22 +6599,22 @@
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>17</v>
@@ -6270,19 +6629,19 @@
         <v>23</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -6296,28 +6655,30 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>334</v>
+        <v>381</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>336</v>
+        <v>383</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>337</v>
+        <v>384</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>338</v>
+        <v>385</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="2"/>
       <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
+      <c r="O8" s="13" t="s">
+        <v>386</v>
+      </c>
       <c r="P8" s="13"/>
     </row>
     <row r="9" spans="1:16">
@@ -6328,25 +6689,27 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>191</v>
+        <v>383</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>340</v>
+        <v>388</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>341</v>
+        <v>389</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="2"/>
       <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
+      <c r="O9" s="13" t="s">
+        <v>390</v>
+      </c>
       <c r="P9" s="13"/>
     </row>
     <row r="10" spans="1:16">
@@ -6357,20 +6720,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>342</v>
+        <v>391</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>343</v>
+        <v>392</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>344</v>
+        <v>393</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>345</v>
+        <v>394</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="2"/>
@@ -6386,25 +6749,27 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>346</v>
+        <v>395</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>347</v>
+        <v>396</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>348</v>
+        <v>397</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>349</v>
+        <v>398</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
+      <c r="O11" s="13" t="s">
+        <v>399</v>
+      </c>
       <c r="P11" s="13"/>
     </row>
     <row r="12" spans="1:16">
@@ -6415,20 +6780,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>351</v>
+        <v>401</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>352</v>
+        <v>402</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>353</v>
+        <v>403</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="2"/>

--- a/結合試験仕様書.xlsx
+++ b/結合試験仕様書.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="526">
   <si>
     <t xml:space="preserve">ACTIO（イベント主催・管理サービス）</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t xml:space="preserve">イベントが作成されて詳細の画面に切り替わる。イベント一覧にも「公開中」として並ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">三原</t>
   </si>
   <si>
     <t xml:space="preserve">ID: F-01</t>
@@ -2436,7 +2439,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2448,7 +2451,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -2459,7 +2462,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -2544,29 +2547,31 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>411</v>
-      </c>
-      <c r="L8" s="13"/>
+        <v>412</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M8" s="2"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -2578,26 +2583,28 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>416</v>
-      </c>
-      <c r="L9" s="13"/>
+        <v>417</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M9" s="2"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -2609,26 +2616,28 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>421</v>
-      </c>
-      <c r="L10" s="13"/>
+        <v>422</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M10" s="2"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -2640,26 +2649,28 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>426</v>
-      </c>
-      <c r="L11" s="13"/>
+        <v>427</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -2671,26 +2682,28 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>431</v>
-      </c>
-      <c r="L12" s="13"/>
+        <v>432</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M12" s="2"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -2702,26 +2715,28 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>436</v>
-      </c>
-      <c r="L13" s="13"/>
+        <v>437</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M13" s="2"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -2733,26 +2748,28 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="L14" s="13"/>
+        <v>442</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -2764,26 +2781,28 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>446</v>
-      </c>
-      <c r="L15" s="13"/>
+        <v>447</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M15" s="2"/>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P15" s="13"/>
     </row>
@@ -2795,26 +2814,28 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>451</v>
-      </c>
-      <c r="L16" s="13"/>
+        <v>452</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M16" s="2"/>
       <c r="N16" s="13"/>
       <c r="O16" s="13" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="P16" s="13"/>
     </row>
@@ -2826,26 +2847,28 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>456</v>
-      </c>
-      <c r="L17" s="13"/>
+        <v>457</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M17" s="2"/>
       <c r="N17" s="13"/>
       <c r="O17" s="13" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P17" s="13"/>
     </row>
@@ -2888,7 +2911,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2900,7 +2923,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -2911,7 +2934,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -2996,29 +3019,31 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>465</v>
-      </c>
-      <c r="L8" s="13"/>
+        <v>466</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M8" s="2"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -3030,26 +3055,28 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>469</v>
-      </c>
-      <c r="L9" s="13"/>
+        <v>470</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M9" s="2"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -3061,22 +3088,24 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>474</v>
-      </c>
-      <c r="L10" s="13"/>
+        <v>475</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M10" s="2"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13"/>
@@ -3090,26 +3119,28 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>478</v>
-      </c>
-      <c r="L11" s="13"/>
+        <v>479</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -3121,26 +3152,28 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>483</v>
-      </c>
-      <c r="L12" s="13"/>
+        <v>484</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M12" s="2"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -3183,7 +3216,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -3195,7 +3228,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -3206,7 +3239,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -3291,25 +3324,27 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>491</v>
-      </c>
-      <c r="L8" s="13"/>
+        <v>492</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M8" s="2"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13"/>
@@ -3323,26 +3358,28 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>495</v>
-      </c>
-      <c r="L9" s="13"/>
+        <v>496</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M9" s="2"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -3354,26 +3391,28 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>500</v>
-      </c>
-      <c r="L10" s="13"/>
+        <v>501</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M10" s="2"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -3385,26 +3424,28 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>505</v>
-      </c>
-      <c r="L11" s="13"/>
+        <v>506</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -3416,26 +3457,28 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>510</v>
-      </c>
-      <c r="L12" s="13"/>
+        <v>511</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M12" s="2"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -3447,26 +3490,28 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>515</v>
-      </c>
-      <c r="L13" s="13"/>
+        <v>516</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M13" s="2"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -3503,12 +3548,12 @@
   <sheetData>
     <row r="1" spans="1:12" ht="26.5">
       <c r="B1" s="24" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="B2" s="13" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -3516,16 +3561,16 @@
         <v>73</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>17</v>
@@ -3534,10 +3579,10 @@
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
@@ -3973,11 +4018,13 @@
       <c r="K8" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="L8" s="13"/>
+      <c r="L8" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M8" s="2"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -3989,22 +4036,24 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="L9" s="13"/>
+        <v>92</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M9" s="2"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13"/>
@@ -4018,26 +4067,28 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="L10" s="13"/>
+        <v>96</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M10" s="2"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -4049,26 +4100,28 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="L11" s="13"/>
+        <v>100</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -4080,26 +4133,28 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="L12" s="13"/>
+        <v>105</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M12" s="2"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -4111,26 +4166,28 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="L13" s="13"/>
+        <v>110</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M13" s="2"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -4142,26 +4199,28 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="L14" s="13"/>
+        <v>114</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -4173,26 +4232,28 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="L15" s="13"/>
+        <v>119</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M15" s="2"/>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P15" s="13"/>
     </row>
@@ -4204,26 +4265,28 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="L16" s="13"/>
+        <v>124</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M16" s="2"/>
       <c r="N16" s="13"/>
       <c r="O16" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P16" s="13"/>
     </row>
@@ -4235,26 +4298,28 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="L17" s="13"/>
+        <v>129</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M17" s="2"/>
       <c r="N17" s="13"/>
       <c r="O17" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P17" s="13"/>
     </row>
@@ -4266,26 +4331,28 @@
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="L18" s="13"/>
+        <v>134</v>
+      </c>
+      <c r="L18" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M18" s="2"/>
       <c r="N18" s="13"/>
       <c r="O18" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P18" s="13"/>
     </row>
@@ -4297,26 +4364,28 @@
       </c>
       <c r="E19" s="32"/>
       <c r="F19" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="L19" s="13"/>
+        <v>138</v>
+      </c>
+      <c r="L19" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M19" s="2"/>
       <c r="N19" s="13"/>
       <c r="O19" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P19" s="13"/>
     </row>
@@ -4328,26 +4397,28 @@
       </c>
       <c r="E20" s="32"/>
       <c r="F20" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G20" s="13"/>
       <c r="H20" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="L20" s="13"/>
+        <v>143</v>
+      </c>
+      <c r="L20" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M20" s="2"/>
       <c r="N20" s="13"/>
       <c r="O20" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P20" s="13"/>
     </row>
@@ -4359,26 +4430,28 @@
       </c>
       <c r="E21" s="32"/>
       <c r="F21" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="L21" s="13"/>
+        <v>148</v>
+      </c>
+      <c r="L21" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M21" s="2"/>
       <c r="N21" s="13"/>
       <c r="O21" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P21" s="13"/>
     </row>
@@ -4421,7 +4494,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -4433,7 +4506,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -4444,7 +4517,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -4529,29 +4602,31 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="L8" s="13"/>
+        <v>157</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M8" s="2"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -4563,26 +4638,28 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="L9" s="13"/>
+        <v>161</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M9" s="2"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -4594,26 +4671,28 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="L10" s="13"/>
+        <v>161</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M10" s="2"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -4625,26 +4704,28 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="L11" s="13"/>
+        <v>169</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -4656,26 +4737,28 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="L12" s="13"/>
+        <v>173</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M12" s="2"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -4687,26 +4770,28 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="L13" s="13"/>
+        <v>178</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M13" s="2"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -4718,26 +4803,28 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="L14" s="13"/>
+        <v>182</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -4749,26 +4836,28 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="L15" s="13"/>
+        <v>187</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M15" s="2"/>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P15" s="13"/>
     </row>
@@ -4780,26 +4869,28 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="L16" s="13"/>
+        <v>192</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M16" s="2"/>
       <c r="N16" s="13"/>
       <c r="O16" s="13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P16" s="13"/>
     </row>
@@ -4842,7 +4933,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -4854,7 +4945,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -4865,7 +4956,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -4950,29 +5041,31 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="L8" s="13"/>
+        <v>201</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M8" s="2"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -4984,26 +5077,28 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="L9" s="13"/>
+        <v>206</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M9" s="2"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -5015,26 +5110,28 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="L10" s="13"/>
+        <v>211</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M10" s="2"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -5046,22 +5143,24 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="L11" s="13"/>
+        <v>216</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13"/>
@@ -5075,26 +5174,28 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="L12" s="13"/>
+        <v>219</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M12" s="2"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -5106,22 +5207,24 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="L13" s="13"/>
+        <v>223</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M13" s="2"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -5135,26 +5238,28 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="L14" s="13"/>
+        <v>227</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -5166,26 +5271,28 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
         <v>43</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="L15" s="13"/>
+        <v>232</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M15" s="2"/>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P15" s="13"/>
     </row>
@@ -5228,7 +5335,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -5240,7 +5347,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -5251,7 +5358,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -5336,29 +5443,31 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="L8" s="13"/>
+        <v>240</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M8" s="2"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -5370,26 +5479,28 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="L9" s="13"/>
+        <v>245</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M9" s="2"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -5401,26 +5512,28 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="L10" s="13"/>
+        <v>249</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M10" s="2"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -5432,22 +5545,24 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="L11" s="13"/>
+        <v>254</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13"/>
@@ -5461,26 +5576,28 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="L12" s="13"/>
+        <v>258</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M12" s="2"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -5492,26 +5609,28 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="L13" s="13"/>
+        <v>262</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M13" s="2"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -5523,26 +5642,28 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="L14" s="13"/>
+        <v>267</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -5554,26 +5675,28 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="L15" s="13"/>
+        <v>272</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M15" s="2"/>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P15" s="13"/>
     </row>
@@ -5585,26 +5708,28 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="L16" s="13"/>
+        <v>276</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M16" s="2"/>
       <c r="N16" s="13"/>
       <c r="O16" s="13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P16" s="13"/>
     </row>
@@ -5616,26 +5741,28 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="L17" s="13"/>
+        <v>281</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M17" s="2"/>
       <c r="N17" s="13"/>
       <c r="O17" s="13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P17" s="13"/>
     </row>
@@ -5678,7 +5805,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -5690,7 +5817,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -5701,7 +5828,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -5789,26 +5916,28 @@
         <v>56</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="L8" s="13"/>
+        <v>289</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M8" s="2"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -5820,22 +5949,24 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="L9" s="13"/>
+        <v>293</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M9" s="2"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13"/>
@@ -5849,26 +5980,28 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="L10" s="13"/>
+        <v>297</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M10" s="2"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -5880,26 +6013,28 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>301</v>
-      </c>
-      <c r="L11" s="13"/>
+        <v>302</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -5911,22 +6046,24 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="L12" s="13"/>
+        <v>307</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M12" s="2"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
@@ -5940,26 +6077,28 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="L13" s="13"/>
+        <v>310</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M13" s="2"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -6002,7 +6141,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -6014,7 +6153,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -6025,7 +6164,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -6110,29 +6249,31 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="L8" s="13"/>
+        <v>319</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M8" s="2"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -6144,26 +6285,28 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="L9" s="13"/>
+        <v>324</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M9" s="2"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -6175,26 +6318,28 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="L10" s="13"/>
+        <v>329</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M10" s="2"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -6206,26 +6351,28 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>333</v>
-      </c>
-      <c r="L11" s="13"/>
+        <v>334</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -6237,26 +6384,28 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="L12" s="13"/>
+        <v>339</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M12" s="2"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -6268,26 +6417,28 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="L13" s="13"/>
+        <v>344</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M13" s="2"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -6299,26 +6450,28 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>348</v>
-      </c>
-      <c r="L14" s="13"/>
+        <v>349</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -6330,26 +6483,28 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>353</v>
-      </c>
-      <c r="L15" s="13"/>
+        <v>354</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M15" s="2"/>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P15" s="13"/>
     </row>
@@ -6361,26 +6516,28 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="L16" s="13"/>
+        <v>359</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M16" s="2"/>
       <c r="N16" s="13"/>
       <c r="O16" s="13" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P16" s="13"/>
     </row>
@@ -6392,26 +6549,28 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>362</v>
-      </c>
-      <c r="L17" s="13"/>
+        <v>363</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M17" s="2"/>
       <c r="N17" s="13"/>
       <c r="O17" s="13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P17" s="13"/>
     </row>
@@ -6423,26 +6582,28 @@
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="L18" s="13"/>
+        <v>368</v>
+      </c>
+      <c r="L18" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M18" s="2"/>
       <c r="N18" s="13"/>
       <c r="O18" s="13" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P18" s="13"/>
     </row>
@@ -6454,26 +6615,28 @@
       </c>
       <c r="E19" s="32"/>
       <c r="F19" s="13" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>371</v>
-      </c>
-      <c r="L19" s="13"/>
+        <v>372</v>
+      </c>
+      <c r="L19" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M19" s="2"/>
       <c r="N19" s="13"/>
       <c r="O19" s="13" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P19" s="13"/>
     </row>
@@ -6485,26 +6648,28 @@
       </c>
       <c r="E20" s="32"/>
       <c r="F20" s="13" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G20" s="13"/>
       <c r="H20" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>376</v>
-      </c>
-      <c r="L20" s="13"/>
+        <v>377</v>
+      </c>
+      <c r="L20" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M20" s="2"/>
       <c r="N20" s="13"/>
       <c r="O20" s="13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P20" s="13"/>
     </row>
@@ -6547,7 +6712,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -6559,7 +6724,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -6570,7 +6735,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -6655,29 +6820,31 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="L8" s="13"/>
+        <v>386</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M8" s="2"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -6689,26 +6856,28 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>389</v>
-      </c>
-      <c r="L9" s="13"/>
+        <v>390</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M9" s="2"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -6720,22 +6889,24 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>394</v>
-      </c>
-      <c r="L10" s="13"/>
+        <v>395</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M10" s="2"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13"/>
@@ -6749,26 +6920,28 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="L11" s="13"/>
+        <v>399</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M11" s="2"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -6780,22 +6953,24 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>403</v>
-      </c>
-      <c r="L12" s="13"/>
+        <v>404</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="M12" s="2"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>

--- a/結合試験仕様書.xlsx
+++ b/結合試験仕様書.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="528">
   <si>
     <t xml:space="preserve">ACTIO（イベント主催・管理サービス）</t>
   </si>
@@ -97,10 +97,10 @@
     <t xml:space="preserve">操作後に「こうなっていれば正しい」という状態。</t>
   </si>
   <si>
-    <t xml:space="preserve">結果（OK / NG）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK＝期待どおり動いた。NG＝期待どおりにならなかった（不具合）。</t>
+    <t xml:space="preserve">結果（〇 / ×）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">〇＝期待どおり動いた。×＝期待どおりにならなかった（不具合）。×はNG項目一覧に転記します。</t>
   </si>
   <si>
     <t xml:space="preserve">備考</t>
@@ -112,7 +112,7 @@
     <t xml:space="preserve">AI</t>
   </si>
   <si>
-    <t xml:space="preserve">AI が提案した項目である場合に「利用」と記入します。</t>
+    <t xml:space="preserve">AI を利用した項目に「利用」と記入します。本仕様書では、AI が自動で実施した項目に記入しています。</t>
   </si>
   <si>
     <t xml:space="preserve">操作</t>
@@ -1598,6 +1598,12 @@
   </si>
   <si>
     <t xml:space="preserve">対応・備考</t>
+  </si>
+  <si>
+    <t xml:space="preserve">〇</t>
+  </si>
+  <si>
+    <t xml:space="preserve">利用</t>
   </si>
 </sst>
 </file>
@@ -2568,12 +2574,18 @@
       <c r="L8" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="13"/>
+      <c r="M8" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O8" s="13" t="s">
         <v>413</v>
       </c>
-      <c r="P8" s="13"/>
+      <c r="P8" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="9" spans="1:16">
       <c r="B9" s="29"/>
@@ -2601,12 +2613,18 @@
       <c r="L9" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="13"/>
+      <c r="M9" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O9" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="P9" s="13"/>
+      <c r="P9" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="10" spans="1:16">
       <c r="B10" s="29"/>
@@ -2667,12 +2685,18 @@
       <c r="L11" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="13"/>
+      <c r="M11" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O11" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="P11" s="13"/>
+      <c r="P11" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="12" spans="1:16">
       <c r="B12" s="29"/>
@@ -2700,12 +2724,18 @@
       <c r="L12" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="13"/>
+      <c r="M12" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O12" s="13" t="s">
         <v>433</v>
       </c>
-      <c r="P12" s="13"/>
+      <c r="P12" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="13" spans="1:16">
       <c r="B13" s="29"/>
@@ -2733,12 +2763,18 @@
       <c r="L13" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="13"/>
+      <c r="M13" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O13" s="13" t="s">
         <v>438</v>
       </c>
-      <c r="P13" s="13"/>
+      <c r="P13" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="14" spans="1:16">
       <c r="B14" s="29"/>
@@ -2766,12 +2802,18 @@
       <c r="L14" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="13"/>
+      <c r="M14" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O14" s="13" t="s">
         <v>443</v>
       </c>
-      <c r="P14" s="13"/>
+      <c r="P14" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="15" spans="1:16">
       <c r="B15" s="29"/>
@@ -2799,12 +2841,18 @@
       <c r="L15" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M15" s="2"/>
-      <c r="N15" s="13"/>
+      <c r="M15" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O15" s="13" t="s">
         <v>448</v>
       </c>
-      <c r="P15" s="13"/>
+      <c r="P15" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="16" spans="1:16">
       <c r="B16" s="29"/>
@@ -2832,12 +2880,18 @@
       <c r="L16" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="13"/>
+      <c r="M16" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O16" s="13" t="s">
         <v>453</v>
       </c>
-      <c r="P16" s="13"/>
+      <c r="P16" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="17" spans="1:16">
       <c r="B17" s="29"/>
@@ -2865,12 +2919,18 @@
       <c r="L17" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M17" s="2"/>
-      <c r="N17" s="13"/>
+      <c r="M17" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O17" s="13" t="s">
         <v>458</v>
       </c>
-      <c r="P17" s="13"/>
+      <c r="P17" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3040,12 +3100,18 @@
       <c r="L8" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="13"/>
+      <c r="M8" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O8" s="13" t="s">
         <v>467</v>
       </c>
-      <c r="P8" s="13"/>
+      <c r="P8" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="9" spans="1:16">
       <c r="B9" s="29"/>
@@ -3073,12 +3139,18 @@
       <c r="L9" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="13"/>
+      <c r="M9" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O9" s="13" t="s">
         <v>471</v>
       </c>
-      <c r="P9" s="13"/>
+      <c r="P9" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="10" spans="1:16">
       <c r="B10" s="29"/>
@@ -3106,10 +3178,16 @@
       <c r="L10" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="13"/>
+      <c r="M10" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
+      <c r="P10" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="11" spans="1:16">
       <c r="B11" s="29"/>
@@ -3137,12 +3215,18 @@
       <c r="L11" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="13"/>
+      <c r="M11" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O11" s="13" t="s">
         <v>480</v>
       </c>
-      <c r="P11" s="13"/>
+      <c r="P11" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="12" spans="1:16">
       <c r="B12" s="29"/>
@@ -3170,12 +3254,18 @@
       <c r="L12" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="13"/>
+      <c r="M12" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O12" s="13" t="s">
         <v>485</v>
       </c>
-      <c r="P12" s="13"/>
+      <c r="P12" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3345,10 +3435,16 @@
       <c r="L8" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="13"/>
+      <c r="M8" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
+      <c r="P8" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="9" spans="1:16">
       <c r="B9" s="29"/>
@@ -3376,12 +3472,18 @@
       <c r="L9" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="13"/>
+      <c r="M9" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O9" s="13" t="s">
         <v>497</v>
       </c>
-      <c r="P9" s="13"/>
+      <c r="P9" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="10" spans="1:16">
       <c r="B10" s="29"/>
@@ -3409,12 +3511,18 @@
       <c r="L10" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="13"/>
+      <c r="M10" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O10" s="13" t="s">
         <v>502</v>
       </c>
-      <c r="P10" s="13"/>
+      <c r="P10" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="11" spans="1:16">
       <c r="B11" s="29"/>
@@ -3475,12 +3583,18 @@
       <c r="L12" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="13"/>
+      <c r="M12" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O12" s="13" t="s">
         <v>512</v>
       </c>
-      <c r="P12" s="13"/>
+      <c r="P12" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="13" spans="1:16">
       <c r="B13" s="29"/>
@@ -3508,12 +3622,18 @@
       <c r="L13" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="13"/>
+      <c r="M13" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O13" s="13" t="s">
         <v>517</v>
       </c>
-      <c r="P13" s="13"/>
+      <c r="P13" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4021,8 +4141,12 @@
       <c r="L8" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="13"/>
+      <c r="M8" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O8" s="13" t="s">
         <v>88</v>
       </c>
@@ -4054,8 +4178,12 @@
       <c r="L9" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="13"/>
+      <c r="M9" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O9" s="13"/>
       <c r="P9" s="13"/>
     </row>
@@ -4085,8 +4213,12 @@
       <c r="L10" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="13"/>
+      <c r="M10" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O10" s="13" t="s">
         <v>97</v>
       </c>
@@ -4118,8 +4250,12 @@
       <c r="L11" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="13"/>
+      <c r="M11" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O11" s="13" t="s">
         <v>101</v>
       </c>
@@ -4151,8 +4287,12 @@
       <c r="L12" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="13"/>
+      <c r="M12" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O12" s="13" t="s">
         <v>106</v>
       </c>
@@ -4184,8 +4324,12 @@
       <c r="L13" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="13"/>
+      <c r="M13" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O13" s="13" t="s">
         <v>111</v>
       </c>
@@ -4217,8 +4361,12 @@
       <c r="L14" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="13"/>
+      <c r="M14" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O14" s="13" t="s">
         <v>115</v>
       </c>
@@ -4250,8 +4398,12 @@
       <c r="L15" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M15" s="2"/>
-      <c r="N15" s="13"/>
+      <c r="M15" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O15" s="13" t="s">
         <v>120</v>
       </c>
@@ -4283,8 +4435,12 @@
       <c r="L16" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="13"/>
+      <c r="M16" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O16" s="13" t="s">
         <v>125</v>
       </c>
@@ -4316,8 +4472,12 @@
       <c r="L17" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M17" s="2"/>
-      <c r="N17" s="13"/>
+      <c r="M17" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O17" s="13" t="s">
         <v>130</v>
       </c>
@@ -4349,8 +4509,12 @@
       <c r="L18" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M18" s="2"/>
-      <c r="N18" s="13"/>
+      <c r="M18" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O18" s="13" t="s">
         <v>135</v>
       </c>
@@ -4382,8 +4546,12 @@
       <c r="L19" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M19" s="2"/>
-      <c r="N19" s="13"/>
+      <c r="M19" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O19" s="13" t="s">
         <v>139</v>
       </c>
@@ -4415,8 +4583,12 @@
       <c r="L20" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M20" s="2"/>
-      <c r="N20" s="13"/>
+      <c r="M20" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O20" s="13" t="s">
         <v>144</v>
       </c>
@@ -4448,8 +4620,12 @@
       <c r="L21" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M21" s="2"/>
-      <c r="N21" s="13"/>
+      <c r="M21" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N21" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O21" s="13" t="s">
         <v>149</v>
       </c>
@@ -4623,8 +4799,12 @@
       <c r="L8" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="13"/>
+      <c r="M8" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O8" s="13" t="s">
         <v>158</v>
       </c>
@@ -4656,8 +4836,12 @@
       <c r="L9" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="13"/>
+      <c r="M9" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O9" s="13" t="s">
         <v>162</v>
       </c>
@@ -4689,8 +4873,12 @@
       <c r="L10" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="13"/>
+      <c r="M10" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O10" s="13" t="s">
         <v>165</v>
       </c>
@@ -4722,8 +4910,12 @@
       <c r="L11" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="13"/>
+      <c r="M11" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O11" s="13" t="s">
         <v>170</v>
       </c>
@@ -4755,8 +4947,12 @@
       <c r="L12" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="13"/>
+      <c r="M12" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O12" s="13" t="s">
         <v>174</v>
       </c>
@@ -4788,8 +4984,12 @@
       <c r="L13" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="13"/>
+      <c r="M13" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O13" s="13" t="s">
         <v>179</v>
       </c>
@@ -4821,8 +5021,12 @@
       <c r="L14" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="13"/>
+      <c r="M14" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O14" s="13" t="s">
         <v>183</v>
       </c>
@@ -4854,8 +5058,12 @@
       <c r="L15" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M15" s="2"/>
-      <c r="N15" s="13"/>
+      <c r="M15" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O15" s="13" t="s">
         <v>188</v>
       </c>
@@ -4887,8 +5095,12 @@
       <c r="L16" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="13"/>
+      <c r="M16" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O16" s="13" t="s">
         <v>193</v>
       </c>
@@ -5062,8 +5274,12 @@
       <c r="L8" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="13"/>
+      <c r="M8" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O8" s="13" t="s">
         <v>202</v>
       </c>
@@ -5095,8 +5311,12 @@
       <c r="L9" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="13"/>
+      <c r="M9" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O9" s="13" t="s">
         <v>207</v>
       </c>
@@ -5128,8 +5348,12 @@
       <c r="L10" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="13"/>
+      <c r="M10" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O10" s="13" t="s">
         <v>212</v>
       </c>
@@ -5161,8 +5385,12 @@
       <c r="L11" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="13"/>
+      <c r="M11" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O11" s="13"/>
       <c r="P11" s="13"/>
     </row>
@@ -5192,8 +5420,12 @@
       <c r="L12" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="13"/>
+      <c r="M12" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O12" s="13" t="s">
         <v>220</v>
       </c>
@@ -5225,8 +5457,12 @@
       <c r="L13" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="13"/>
+      <c r="M13" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O13" s="13"/>
       <c r="P13" s="13"/>
     </row>
@@ -5256,8 +5492,12 @@
       <c r="L14" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="13"/>
+      <c r="M14" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O14" s="13" t="s">
         <v>228</v>
       </c>
@@ -5289,8 +5529,12 @@
       <c r="L15" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M15" s="2"/>
-      <c r="N15" s="13"/>
+      <c r="M15" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O15" s="13" t="s">
         <v>233</v>
       </c>
@@ -5464,12 +5708,18 @@
       <c r="L8" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="13"/>
+      <c r="M8" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O8" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="P8" s="13"/>
+      <c r="P8" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="9" spans="1:16">
       <c r="B9" s="29"/>
@@ -5497,12 +5747,18 @@
       <c r="L9" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="13"/>
+      <c r="M9" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O9" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="P9" s="13"/>
+      <c r="P9" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="10" spans="1:16">
       <c r="B10" s="29"/>
@@ -5530,12 +5786,18 @@
       <c r="L10" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="13"/>
+      <c r="M10" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O10" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="P10" s="13"/>
+      <c r="P10" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="11" spans="1:16">
       <c r="B11" s="29"/>
@@ -5563,10 +5825,16 @@
       <c r="L11" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="13"/>
+      <c r="M11" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
+      <c r="P11" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="12" spans="1:16">
       <c r="B12" s="29"/>
@@ -5594,12 +5862,18 @@
       <c r="L12" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="13"/>
+      <c r="M12" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O12" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="P12" s="13"/>
+      <c r="P12" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="13" spans="1:16">
       <c r="B13" s="29"/>
@@ -5627,12 +5901,18 @@
       <c r="L13" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="13"/>
+      <c r="M13" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O13" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="P13" s="13"/>
+      <c r="P13" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="14" spans="1:16">
       <c r="B14" s="29"/>
@@ -5660,12 +5940,18 @@
       <c r="L14" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="13"/>
+      <c r="M14" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O14" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="P14" s="13"/>
+      <c r="P14" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="15" spans="1:16">
       <c r="B15" s="29"/>
@@ -5693,12 +5979,18 @@
       <c r="L15" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M15" s="2"/>
-      <c r="N15" s="13"/>
+      <c r="M15" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O15" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="P15" s="13"/>
+      <c r="P15" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="16" spans="1:16">
       <c r="B16" s="29"/>
@@ -5726,12 +6018,18 @@
       <c r="L16" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="13"/>
+      <c r="M16" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O16" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="P16" s="13"/>
+      <c r="P16" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="17" spans="1:16">
       <c r="B17" s="29"/>
@@ -5759,12 +6057,18 @@
       <c r="L17" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M17" s="2"/>
-      <c r="N17" s="13"/>
+      <c r="M17" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O17" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="P17" s="13"/>
+      <c r="P17" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -5934,12 +6238,18 @@
       <c r="L8" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="13"/>
+      <c r="M8" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O8" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="P8" s="13"/>
+      <c r="P8" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="9" spans="1:16">
       <c r="B9" s="29"/>
@@ -5967,10 +6277,16 @@
       <c r="L9" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="13"/>
+      <c r="M9" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
+      <c r="P9" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="10" spans="1:16">
       <c r="B10" s="29"/>
@@ -5998,12 +6314,18 @@
       <c r="L10" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="13"/>
+      <c r="M10" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O10" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="P10" s="13"/>
+      <c r="P10" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="11" spans="1:16">
       <c r="B11" s="29"/>
@@ -6064,10 +6386,16 @@
       <c r="L12" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="13"/>
+      <c r="M12" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
+      <c r="P12" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="13" spans="1:16">
       <c r="B13" s="29"/>
@@ -6095,12 +6423,18 @@
       <c r="L13" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="13"/>
+      <c r="M13" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O13" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="P13" s="13"/>
+      <c r="P13" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -6270,12 +6604,18 @@
       <c r="L8" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="13"/>
+      <c r="M8" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O8" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="P8" s="13"/>
+      <c r="P8" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="9" spans="1:16">
       <c r="B9" s="29"/>
@@ -6303,12 +6643,18 @@
       <c r="L9" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="13"/>
+      <c r="M9" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O9" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="P9" s="13"/>
+      <c r="P9" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="10" spans="1:16">
       <c r="B10" s="29"/>
@@ -6336,12 +6682,18 @@
       <c r="L10" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="13"/>
+      <c r="M10" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O10" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="P10" s="13"/>
+      <c r="P10" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="11" spans="1:16">
       <c r="B11" s="29"/>
@@ -6369,12 +6721,18 @@
       <c r="L11" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="13"/>
+      <c r="M11" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O11" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="P11" s="13"/>
+      <c r="P11" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="12" spans="1:16">
       <c r="B12" s="29"/>
@@ -6402,12 +6760,18 @@
       <c r="L12" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="13"/>
+      <c r="M12" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O12" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="P12" s="13"/>
+      <c r="P12" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="13" spans="1:16">
       <c r="B13" s="29"/>
@@ -6435,12 +6799,18 @@
       <c r="L13" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="13"/>
+      <c r="M13" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O13" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="P13" s="13"/>
+      <c r="P13" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="14" spans="1:16">
       <c r="B14" s="29"/>
@@ -6468,12 +6838,18 @@
       <c r="L14" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="13"/>
+      <c r="M14" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O14" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="P14" s="13"/>
+      <c r="P14" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="15" spans="1:16">
       <c r="B15" s="29"/>
@@ -6501,12 +6877,18 @@
       <c r="L15" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M15" s="2"/>
-      <c r="N15" s="13"/>
+      <c r="M15" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O15" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="P15" s="13"/>
+      <c r="P15" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="16" spans="1:16">
       <c r="B16" s="29"/>
@@ -6534,12 +6916,18 @@
       <c r="L16" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="13"/>
+      <c r="M16" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O16" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="P16" s="13"/>
+      <c r="P16" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="17" spans="1:16">
       <c r="B17" s="29"/>
@@ -6567,12 +6955,18 @@
       <c r="L17" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M17" s="2"/>
-      <c r="N17" s="13"/>
+      <c r="M17" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O17" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="P17" s="13"/>
+      <c r="P17" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="18" spans="1:16">
       <c r="B18" s="29"/>
@@ -6600,12 +6994,18 @@
       <c r="L18" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M18" s="2"/>
-      <c r="N18" s="13"/>
+      <c r="M18" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O18" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="P18" s="13"/>
+      <c r="P18" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="19" spans="1:16">
       <c r="B19" s="29"/>
@@ -6633,12 +7033,18 @@
       <c r="L19" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M19" s="2"/>
-      <c r="N19" s="13"/>
+      <c r="M19" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O19" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="P19" s="13"/>
+      <c r="P19" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="20" spans="1:16">
       <c r="B20" s="29"/>
@@ -6666,12 +7072,18 @@
       <c r="L20" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M20" s="2"/>
-      <c r="N20" s="13"/>
+      <c r="M20" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O20" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="P20" s="13"/>
+      <c r="P20" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -6841,12 +7253,18 @@
       <c r="L8" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="13"/>
+      <c r="M8" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O8" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="P8" s="13"/>
+      <c r="P8" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="9" spans="1:16">
       <c r="B9" s="29"/>
@@ -6874,12 +7292,18 @@
       <c r="L9" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="13"/>
+      <c r="M9" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O9" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="P9" s="13"/>
+      <c r="P9" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="10" spans="1:16">
       <c r="B10" s="29"/>
@@ -6907,10 +7331,16 @@
       <c r="L10" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="13"/>
+      <c r="M10" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
+      <c r="P10" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="11" spans="1:16">
       <c r="B11" s="29"/>
@@ -6938,12 +7368,18 @@
       <c r="L11" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="13"/>
+      <c r="M11" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O11" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="P11" s="13"/>
+      <c r="P11" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="12" spans="1:16">
       <c r="B12" s="29"/>
@@ -6971,10 +7407,16 @@
       <c r="L12" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="13"/>
+      <c r="M12" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>526</v>
+      </c>
       <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
+      <c r="P12" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/結合試験仕様書.xlsx
+++ b/結合試験仕様書.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="633">
   <si>
     <t xml:space="preserve">ACTIO（イベント主催・管理サービス）</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">対象: index.html（単一ファイル・file:// 起動）</t>
   </si>
   <si>
-    <t xml:space="preserve">試験項目: 全86項目（大項目10）</t>
+    <t xml:space="preserve">試験項目: 全109項目（大項目10）</t>
   </si>
   <si>
     <t xml:space="preserve">動作保証: Google Chrome のみ</t>
@@ -472,6 +472,48 @@
     <t xml:space="preserve">ID: D-04 ／ 気づかずに申込ごと消してしまうことを防ぐため</t>
   </si>
   <si>
+    <t xml:space="preserve">確認ダイアログでキャンセルを選ぶとイベントは削除されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベント一覧で「削除」を押し、確認ダイアログで「キャンセル」を選ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベントも申込も削除されず、一覧の件数が変わらない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-04 ／ 誤って押しても実害が出ないことの確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作成をやめると入力内容は保存されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作成画面の5つのステップをすべて入力した状態</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「やめる」を押してイベント一覧に戻る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">下書きも含めてイベントは作られず、一覧の件数が変わらない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入力途中で離脱しても残らないことの確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">終了時刻ちょうどはまだ終了扱いにしない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">終了日時が現在時刻とちょうど同じ公開中のイベント</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参加者向けの公開イベント一覧と、そのイベントの公開ページを開く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">上段の「公開中のイベント」に残り、「終了」とは表示されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-07 ／ 終了と判定するのは終了日時を過ぎたときだけ</t>
+  </si>
+  <si>
     <t xml:space="preserve">・券種・申込フォーム項目</t>
   </si>
   <si>
@@ -604,6 +646,45 @@
     <t xml:space="preserve">ID: F-07 / D-28 ／ 例: 所属部署、参加のきっかけ</t>
   </si>
   <si>
+    <t xml:space="preserve">券種が1件もないと公開できない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作成画面で券種をすべて削除した状態</t>
+  </si>
+  <si>
+    <t xml:space="preserve">他の必須項目を埋めて「公開する」を押す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「公開するには券種を1件以上登録してください」と表示され、公開されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-05 ／ 下書きとしてなら保存できる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">定員は1と9999で保存できる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">定員に 1 を入れて保存し、続けて 9999 を入れて保存する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">どちらもエラーにならずに保存できる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-22 ／ 受け付けられる下限と上限のちょうど</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カスタム項目と選択肢は上限を超えると追加できない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カスタム項目を11件目まで追加し、選択肢を11件入力して保存する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「カスタム項目は10件以内で設定してください」「選択肢は10件以内で入力してください」と表示され、追加されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-28 ／ 上限10件の1つ外側</t>
+  </si>
+  <si>
     <t xml:space="preserve">・公開ページ・集客</t>
   </si>
   <si>
@@ -724,6 +805,18 @@
     <t xml:space="preserve">ID: F-10 ／ 公開前に見え方を確かめるための画面</t>
   </si>
   <si>
+    <t xml:space="preserve">組織ロゴが未設定でも表示が崩れない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">設定・データ管理の一般設定で組織ロゴを削除した状態</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ロゴの代わりに組織名の文字だけが表示され、並びが崩れない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-09 ／ ロゴ未設定のときの既定の見え方</t>
+  </si>
+  <si>
     <t xml:space="preserve">・申込フロー</t>
   </si>
   <si>
@@ -871,6 +964,36 @@
     <t xml:space="preserve">ID: D-43 ／ パスワードはメールアドレスごとに1つ</t>
   </si>
   <si>
+    <t xml:space="preserve">申込をやめると申込は作られない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込フォームに券種・氏名・メールアドレス・パスワードを入力した状態</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「やめる」を押して公開ページに戻る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込は登録されず、受付コードも発行されない。券種の残りも変わらない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参加者が入力途中でやめた場合の確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マイチケット用パスワードの形式が不正だと申し込めない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込フォームを開いている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パスワードに「abc」（3文字）と全角文字を、それぞれ入れて確認画面へ進む</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「マイチケット用パスワードは4〜16文字の英数字で入力してください」と表示され、先に進めない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-43</t>
+  </si>
+  <si>
     <t xml:space="preserve">・マイチケット</t>
   </si>
   <si>
@@ -1159,6 +1282,33 @@
     <t xml:space="preserve">ID: F-19 / F-28 ／ 送信そのものはメールソフトが行う</t>
   </si>
   <si>
+    <t xml:space="preserve">確認ダイアログでキャンセルを選ぶと申込はキャンセルされない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その行の「キャンセル」を押し、確認ダイアログで「キャンセル」を選ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">状態は「参加確定」のまま変わらず、券種の残りも変わらない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-13 ／ 誤って押しても実害が出ないことの確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">編集をやめると変更は保存されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参加者一覧で「編集」を開き、メールアドレスを書き換えた状態</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「やめる」で閉じる。続けて同じ操作を、背景をクリックして閉じる方法でも行う</t>
+  </si>
+  <si>
+    <t xml:space="preserve">どちらの閉じ方でも一覧のメールアドレスは元のままで、保存されていない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-30 ／ Escape キーで閉じた場合も同じ</t>
+  </si>
+  <si>
     <t xml:space="preserve">・ダッシュボード</t>
   </si>
   <si>
@@ -1399,6 +1549,72 @@
     <t xml:space="preserve">ID: F-21 ／ 初期化は元に戻せないため、このシートの最後に行う</t>
   </si>
   <si>
+    <t xml:space="preserve">確認ダイアログでキャンセルを選ぶとデータは変わらない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「デモデータを投入」「全データを初期化」「JSONを読み込む」のそれぞれで、確認ダイアログに「キャンセル」を選ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">どれもデータが変わらず、イベントと申込の件数が元のまま</t>
+  </si>
+  <si>
+    <t xml:space="preserve">初期化は元に戻せないため、取りやめが効くことを必ず確認する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同じ名前のカテゴリは登録できない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">すでにある「勉強会」と同じ名前を入力して「追加」を押す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「このカテゴリはすでに登録されています」と表示され、追加されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">前後の空白を除いて同じ名前かを判定する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カテゴリは21件目を登録できない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カテゴリが20件登録されている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21件目の名前を入力して「追加」を押す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「カテゴリは20件以内で登録してください」と表示され、追加されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">上限20件の1つ外側</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カテゴリが1件もないとイベントを作成できない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カテゴリをすべて削除した状態</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「イベントを作成」を開く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「カテゴリが1件も登録されていないため、イベントを作成できません」と出て、設定画面への案内が示される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-12 ／ 分類のないイベントを作らせないため</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パスコードは4〜16文字の英数字以外を受け付けない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新しいパスコードに「abc」（3文字）・17文字・記号入りを、それぞれ入れて変更する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「パスコードは4〜16文字の英数字で入力してください」と表示され、変更されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-33 ／ 下限4文字・上限16文字の1つ外側</t>
+  </si>
+  <si>
     <t xml:space="preserve">・資料・運営体制</t>
   </si>
   <si>
@@ -1480,6 +1696,48 @@
     <t xml:space="preserve">ID: F-35 / D-44 ／ 誰が何を担当するかを記録しておくため</t>
   </si>
   <si>
+    <t xml:space="preserve">資料を削除でき、取りやめれば削除されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">資料が2件登録されている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1件の「削除」を押して確認ダイアログで「キャンセル」を選ぶ。もう一度押して今度は「OK」を選ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">キャンセルでは残り、OKで削除される。件数が 2 → 2 → 1 と変わる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-34 ／ 誤って押しても実害が出ないことの確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">資料は21件目を登録できない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">資料が20件登録されている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21件目のファイルを登録しようとする</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「資料は20件以内で登録してください」と表示され、登録されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">運営体制の編集をやめると保存されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「運営体制」の編集でメンバーを追加し、氏名と担当を入力した状態</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「やめる」を押して閉じる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パネルの表示は元のままで、追加したメンバーは保存されていない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-35</t>
+  </si>
+  <si>
     <t xml:space="preserve">・境界値・異常系</t>
   </si>
   <si>
@@ -1576,6 +1834,66 @@
     <t xml:space="preserve">ID: D-40</t>
   </si>
   <si>
+    <t xml:space="preserve">文字数の上限を超える入力は保存できない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">上限を1文字超える文字列を用意する（入力欄が止めるため貼り付けで入れる）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベント作成画面でイベント名101文字・説明文2001文字・会場名201文字、申込フォームで氏名51文字・メールアドレス255文字、カテゴリ管理でカテゴリ名31文字を入れて保存する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">いずれも「○○は△文字以内で入力してください」と表示され、保存されない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-11 ／ 参加者情報の編集では入力欄の maxlength で止めている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メールアドレスと視聴URLの形式が不正だと保存できない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込フォームと、オンライン開催のイベント作成画面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メールアドレスに「@ のない文字列」、視聴URLに「http で始まらない文字列」を入れて進む</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「メールアドレスの形式が正しくありません」「視聴URLの形式が正しくありません」と表示され、先に進めない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-18 / D-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">正方形の画像でも崩れず表示される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験データ／画像／生成／試験_正方形_800x800.jpg を用意する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カバー画像・組織ロゴ・ヘッダー画像のそれぞれに登録し、公開ページと一覧のカードを開く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">縦横比が保たれ、はみ出しや余白の破綻がない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-15 / D-37 / D-38 ／ 横長の画像（1-9）とあわせて両方で確認する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">画像を含むデータを書き出して読み込むと画像も戻る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カバー画像つきのイベントと、組織ロゴ・ヘッダー画像がある状態</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JSONを書き出し、全データを初期化してから読み込み、公開ページと一覧のカードを開く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カバー画像・組織ロゴ・ヘッダー画像がすべて表示される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-20 ／ 画像は文字列に変換して書き出している</t>
+  </si>
+  <si>
     <t xml:space="preserve">★ NG項目一覧（試験でNGだった点と対応）</t>
   </si>
   <si>
@@ -1601,9 +1919,6 @@
   </si>
   <si>
     <t xml:space="preserve">〇</t>
-  </si>
-  <si>
-    <t xml:space="preserve">利用</t>
   </si>
 </sst>
 </file>
@@ -2423,6 +2738,1139 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P22"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="2" max="2" width="5.9140625" style="17" customWidth="1"/>
+    <col min="3" max="3" width="3.9140625" style="17" customWidth="1"/>
+    <col min="4" max="4" width="4.1640625" style="17" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" style="17" customWidth="1"/>
+    <col min="6" max="6" width="47.58203125" style="17" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" style="17" customWidth="1"/>
+    <col min="8" max="8" width="9.83203125" style="17" customWidth="1"/>
+    <col min="9" max="9" width="35.6640625" style="17" customWidth="1"/>
+    <col min="10" max="10" width="57.08203125" style="17" customWidth="1"/>
+    <col min="11" max="11" width="71" style="17" customWidth="1"/>
+    <col min="12" max="12" width="10.5" style="17" customWidth="1"/>
+    <col min="13" max="13" width="10.75" style="17" customWidth="1"/>
+    <col min="14" max="14" width="13" style="17" customWidth="1"/>
+    <col min="15" max="15" width="44.58203125" style="17" customWidth="1"/>
+    <col min="16" max="16" width="6.5" style="17" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="26.5">
+      <c r="A1" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+    </row>
+    <row r="3" spans="1:16" ht="42" customHeight="1">
+      <c r="B3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>456</v>
+      </c>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+    </row>
+    <row r="4" spans="1:16" ht="42" customHeight="1">
+      <c r="B4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>457</v>
+      </c>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="B6" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="27"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="B7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" s="15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="B8" s="28">
+        <v>8</v>
+      </c>
+      <c r="C8" s="28">
+        <v>1</v>
+      </c>
+      <c r="D8" s="22">
+        <v>1</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>458</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>460</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>461</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>462</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M8" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O8" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="P8" s="13"/>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="22">
+        <v>2</v>
+      </c>
+      <c r="E9" s="32"/>
+      <c r="F9" s="13" t="s">
+        <v>464</v>
+      </c>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>465</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>466</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M9" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>468</v>
+      </c>
+      <c r="P9" s="13"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="22">
+        <v>3</v>
+      </c>
+      <c r="E10" s="32"/>
+      <c r="F10" s="13" t="s">
+        <v>469</v>
+      </c>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>471</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M10" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O10" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="P10" s="13"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="22">
+        <v>4</v>
+      </c>
+      <c r="E11" s="32"/>
+      <c r="F11" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M11" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O11" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="P11" s="13"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="22">
+        <v>5</v>
+      </c>
+      <c r="E12" s="32"/>
+      <c r="F12" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>482</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M12" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O12" s="13" t="s">
+        <v>483</v>
+      </c>
+      <c r="P12" s="13"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="22">
+        <v>6</v>
+      </c>
+      <c r="E13" s="32"/>
+      <c r="F13" s="13" t="s">
+        <v>484</v>
+      </c>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>485</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>487</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M13" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>488</v>
+      </c>
+      <c r="P13" s="13"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="22">
+        <v>7</v>
+      </c>
+      <c r="E14" s="32"/>
+      <c r="F14" s="13" t="s">
+        <v>489</v>
+      </c>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>490</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>491</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>492</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M14" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O14" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="P14" s="13"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="22">
+        <v>8</v>
+      </c>
+      <c r="E15" s="32"/>
+      <c r="F15" s="13" t="s">
+        <v>494</v>
+      </c>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>495</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>496</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>497</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M15" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O15" s="13" t="s">
+        <v>498</v>
+      </c>
+      <c r="P15" s="13"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="22">
+        <v>9</v>
+      </c>
+      <c r="E16" s="32"/>
+      <c r="F16" s="13" t="s">
+        <v>499</v>
+      </c>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>500</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>501</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>502</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M16" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O16" s="13" t="s">
+        <v>503</v>
+      </c>
+      <c r="P16" s="13"/>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="22">
+        <v>10</v>
+      </c>
+      <c r="E17" s="32"/>
+      <c r="F17" s="13" t="s">
+        <v>504</v>
+      </c>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>506</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>507</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M17" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O17" s="13" t="s">
+        <v>508</v>
+      </c>
+      <c r="P17" s="13"/>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="22">
+        <v>11</v>
+      </c>
+      <c r="E18" s="32"/>
+      <c r="F18" s="13" t="s">
+        <v>509</v>
+      </c>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>510</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>511</v>
+      </c>
+      <c r="L18" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M18" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O18" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="P18" s="13"/>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="22">
+        <v>12</v>
+      </c>
+      <c r="E19" s="32"/>
+      <c r="F19" s="13" t="s">
+        <v>513</v>
+      </c>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>485</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>514</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>515</v>
+      </c>
+      <c r="L19" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M19" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O19" s="13" t="s">
+        <v>516</v>
+      </c>
+      <c r="P19" s="13"/>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="22">
+        <v>13</v>
+      </c>
+      <c r="E20" s="32"/>
+      <c r="F20" s="13" t="s">
+        <v>517</v>
+      </c>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>518</v>
+      </c>
+      <c r="J20" s="13" t="s">
+        <v>519</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>520</v>
+      </c>
+      <c r="L20" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M20" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O20" s="13" t="s">
+        <v>521</v>
+      </c>
+      <c r="P20" s="13"/>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="22">
+        <v>14</v>
+      </c>
+      <c r="E21" s="32"/>
+      <c r="F21" s="13" t="s">
+        <v>522</v>
+      </c>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>524</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>525</v>
+      </c>
+      <c r="L21" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M21" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N21" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O21" s="13" t="s">
+        <v>526</v>
+      </c>
+      <c r="P21" s="13"/>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="22">
+        <v>15</v>
+      </c>
+      <c r="E22" s="32"/>
+      <c r="F22" s="13" t="s">
+        <v>527</v>
+      </c>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>528</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>529</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M22" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O22" s="13" t="s">
+        <v>530</v>
+      </c>
+      <c r="P22" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="B6:K6"/>
+    <mergeCell ref="L6:P6"/>
+    <mergeCell ref="B8:B22"/>
+    <mergeCell ref="C8:C22"/>
+    <mergeCell ref="E8:E22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P15"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="2" max="2" width="5.9140625" style="17" customWidth="1"/>
+    <col min="3" max="3" width="3.9140625" style="17" customWidth="1"/>
+    <col min="4" max="4" width="4.1640625" style="17" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" style="17" customWidth="1"/>
+    <col min="6" max="6" width="47.58203125" style="17" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" style="17" customWidth="1"/>
+    <col min="8" max="8" width="9.83203125" style="17" customWidth="1"/>
+    <col min="9" max="9" width="35.6640625" style="17" customWidth="1"/>
+    <col min="10" max="10" width="57.08203125" style="17" customWidth="1"/>
+    <col min="11" max="11" width="71" style="17" customWidth="1"/>
+    <col min="12" max="12" width="10.5" style="17" customWidth="1"/>
+    <col min="13" max="13" width="10.75" style="17" customWidth="1"/>
+    <col min="14" max="14" width="13" style="17" customWidth="1"/>
+    <col min="15" max="15" width="44.58203125" style="17" customWidth="1"/>
+    <col min="16" max="16" width="6.5" style="17" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="26.5">
+      <c r="A1" s="24" t="s">
+        <v>531</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+    </row>
+    <row r="3" spans="1:16" ht="42" customHeight="1">
+      <c r="B3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>532</v>
+      </c>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+    </row>
+    <row r="4" spans="1:16" ht="42" customHeight="1">
+      <c r="B4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>533</v>
+      </c>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="B6" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="27"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="B7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" s="15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="B8" s="28">
+        <v>9</v>
+      </c>
+      <c r="C8" s="28">
+        <v>1</v>
+      </c>
+      <c r="D8" s="22">
+        <v>1</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>534</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>535</v>
+      </c>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>536</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>537</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>538</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M8" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O8" s="13" t="s">
+        <v>539</v>
+      </c>
+      <c r="P8" s="13"/>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="22">
+        <v>2</v>
+      </c>
+      <c r="E9" s="32"/>
+      <c r="F9" s="13" t="s">
+        <v>540</v>
+      </c>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>536</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>541</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>542</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M9" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>543</v>
+      </c>
+      <c r="P9" s="13"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="22">
+        <v>3</v>
+      </c>
+      <c r="E10" s="32"/>
+      <c r="F10" s="13" t="s">
+        <v>544</v>
+      </c>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>545</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>546</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>547</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M10" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="22">
+        <v>4</v>
+      </c>
+      <c r="E11" s="32"/>
+      <c r="F11" s="13" t="s">
+        <v>548</v>
+      </c>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>549</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>550</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>551</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M11" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O11" s="13" t="s">
+        <v>552</v>
+      </c>
+      <c r="P11" s="13"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="22">
+        <v>5</v>
+      </c>
+      <c r="E12" s="32"/>
+      <c r="F12" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>554</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>555</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>556</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M12" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O12" s="13" t="s">
+        <v>557</v>
+      </c>
+      <c r="P12" s="13"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="22">
+        <v>6</v>
+      </c>
+      <c r="E13" s="32"/>
+      <c r="F13" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>559</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>560</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M13" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>562</v>
+      </c>
+      <c r="P13" s="13"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="22">
+        <v>7</v>
+      </c>
+      <c r="E14" s="32"/>
+      <c r="F14" s="13" t="s">
+        <v>563</v>
+      </c>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>564</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>565</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>566</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M14" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O14" s="13" t="s">
+        <v>521</v>
+      </c>
+      <c r="P14" s="13"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="22">
+        <v>8</v>
+      </c>
+      <c r="E15" s="32"/>
+      <c r="F15" s="13" t="s">
+        <v>567</v>
+      </c>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>568</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>569</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>570</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M15" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O15" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="P15" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="B6:K6"/>
+    <mergeCell ref="L6:P6"/>
+    <mergeCell ref="B8:B15"/>
+    <mergeCell ref="C8:C15"/>
+    <mergeCell ref="E8:E15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P17"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
@@ -2445,7 +3893,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>405</v>
+        <v>572</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2457,7 +3905,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>406</v>
+        <v>573</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -2468,7 +3916,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>407</v>
+        <v>574</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -2544,7 +3992,7 @@
     </row>
     <row r="8" spans="1:16">
       <c r="B8" s="28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C8" s="28">
         <v>1</v>
@@ -2553,23 +4001,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>408</v>
+        <v>575</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>409</v>
+        <v>576</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>410</v>
+        <v>460</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>411</v>
+        <v>577</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>412</v>
+        <v>578</v>
       </c>
       <c r="L8" s="13" t="s">
         <v>87</v>
@@ -2578,14 +4026,10 @@
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O8" s="13" t="s">
-        <v>413</v>
-      </c>
-      <c r="P8" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>632</v>
+      </c>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
     </row>
     <row r="9" spans="1:16">
       <c r="B9" s="29"/>
@@ -2595,20 +4039,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>414</v>
+        <v>579</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>415</v>
+        <v>580</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>416</v>
+        <v>581</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>417</v>
+        <v>582</v>
       </c>
       <c r="L9" s="13" t="s">
         <v>87</v>
@@ -2617,14 +4061,12 @@
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>418</v>
-      </c>
-      <c r="P9" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>583</v>
+      </c>
+      <c r="P9" s="13"/>
     </row>
     <row r="10" spans="1:16">
       <c r="B10" s="29"/>
@@ -2634,28 +4076,32 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>419</v>
+        <v>584</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>420</v>
+        <v>585</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>421</v>
+        <v>586</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>422</v>
+        <v>587</v>
       </c>
       <c r="L10" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="13"/>
+      <c r="M10" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>632</v>
+      </c>
       <c r="O10" s="13" t="s">
-        <v>423</v>
+        <v>588</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -2667,20 +4113,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>424</v>
+        <v>589</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>425</v>
+        <v>590</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>426</v>
+        <v>591</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>427</v>
+        <v>592</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>87</v>
@@ -2689,14 +4135,12 @@
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>428</v>
-      </c>
-      <c r="P11" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="P11" s="13"/>
     </row>
     <row r="12" spans="1:16">
       <c r="B12" s="29"/>
@@ -2706,20 +4150,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>429</v>
+        <v>594</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>430</v>
+        <v>595</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>431</v>
+        <v>596</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>432</v>
+        <v>597</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>87</v>
@@ -2728,14 +4172,12 @@
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>433</v>
-      </c>
-      <c r="P12" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="P12" s="13"/>
     </row>
     <row r="13" spans="1:16">
       <c r="B13" s="29"/>
@@ -2745,20 +4187,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>434</v>
+        <v>599</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>435</v>
+        <v>600</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>436</v>
+        <v>601</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>437</v>
+        <v>602</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>87</v>
@@ -2767,14 +4209,12 @@
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>438</v>
-      </c>
-      <c r="P13" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>603</v>
+      </c>
+      <c r="P13" s="13"/>
     </row>
     <row r="14" spans="1:16">
       <c r="B14" s="29"/>
@@ -2784,20 +4224,20 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>439</v>
+        <v>604</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>440</v>
+        <v>605</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>441</v>
+        <v>606</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>442</v>
+        <v>607</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>87</v>
@@ -2806,14 +4246,12 @@
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>443</v>
-      </c>
-      <c r="P14" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>608</v>
+      </c>
+      <c r="P14" s="13"/>
     </row>
     <row r="15" spans="1:16">
       <c r="B15" s="29"/>
@@ -2823,20 +4261,20 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>444</v>
+        <v>609</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>445</v>
+        <v>610</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>446</v>
+        <v>611</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>447</v>
+        <v>612</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>87</v>
@@ -2845,14 +4283,12 @@
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>448</v>
-      </c>
-      <c r="P15" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>613</v>
+      </c>
+      <c r="P15" s="13"/>
     </row>
     <row r="16" spans="1:16">
       <c r="B16" s="29"/>
@@ -2862,20 +4298,20 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>449</v>
+        <v>614</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>450</v>
+        <v>615</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>451</v>
+        <v>616</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>452</v>
+        <v>617</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>87</v>
@@ -2884,14 +4320,12 @@
         <v>46232</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="P16" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>618</v>
+      </c>
+      <c r="P16" s="13"/>
     </row>
     <row r="17" spans="1:16">
       <c r="B17" s="29"/>
@@ -2901,20 +4335,20 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>454</v>
+        <v>619</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>455</v>
+        <v>620</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>456</v>
+        <v>621</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>457</v>
+        <v>622</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>87</v>
@@ -2923,14 +4357,12 @@
         <v>46232</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>458</v>
-      </c>
-      <c r="P17" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>623</v>
+      </c>
+      <c r="P17" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2942,709 +4374,6 @@
     <mergeCell ref="B8:B17"/>
     <mergeCell ref="C8:C17"/>
     <mergeCell ref="E8:E17"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P12"/>
-  <sheetFormatPr defaultRowHeight="18"/>
-  <cols>
-    <col min="2" max="2" width="5.9140625" style="17" customWidth="1"/>
-    <col min="3" max="3" width="3.9140625" style="17" customWidth="1"/>
-    <col min="4" max="4" width="4.1640625" style="17" customWidth="1"/>
-    <col min="5" max="5" width="22.6640625" style="17" customWidth="1"/>
-    <col min="6" max="6" width="47.58203125" style="17" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" style="17" customWidth="1"/>
-    <col min="8" max="8" width="9.83203125" style="17" customWidth="1"/>
-    <col min="9" max="9" width="35.6640625" style="17" customWidth="1"/>
-    <col min="10" max="10" width="57.08203125" style="17" customWidth="1"/>
-    <col min="11" max="11" width="71" style="17" customWidth="1"/>
-    <col min="12" max="12" width="10.5" style="17" customWidth="1"/>
-    <col min="13" max="13" width="10.75" style="17" customWidth="1"/>
-    <col min="14" max="14" width="13" style="17" customWidth="1"/>
-    <col min="15" max="15" width="44.58203125" style="17" customWidth="1"/>
-    <col min="16" max="16" width="6.5" style="17" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="26.5">
-      <c r="A1" s="24" t="s">
-        <v>459</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-    </row>
-    <row r="3" spans="1:16" ht="42" customHeight="1">
-      <c r="B3" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>460</v>
-      </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-    </row>
-    <row r="4" spans="1:16" ht="42" customHeight="1">
-      <c r="B4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>461</v>
-      </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="B6" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="27"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="B7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="P7" s="15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="B8" s="28">
-        <v>9</v>
-      </c>
-      <c r="C8" s="28">
-        <v>1</v>
-      </c>
-      <c r="D8" s="22">
-        <v>1</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>462</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>463</v>
-      </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>464</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>465</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>466</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M8" s="2">
-        <v>46232</v>
-      </c>
-      <c r="N8" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O8" s="13" t="s">
-        <v>467</v>
-      </c>
-      <c r="P8" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="22">
-        <v>2</v>
-      </c>
-      <c r="E9" s="32"/>
-      <c r="F9" s="13" t="s">
-        <v>468</v>
-      </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>464</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>469</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>470</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M9" s="2">
-        <v>46232</v>
-      </c>
-      <c r="N9" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O9" s="13" t="s">
-        <v>471</v>
-      </c>
-      <c r="P9" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="22">
-        <v>3</v>
-      </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="13" t="s">
-        <v>472</v>
-      </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>473</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>474</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>475</v>
-      </c>
-      <c r="L10" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M10" s="2">
-        <v>46232</v>
-      </c>
-      <c r="N10" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="22">
-        <v>4</v>
-      </c>
-      <c r="E11" s="32"/>
-      <c r="F11" s="13" t="s">
-        <v>476</v>
-      </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>477</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>478</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>479</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M11" s="2">
-        <v>46232</v>
-      </c>
-      <c r="N11" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O11" s="13" t="s">
-        <v>480</v>
-      </c>
-      <c r="P11" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="22">
-        <v>5</v>
-      </c>
-      <c r="E12" s="32"/>
-      <c r="F12" s="13" t="s">
-        <v>481</v>
-      </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>482</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>483</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>484</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M12" s="2">
-        <v>46232</v>
-      </c>
-      <c r="N12" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O12" s="13" t="s">
-        <v>485</v>
-      </c>
-      <c r="P12" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="B6:K6"/>
-    <mergeCell ref="L6:P6"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="C8:C12"/>
-    <mergeCell ref="E8:E12"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultRowHeight="18"/>
-  <cols>
-    <col min="2" max="2" width="5.9140625" style="17" customWidth="1"/>
-    <col min="3" max="3" width="3.9140625" style="17" customWidth="1"/>
-    <col min="4" max="4" width="4.1640625" style="17" customWidth="1"/>
-    <col min="5" max="5" width="22.6640625" style="17" customWidth="1"/>
-    <col min="6" max="6" width="47.58203125" style="17" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" style="17" customWidth="1"/>
-    <col min="8" max="8" width="9.83203125" style="17" customWidth="1"/>
-    <col min="9" max="9" width="35.6640625" style="17" customWidth="1"/>
-    <col min="10" max="10" width="57.08203125" style="17" customWidth="1"/>
-    <col min="11" max="11" width="71" style="17" customWidth="1"/>
-    <col min="12" max="12" width="10.5" style="17" customWidth="1"/>
-    <col min="13" max="13" width="10.75" style="17" customWidth="1"/>
-    <col min="14" max="14" width="13" style="17" customWidth="1"/>
-    <col min="15" max="15" width="44.58203125" style="17" customWidth="1"/>
-    <col min="16" max="16" width="6.5" style="17" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="26.5">
-      <c r="A1" s="24" t="s">
-        <v>486</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-    </row>
-    <row r="3" spans="1:16" ht="42" customHeight="1">
-      <c r="B3" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>487</v>
-      </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-    </row>
-    <row r="4" spans="1:16" ht="42" customHeight="1">
-      <c r="B4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>488</v>
-      </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="B6" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="27"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="B7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="P7" s="15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="B8" s="28">
-        <v>10</v>
-      </c>
-      <c r="C8" s="28">
-        <v>1</v>
-      </c>
-      <c r="D8" s="22">
-        <v>1</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>489</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>490</v>
-      </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>410</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>491</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>492</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M8" s="2">
-        <v>46232</v>
-      </c>
-      <c r="N8" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="22">
-        <v>2</v>
-      </c>
-      <c r="E9" s="32"/>
-      <c r="F9" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>494</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>495</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>496</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M9" s="2">
-        <v>46232</v>
-      </c>
-      <c r="N9" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O9" s="13" t="s">
-        <v>497</v>
-      </c>
-      <c r="P9" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="22">
-        <v>3</v>
-      </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="13" t="s">
-        <v>498</v>
-      </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>499</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>500</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>501</v>
-      </c>
-      <c r="L10" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M10" s="2">
-        <v>46232</v>
-      </c>
-      <c r="N10" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O10" s="13" t="s">
-        <v>502</v>
-      </c>
-      <c r="P10" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="22">
-        <v>4</v>
-      </c>
-      <c r="E11" s="32"/>
-      <c r="F11" s="13" t="s">
-        <v>503</v>
-      </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>504</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>505</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>506</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13" t="s">
-        <v>507</v>
-      </c>
-      <c r="P11" s="13"/>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="22">
-        <v>5</v>
-      </c>
-      <c r="E12" s="32"/>
-      <c r="F12" s="13" t="s">
-        <v>508</v>
-      </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>509</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>510</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>511</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M12" s="2">
-        <v>46232</v>
-      </c>
-      <c r="N12" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O12" s="13" t="s">
-        <v>512</v>
-      </c>
-      <c r="P12" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="22">
-        <v>6</v>
-      </c>
-      <c r="E13" s="32"/>
-      <c r="F13" s="13" t="s">
-        <v>513</v>
-      </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>514</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>515</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>516</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M13" s="2">
-        <v>46232</v>
-      </c>
-      <c r="N13" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O13" s="13" t="s">
-        <v>517</v>
-      </c>
-      <c r="P13" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="B6:K6"/>
-    <mergeCell ref="L6:P6"/>
-    <mergeCell ref="B8:B13"/>
-    <mergeCell ref="C8:C13"/>
-    <mergeCell ref="E8:E13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3668,12 +4397,12 @@
   <sheetData>
     <row r="1" spans="1:12" ht="26.5">
       <c r="B1" s="24" t="s">
-        <v>518</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="B2" s="13" t="s">
-        <v>519</v>
+        <v>625</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -3681,16 +4410,16 @@
         <v>73</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>520</v>
+        <v>626</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>521</v>
+        <v>627</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>522</v>
+        <v>628</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>523</v>
+        <v>629</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>17</v>
@@ -3699,10 +4428,10 @@
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>524</v>
+        <v>630</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>525</v>
+        <v>631</v>
       </c>
     </row>
   </sheetData>
@@ -3990,7 +4719,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="5.9140625" style="17" customWidth="1"/>
@@ -4145,7 +4874,7 @@
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O8" s="13" t="s">
         <v>88</v>
@@ -4182,7 +4911,7 @@
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O9" s="13"/>
       <c r="P9" s="13"/>
@@ -4217,7 +4946,7 @@
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O10" s="13" t="s">
         <v>97</v>
@@ -4254,7 +4983,7 @@
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O11" s="13" t="s">
         <v>101</v>
@@ -4291,7 +5020,7 @@
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O12" s="13" t="s">
         <v>106</v>
@@ -4328,7 +5057,7 @@
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O13" s="13" t="s">
         <v>111</v>
@@ -4365,7 +5094,7 @@
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O14" s="13" t="s">
         <v>115</v>
@@ -4402,7 +5131,7 @@
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O15" s="13" t="s">
         <v>120</v>
@@ -4439,7 +5168,7 @@
         <v>46232</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O16" s="13" t="s">
         <v>125</v>
@@ -4476,7 +5205,7 @@
         <v>46232</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O17" s="13" t="s">
         <v>130</v>
@@ -4513,7 +5242,7 @@
         <v>46232</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O18" s="13" t="s">
         <v>135</v>
@@ -4550,7 +5279,7 @@
         <v>46232</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O19" s="13" t="s">
         <v>139</v>
@@ -4587,7 +5316,7 @@
         <v>46232</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O20" s="13" t="s">
         <v>144</v>
@@ -4624,12 +5353,123 @@
         <v>46232</v>
       </c>
       <c r="N21" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O21" s="13" t="s">
         <v>149</v>
       </c>
       <c r="P21" s="13"/>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="22">
+        <v>15</v>
+      </c>
+      <c r="E22" s="32"/>
+      <c r="F22" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M22" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O22" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="P22" s="13"/>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="22">
+        <v>16</v>
+      </c>
+      <c r="E23" s="32"/>
+      <c r="F23" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M23" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N23" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O23" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="P23" s="13"/>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="22">
+        <v>17</v>
+      </c>
+      <c r="E24" s="32"/>
+      <c r="F24" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M24" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N24" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O24" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="P24" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4638,15 +5478,601 @@
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="L6:P6"/>
-    <mergeCell ref="B8:B21"/>
-    <mergeCell ref="C8:C21"/>
-    <mergeCell ref="E8:E21"/>
+    <mergeCell ref="B8:B24"/>
+    <mergeCell ref="C8:C24"/>
+    <mergeCell ref="E8:E24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P19"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="2" max="2" width="5.9140625" style="17" customWidth="1"/>
+    <col min="3" max="3" width="3.9140625" style="17" customWidth="1"/>
+    <col min="4" max="4" width="4.1640625" style="17" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" style="17" customWidth="1"/>
+    <col min="6" max="6" width="47.58203125" style="17" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" style="17" customWidth="1"/>
+    <col min="8" max="8" width="9.83203125" style="17" customWidth="1"/>
+    <col min="9" max="9" width="35.6640625" style="17" customWidth="1"/>
+    <col min="10" max="10" width="57.08203125" style="17" customWidth="1"/>
+    <col min="11" max="11" width="71" style="17" customWidth="1"/>
+    <col min="12" max="12" width="10.5" style="17" customWidth="1"/>
+    <col min="13" max="13" width="10.75" style="17" customWidth="1"/>
+    <col min="14" max="14" width="13" style="17" customWidth="1"/>
+    <col min="15" max="15" width="44.58203125" style="17" customWidth="1"/>
+    <col min="16" max="16" width="6.5" style="17" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="26.5">
+      <c r="A1" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+    </row>
+    <row r="3" spans="1:16" ht="42" customHeight="1">
+      <c r="B3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+    </row>
+    <row r="4" spans="1:16" ht="42" customHeight="1">
+      <c r="B4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="B6" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="27"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="B7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" s="15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="B8" s="28">
+        <v>2</v>
+      </c>
+      <c r="C8" s="28">
+        <v>1</v>
+      </c>
+      <c r="D8" s="22">
+        <v>1</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>167</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M8" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O8" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="P8" s="13"/>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="22">
+        <v>2</v>
+      </c>
+      <c r="E9" s="32"/>
+      <c r="F9" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M9" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="P9" s="13"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="22">
+        <v>3</v>
+      </c>
+      <c r="E10" s="32"/>
+      <c r="F10" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M10" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O10" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="P10" s="13"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="22">
+        <v>4</v>
+      </c>
+      <c r="E11" s="32"/>
+      <c r="F11" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M11" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O11" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="P11" s="13"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="22">
+        <v>5</v>
+      </c>
+      <c r="E12" s="32"/>
+      <c r="F12" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M12" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O12" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="P12" s="13"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="22">
+        <v>6</v>
+      </c>
+      <c r="E13" s="32"/>
+      <c r="F13" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M13" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="P13" s="13"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="22">
+        <v>7</v>
+      </c>
+      <c r="E14" s="32"/>
+      <c r="F14" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M14" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O14" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="P14" s="13"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="22">
+        <v>8</v>
+      </c>
+      <c r="E15" s="32"/>
+      <c r="F15" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M15" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O15" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="P15" s="13"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="22">
+        <v>9</v>
+      </c>
+      <c r="E16" s="32"/>
+      <c r="F16" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M16" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O16" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="P16" s="13"/>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="22">
+        <v>10</v>
+      </c>
+      <c r="E17" s="32"/>
+      <c r="F17" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M17" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O17" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="P17" s="13"/>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="22">
+        <v>11</v>
+      </c>
+      <c r="E18" s="32"/>
+      <c r="F18" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="L18" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M18" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O18" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="P18" s="13"/>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="22">
+        <v>12</v>
+      </c>
+      <c r="E19" s="32"/>
+      <c r="F19" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="L19" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M19" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O19" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="P19" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="B6:K6"/>
+    <mergeCell ref="L6:P6"/>
+    <mergeCell ref="B8:B19"/>
+    <mergeCell ref="C8:C19"/>
+    <mergeCell ref="E8:E19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P16"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -4670,7 +6096,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>150</v>
+        <v>221</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -4682,7 +6108,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>151</v>
+        <v>222</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -4693,7 +6119,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>152</v>
+        <v>223</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -4769,7 +6195,7 @@
     </row>
     <row r="8" spans="1:16">
       <c r="B8" s="28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" s="28">
         <v>1</v>
@@ -4778,23 +6204,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>153</v>
+        <v>224</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>154</v>
+        <v>225</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>155</v>
+        <v>226</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>156</v>
+        <v>227</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>157</v>
+        <v>228</v>
       </c>
       <c r="L8" s="13" t="s">
         <v>87</v>
@@ -4803,10 +6229,10 @@
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>158</v>
+        <v>229</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -4818,20 +6244,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>159</v>
+        <v>230</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>155</v>
+        <v>231</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>160</v>
+        <v>232</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>161</v>
+        <v>233</v>
       </c>
       <c r="L9" s="13" t="s">
         <v>87</v>
@@ -4840,10 +6266,10 @@
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>162</v>
+        <v>234</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -4855,20 +6281,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>163</v>
+        <v>235</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>155</v>
+        <v>236</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>161</v>
+        <v>238</v>
       </c>
       <c r="L10" s="13" t="s">
         <v>87</v>
@@ -4877,10 +6303,10 @@
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>165</v>
+        <v>239</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -4892,20 +6318,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>166</v>
+        <v>240</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>167</v>
+        <v>241</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>168</v>
+        <v>242</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>169</v>
+        <v>243</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>87</v>
@@ -4914,11 +6340,9 @@
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O11" s="13" t="s">
-        <v>170</v>
-      </c>
+        <v>632</v>
+      </c>
+      <c r="O11" s="13"/>
       <c r="P11" s="13"/>
     </row>
     <row r="12" spans="1:16">
@@ -4929,20 +6353,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>167</v>
+        <v>241</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>172</v>
+        <v>245</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>173</v>
+        <v>246</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>87</v>
@@ -4951,10 +6375,10 @@
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>174</v>
+        <v>247</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -4966,20 +6390,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>175</v>
+        <v>248</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>176</v>
+        <v>249</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>177</v>
+        <v>227</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>178</v>
+        <v>250</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>87</v>
@@ -4988,11 +6412,9 @@
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O13" s="13" t="s">
-        <v>179</v>
-      </c>
+        <v>632</v>
+      </c>
+      <c r="O13" s="13"/>
       <c r="P13" s="13"/>
     </row>
     <row r="14" spans="1:16">
@@ -5003,20 +6425,20 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>180</v>
+        <v>251</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>181</v>
+        <v>253</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>182</v>
+        <v>254</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>87</v>
@@ -5025,10 +6447,10 @@
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>183</v>
+        <v>255</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -5040,20 +6462,20 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>185</v>
+        <v>257</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>186</v>
+        <v>258</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>187</v>
+        <v>259</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>87</v>
@@ -5062,10 +6484,10 @@
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="P15" s="13"/>
     </row>
@@ -5077,20 +6499,20 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>189</v>
+        <v>261</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>190</v>
+        <v>262</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>192</v>
+        <v>263</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>87</v>
@@ -5099,10 +6521,10 @@
         <v>46232</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>193</v>
+        <v>264</v>
       </c>
       <c r="P16" s="13"/>
     </row>
@@ -5121,9 +6543,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="5.9140625" style="17" customWidth="1"/>
@@ -5145,7 +6567,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>194</v>
+        <v>265</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -5157,7 +6579,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>195</v>
+        <v>266</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -5168,7 +6590,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -5244,7 +6666,7 @@
     </row>
     <row r="8" spans="1:16">
       <c r="B8" s="28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" s="28">
         <v>1</v>
@@ -5253,23 +6675,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>197</v>
+        <v>267</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>198</v>
+        <v>268</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>199</v>
+        <v>269</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>201</v>
+        <v>271</v>
       </c>
       <c r="L8" s="13" t="s">
         <v>87</v>
@@ -5278,10 +6700,10 @@
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>202</v>
+        <v>272</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -5293,20 +6715,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>203</v>
+        <v>273</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>204</v>
+        <v>274</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>205</v>
+        <v>275</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>206</v>
+        <v>276</v>
       </c>
       <c r="L9" s="13" t="s">
         <v>87</v>
@@ -5315,10 +6737,10 @@
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>207</v>
+        <v>277</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -5330,20 +6752,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>208</v>
+        <v>278</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>209</v>
+        <v>274</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>210</v>
+        <v>279</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>211</v>
+        <v>280</v>
       </c>
       <c r="L10" s="13" t="s">
         <v>87</v>
@@ -5352,10 +6774,10 @@
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>212</v>
+        <v>281</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -5367,20 +6789,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>213</v>
+        <v>282</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>214</v>
+        <v>283</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>215</v>
+        <v>284</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>216</v>
+        <v>285</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>87</v>
@@ -5389,7 +6811,7 @@
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O11" s="13"/>
       <c r="P11" s="13"/>
@@ -5402,20 +6824,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>217</v>
+        <v>286</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>214</v>
+        <v>287</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>218</v>
+        <v>288</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>219</v>
+        <v>289</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>87</v>
@@ -5424,10 +6846,10 @@
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>220</v>
+        <v>290</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -5439,20 +6861,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>221</v>
+        <v>291</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>222</v>
+        <v>292</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>200</v>
+        <v>253</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>223</v>
+        <v>293</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>87</v>
@@ -5461,9 +6883,11 @@
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O13" s="13"/>
+        <v>632</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>294</v>
+      </c>
       <c r="P13" s="13"/>
     </row>
     <row r="14" spans="1:16">
@@ -5474,20 +6898,20 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>224</v>
+        <v>295</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>226</v>
+        <v>297</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>227</v>
+        <v>298</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>87</v>
@@ -5496,10 +6920,10 @@
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>228</v>
+        <v>299</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -5511,20 +6935,20 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>229</v>
+        <v>300</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>230</v>
+        <v>301</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>231</v>
+        <v>302</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>232</v>
+        <v>303</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>87</v>
@@ -5533,12 +6957,160 @@
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>233</v>
+        <v>304</v>
       </c>
       <c r="P15" s="13"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="22">
+        <v>9</v>
+      </c>
+      <c r="E16" s="32"/>
+      <c r="F16" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M16" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O16" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="P16" s="13"/>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="22">
+        <v>10</v>
+      </c>
+      <c r="E17" s="32"/>
+      <c r="F17" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M17" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O17" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="P17" s="13"/>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="22">
+        <v>11</v>
+      </c>
+      <c r="E18" s="32"/>
+      <c r="F18" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="L18" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M18" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O18" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="P18" s="13"/>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="22">
+        <v>12</v>
+      </c>
+      <c r="E19" s="32"/>
+      <c r="F19" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="L19" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M19" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O19" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="P19" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -5547,539 +7119,9 @@
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="L6:P6"/>
-    <mergeCell ref="B8:B15"/>
-    <mergeCell ref="C8:C15"/>
-    <mergeCell ref="E8:E15"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P17"/>
-  <sheetFormatPr defaultRowHeight="18"/>
-  <cols>
-    <col min="2" max="2" width="5.9140625" style="17" customWidth="1"/>
-    <col min="3" max="3" width="3.9140625" style="17" customWidth="1"/>
-    <col min="4" max="4" width="4.1640625" style="17" customWidth="1"/>
-    <col min="5" max="5" width="22.6640625" style="17" customWidth="1"/>
-    <col min="6" max="6" width="47.58203125" style="17" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" style="17" customWidth="1"/>
-    <col min="8" max="8" width="9.83203125" style="17" customWidth="1"/>
-    <col min="9" max="9" width="35.6640625" style="17" customWidth="1"/>
-    <col min="10" max="10" width="57.08203125" style="17" customWidth="1"/>
-    <col min="11" max="11" width="71" style="17" customWidth="1"/>
-    <col min="12" max="12" width="10.5" style="17" customWidth="1"/>
-    <col min="13" max="13" width="10.75" style="17" customWidth="1"/>
-    <col min="14" max="14" width="13" style="17" customWidth="1"/>
-    <col min="15" max="15" width="44.58203125" style="17" customWidth="1"/>
-    <col min="16" max="16" width="6.5" style="17" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="26.5">
-      <c r="A1" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-    </row>
-    <row r="3" spans="1:16" ht="42" customHeight="1">
-      <c r="B3" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-    </row>
-    <row r="4" spans="1:16" ht="42" customHeight="1">
-      <c r="B4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="B6" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="27"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="B7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="P7" s="15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="B8" s="28">
-        <v>4</v>
-      </c>
-      <c r="C8" s="28">
-        <v>1</v>
-      </c>
-      <c r="D8" s="22">
-        <v>1</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>236</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M8" s="2">
-        <v>46232</v>
-      </c>
-      <c r="N8" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O8" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="P8" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="22">
-        <v>2</v>
-      </c>
-      <c r="E9" s="32"/>
-      <c r="F9" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M9" s="2">
-        <v>46232</v>
-      </c>
-      <c r="N9" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O9" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="P9" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="22">
-        <v>3</v>
-      </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="L10" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M10" s="2">
-        <v>46232</v>
-      </c>
-      <c r="N10" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O10" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="P10" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="22">
-        <v>4</v>
-      </c>
-      <c r="E11" s="32"/>
-      <c r="F11" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M11" s="2">
-        <v>46232</v>
-      </c>
-      <c r="N11" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="22">
-        <v>5</v>
-      </c>
-      <c r="E12" s="32"/>
-      <c r="F12" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M12" s="2">
-        <v>46232</v>
-      </c>
-      <c r="N12" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O12" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="P12" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="22">
-        <v>6</v>
-      </c>
-      <c r="E13" s="32"/>
-      <c r="F13" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M13" s="2">
-        <v>46232</v>
-      </c>
-      <c r="N13" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O13" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="P13" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="22">
-        <v>7</v>
-      </c>
-      <c r="E14" s="32"/>
-      <c r="F14" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M14" s="2">
-        <v>46232</v>
-      </c>
-      <c r="N14" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O14" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="P14" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="22">
-        <v>8</v>
-      </c>
-      <c r="E15" s="32"/>
-      <c r="F15" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M15" s="2">
-        <v>46232</v>
-      </c>
-      <c r="N15" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O15" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="P15" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="22">
-        <v>9</v>
-      </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="J16" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="K16" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="L16" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M16" s="2">
-        <v>46232</v>
-      </c>
-      <c r="N16" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O16" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="P16" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="22">
-        <v>10</v>
-      </c>
-      <c r="E17" s="32"/>
-      <c r="F17" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="K17" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M17" s="2">
-        <v>46232</v>
-      </c>
-      <c r="N17" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="O17" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="P17" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="B6:K6"/>
-    <mergeCell ref="L6:P6"/>
-    <mergeCell ref="B8:B17"/>
-    <mergeCell ref="C8:C17"/>
-    <mergeCell ref="E8:E17"/>
+    <mergeCell ref="B8:B19"/>
+    <mergeCell ref="C8:C19"/>
+    <mergeCell ref="E8:E19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6109,7 +7151,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>283</v>
+        <v>324</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -6121,7 +7163,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -6132,7 +7174,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>285</v>
+        <v>326</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -6220,20 +7262,20 @@
         <v>56</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>286</v>
+        <v>327</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>287</v>
+        <v>328</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>288</v>
+        <v>329</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>289</v>
+        <v>330</v>
       </c>
       <c r="L8" s="13" t="s">
         <v>87</v>
@@ -6242,14 +7284,12 @@
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="P8" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="P8" s="13"/>
     </row>
     <row r="9" spans="1:16">
       <c r="B9" s="29"/>
@@ -6259,20 +7299,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>291</v>
+        <v>332</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>287</v>
+        <v>328</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>292</v>
+        <v>333</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>293</v>
+        <v>334</v>
       </c>
       <c r="L9" s="13" t="s">
         <v>87</v>
@@ -6281,12 +7321,10 @@
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O9" s="13"/>
-      <c r="P9" s="13" t="s">
-        <v>527</v>
-      </c>
+      <c r="P9" s="13"/>
     </row>
     <row r="10" spans="1:16">
       <c r="B10" s="29"/>
@@ -6296,20 +7334,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>294</v>
+        <v>335</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>295</v>
+        <v>336</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>297</v>
+        <v>338</v>
       </c>
       <c r="L10" s="13" t="s">
         <v>87</v>
@@ -6318,14 +7356,12 @@
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="P10" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="P10" s="13"/>
     </row>
     <row r="11" spans="1:16">
       <c r="B11" s="29"/>
@@ -6335,28 +7371,32 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>299</v>
+        <v>340</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>301</v>
+        <v>342</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>302</v>
+        <v>343</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="13"/>
+      <c r="M11" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>632</v>
+      </c>
       <c r="O11" s="13" t="s">
-        <v>303</v>
+        <v>344</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -6368,20 +7408,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>304</v>
+        <v>345</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>305</v>
+        <v>346</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>306</v>
+        <v>347</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>307</v>
+        <v>348</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>87</v>
@@ -6390,12 +7430,10 @@
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O12" s="13"/>
-      <c r="P12" s="13" t="s">
-        <v>527</v>
-      </c>
+      <c r="P12" s="13"/>
     </row>
     <row r="13" spans="1:16">
       <c r="B13" s="29"/>
@@ -6405,20 +7443,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>309</v>
+        <v>350</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>306</v>
+        <v>347</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>310</v>
+        <v>351</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>87</v>
@@ -6427,14 +7465,12 @@
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>311</v>
-      </c>
-      <c r="P13" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="P13" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -6453,7 +7489,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="5.9140625" style="17" customWidth="1"/>
@@ -6475,7 +7511,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -6487,7 +7523,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>313</v>
+        <v>354</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -6498,7 +7534,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>314</v>
+        <v>355</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -6583,23 +7619,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>316</v>
+        <v>357</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>317</v>
+        <v>358</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>319</v>
+        <v>360</v>
       </c>
       <c r="L8" s="13" t="s">
         <v>87</v>
@@ -6608,14 +7644,12 @@
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>320</v>
-      </c>
-      <c r="P8" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="P8" s="13"/>
     </row>
     <row r="9" spans="1:16">
       <c r="B9" s="29"/>
@@ -6625,20 +7659,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>321</v>
+        <v>362</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>323</v>
+        <v>364</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>324</v>
+        <v>365</v>
       </c>
       <c r="L9" s="13" t="s">
         <v>87</v>
@@ -6647,14 +7681,12 @@
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="P9" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="P9" s="13"/>
     </row>
     <row r="10" spans="1:16">
       <c r="B10" s="29"/>
@@ -6664,20 +7696,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>326</v>
+        <v>367</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>329</v>
+        <v>370</v>
       </c>
       <c r="L10" s="13" t="s">
         <v>87</v>
@@ -6686,14 +7718,12 @@
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="P10" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="P10" s="13"/>
     </row>
     <row r="11" spans="1:16">
       <c r="B11" s="29"/>
@@ -6703,20 +7733,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>331</v>
+        <v>372</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>332</v>
+        <v>373</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>333</v>
+        <v>374</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>334</v>
+        <v>375</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>87</v>
@@ -6725,14 +7755,12 @@
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="P11" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="P11" s="13"/>
     </row>
     <row r="12" spans="1:16">
       <c r="B12" s="29"/>
@@ -6742,20 +7770,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>336</v>
+        <v>377</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>337</v>
+        <v>378</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>87</v>
@@ -6764,14 +7792,12 @@
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="P12" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="P12" s="13"/>
     </row>
     <row r="13" spans="1:16">
       <c r="B13" s="29"/>
@@ -6781,20 +7807,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>341</v>
+        <v>382</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>343</v>
+        <v>384</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>87</v>
@@ -6803,14 +7829,12 @@
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="P13" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="P13" s="13"/>
     </row>
     <row r="14" spans="1:16">
       <c r="B14" s="29"/>
@@ -6820,20 +7844,20 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>347</v>
+        <v>388</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>348</v>
+        <v>389</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>349</v>
+        <v>390</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>87</v>
@@ -6842,14 +7866,12 @@
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="P14" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="P14" s="13"/>
     </row>
     <row r="15" spans="1:16">
       <c r="B15" s="29"/>
@@ -6859,20 +7881,20 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>351</v>
+        <v>392</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>353</v>
+        <v>394</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>354</v>
+        <v>395</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>87</v>
@@ -6881,14 +7903,12 @@
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>355</v>
-      </c>
-      <c r="P15" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="P15" s="13"/>
     </row>
     <row r="16" spans="1:16">
       <c r="B16" s="29"/>
@@ -6898,20 +7918,20 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>356</v>
+        <v>397</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>357</v>
+        <v>398</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>358</v>
+        <v>399</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>359</v>
+        <v>400</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>87</v>
@@ -6920,14 +7940,12 @@
         <v>46232</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>360</v>
-      </c>
-      <c r="P16" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="P16" s="13"/>
     </row>
     <row r="17" spans="1:16">
       <c r="B17" s="29"/>
@@ -6937,20 +7955,20 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>361</v>
+        <v>402</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>362</v>
+        <v>403</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>363</v>
+        <v>404</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>87</v>
@@ -6959,14 +7977,12 @@
         <v>46232</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>364</v>
-      </c>
-      <c r="P17" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="P17" s="13"/>
     </row>
     <row r="18" spans="1:16">
       <c r="B18" s="29"/>
@@ -6976,20 +7992,20 @@
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="13" t="s">
-        <v>365</v>
+        <v>406</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>366</v>
+        <v>407</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>367</v>
+        <v>408</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>368</v>
+        <v>409</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>87</v>
@@ -6998,14 +8014,12 @@
         <v>46232</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O18" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="P18" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="P18" s="13"/>
     </row>
     <row r="19" spans="1:16">
       <c r="B19" s="29"/>
@@ -7015,20 +8029,20 @@
       </c>
       <c r="E19" s="32"/>
       <c r="F19" s="13" t="s">
-        <v>370</v>
+        <v>411</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>371</v>
+        <v>412</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>372</v>
+        <v>413</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>87</v>
@@ -7037,14 +8051,12 @@
         <v>46232</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O19" s="13" t="s">
-        <v>373</v>
-      </c>
-      <c r="P19" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="P19" s="13"/>
     </row>
     <row r="20" spans="1:16">
       <c r="B20" s="29"/>
@@ -7054,20 +8066,20 @@
       </c>
       <c r="E20" s="32"/>
       <c r="F20" s="13" t="s">
-        <v>374</v>
+        <v>415</v>
       </c>
       <c r="G20" s="13"/>
       <c r="H20" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>375</v>
+        <v>416</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>376</v>
+        <v>417</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="L20" s="13" t="s">
         <v>87</v>
@@ -7076,14 +8088,86 @@
         <v>46232</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O20" s="13" t="s">
-        <v>378</v>
-      </c>
-      <c r="P20" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="P20" s="13"/>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="22">
+        <v>14</v>
+      </c>
+      <c r="E21" s="32"/>
+      <c r="F21" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="L21" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M21" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N21" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O21" s="13" t="s">
+        <v>423</v>
+      </c>
+      <c r="P21" s="13"/>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="22">
+        <v>15</v>
+      </c>
+      <c r="E22" s="32"/>
+      <c r="F22" s="13" t="s">
+        <v>424</v>
+      </c>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M22" s="2">
+        <v>46232</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="O22" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="P22" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -7092,9 +8176,9 @@
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="L6:P6"/>
-    <mergeCell ref="B8:B20"/>
-    <mergeCell ref="C8:C20"/>
-    <mergeCell ref="E8:E20"/>
+    <mergeCell ref="B8:B22"/>
+    <mergeCell ref="C8:C22"/>
+    <mergeCell ref="E8:E22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7124,7 +8208,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>379</v>
+        <v>429</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -7136,7 +8220,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>380</v>
+        <v>430</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -7147,7 +8231,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>381</v>
+        <v>431</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -7232,23 +8316,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>382</v>
+        <v>432</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>383</v>
+        <v>433</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>384</v>
+        <v>434</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>385</v>
+        <v>435</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>386</v>
+        <v>436</v>
       </c>
       <c r="L8" s="13" t="s">
         <v>87</v>
@@ -7257,14 +8341,12 @@
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="P8" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="P8" s="13"/>
     </row>
     <row r="9" spans="1:16">
       <c r="B9" s="29"/>
@@ -7274,20 +8356,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>388</v>
+        <v>438</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>384</v>
+        <v>434</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>389</v>
+        <v>439</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>390</v>
+        <v>440</v>
       </c>
       <c r="L9" s="13" t="s">
         <v>87</v>
@@ -7296,14 +8378,12 @@
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="P9" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="P9" s="13"/>
     </row>
     <row r="10" spans="1:16">
       <c r="B10" s="29"/>
@@ -7313,20 +8393,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>392</v>
+        <v>442</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>393</v>
+        <v>443</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>394</v>
+        <v>444</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>395</v>
+        <v>445</v>
       </c>
       <c r="L10" s="13" t="s">
         <v>87</v>
@@ -7335,12 +8415,10 @@
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O10" s="13"/>
-      <c r="P10" s="13" t="s">
-        <v>527</v>
-      </c>
+      <c r="P10" s="13"/>
     </row>
     <row r="11" spans="1:16">
       <c r="B11" s="29"/>
@@ -7350,20 +8428,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>396</v>
+        <v>446</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>397</v>
+        <v>447</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>398</v>
+        <v>448</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>399</v>
+        <v>449</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>87</v>
@@ -7372,14 +8450,12 @@
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>400</v>
-      </c>
-      <c r="P11" s="13" t="s">
-        <v>527</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="P11" s="13"/>
     </row>
     <row r="12" spans="1:16">
       <c r="B12" s="29"/>
@@ -7389,20 +8465,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>401</v>
+        <v>451</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>402</v>
+        <v>452</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>403</v>
+        <v>453</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>404</v>
+        <v>454</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>87</v>
@@ -7411,12 +8487,10 @@
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>526</v>
+        <v>632</v>
       </c>
       <c r="O12" s="13"/>
-      <c r="P12" s="13" t="s">
-        <v>527</v>
-      </c>
+      <c r="P12" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/結合試験仕様書.xlsx
+++ b/結合試験仕様書.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="634">
   <si>
     <t xml:space="preserve">ACTIO（イベント主催・管理サービス）</t>
   </si>
@@ -112,7 +112,7 @@
     <t xml:space="preserve">AI</t>
   </si>
   <si>
-    <t xml:space="preserve">AI を利用した項目に「利用」と記入します。本仕様書では、AI が自動で実施した項目に記入しています。</t>
+    <t xml:space="preserve">AI を利用した項目に「利用」と記入します。本仕様書では、AI のレビューで追記した項目に記入し、備考にも「AIレビューにより追記」と残しています。</t>
   </si>
   <si>
     <t xml:space="preserve">操作</t>
@@ -481,7 +481,10 @@
     <t xml:space="preserve">イベントも申込も削除されず、一覧の件数が変わらない</t>
   </si>
   <si>
-    <t xml:space="preserve">ID: D-04 ／ 誤って押しても実害が出ないことの確認</t>
+    <t xml:space="preserve">ID: D-04 ／ 誤って押しても実害が出ないことの確認 ／ AIレビューにより追記</t>
+  </si>
+  <si>
+    <t xml:space="preserve">利用</t>
   </si>
   <si>
     <t xml:space="preserve">作成をやめると入力内容は保存されない</t>
@@ -496,7 +499,7 @@
     <t xml:space="preserve">下書きも含めてイベントは作られず、一覧の件数が変わらない</t>
   </si>
   <si>
-    <t xml:space="preserve">入力途中で離脱しても残らないことの確認</t>
+    <t xml:space="preserve">入力途中で離脱しても残らないことの確認 ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">終了時刻ちょうどはまだ終了扱いにしない</t>
@@ -511,7 +514,7 @@
     <t xml:space="preserve">上段の「公開中のイベント」に残り、「終了」とは表示されない</t>
   </si>
   <si>
-    <t xml:space="preserve">ID: D-07 ／ 終了と判定するのは終了日時を過ぎたときだけ</t>
+    <t xml:space="preserve">ID: D-07 ／ 終了と判定するのは終了日時を過ぎたときだけ ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">・券種・申込フォーム項目</t>
@@ -658,7 +661,7 @@
     <t xml:space="preserve">「公開するには券種を1件以上登録してください」と表示され、公開されない</t>
   </si>
   <si>
-    <t xml:space="preserve">ID: D-05 ／ 下書きとしてなら保存できる</t>
+    <t xml:space="preserve">ID: D-05 ／ 下書きとしてなら保存できる ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">定員は1と9999で保存できる</t>
@@ -670,7 +673,7 @@
     <t xml:space="preserve">どちらもエラーにならずに保存できる</t>
   </si>
   <si>
-    <t xml:space="preserve">ID: D-22 ／ 受け付けられる下限と上限のちょうど</t>
+    <t xml:space="preserve">ID: D-22 ／ 受け付けられる下限と上限のちょうど ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">カスタム項目と選択肢は上限を超えると追加できない</t>
@@ -682,7 +685,7 @@
     <t xml:space="preserve">「カスタム項目は10件以内で設定してください」「選択肢は10件以内で入力してください」と表示され、追加されない</t>
   </si>
   <si>
-    <t xml:space="preserve">ID: D-28 ／ 上限10件の1つ外側</t>
+    <t xml:space="preserve">ID: D-28 ／ 上限10件の1つ外側 ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">・公開ページ・集客</t>
@@ -814,7 +817,7 @@
     <t xml:space="preserve">ロゴの代わりに組織名の文字だけが表示され、並びが崩れない</t>
   </si>
   <si>
-    <t xml:space="preserve">ID: F-09 ／ ロゴ未設定のときの既定の見え方</t>
+    <t xml:space="preserve">ID: F-09 ／ ロゴ未設定のときの既定の見え方 ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">・申込フロー</t>
@@ -976,7 +979,7 @@
     <t xml:space="preserve">申込は登録されず、受付コードも発行されない。券種の残りも変わらない</t>
   </si>
   <si>
-    <t xml:space="preserve">参加者が入力途中でやめた場合の確認</t>
+    <t xml:space="preserve">参加者が入力途中でやめた場合の確認 ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">マイチケット用パスワードの形式が不正だと申し込めない</t>
@@ -991,7 +994,7 @@
     <t xml:space="preserve">「マイチケット用パスワードは4〜16文字の英数字で入力してください」と表示され、先に進めない</t>
   </si>
   <si>
-    <t xml:space="preserve">ID: D-43</t>
+    <t xml:space="preserve">ID: D-43 ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">・マイチケット</t>
@@ -1291,7 +1294,7 @@
     <t xml:space="preserve">状態は「参加確定」のまま変わらず、券種の残りも変わらない</t>
   </si>
   <si>
-    <t xml:space="preserve">ID: F-13 ／ 誤って押しても実害が出ないことの確認</t>
+    <t xml:space="preserve">ID: F-13 ／ 誤って押しても実害が出ないことの確認 ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">編集をやめると変更は保存されない</t>
@@ -1306,7 +1309,7 @@
     <t xml:space="preserve">どちらの閉じ方でも一覧のメールアドレスは元のままで、保存されていない</t>
   </si>
   <si>
-    <t xml:space="preserve">ID: F-30 ／ Escape キーで閉じた場合も同じ</t>
+    <t xml:space="preserve">ID: F-30 ／ Escape キーで閉じた場合も同じ ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">・ダッシュボード</t>
@@ -1558,7 +1561,7 @@
     <t xml:space="preserve">どれもデータが変わらず、イベントと申込の件数が元のまま</t>
   </si>
   <si>
-    <t xml:space="preserve">初期化は元に戻せないため、取りやめが効くことを必ず確認する</t>
+    <t xml:space="preserve">初期化は元に戻せないため、取りやめが効くことを必ず確認する ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">同じ名前のカテゴリは登録できない</t>
@@ -1570,7 +1573,7 @@
     <t xml:space="preserve">「このカテゴリはすでに登録されています」と表示され、追加されない</t>
   </si>
   <si>
-    <t xml:space="preserve">前後の空白を除いて同じ名前かを判定する</t>
+    <t xml:space="preserve">前後の空白を除いて同じ名前かを判定する ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">カテゴリは21件目を登録できない</t>
@@ -1585,7 +1588,7 @@
     <t xml:space="preserve">「カテゴリは20件以内で登録してください」と表示され、追加されない</t>
   </si>
   <si>
-    <t xml:space="preserve">上限20件の1つ外側</t>
+    <t xml:space="preserve">上限20件の1つ外側 ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">カテゴリが1件もないとイベントを作成できない</t>
@@ -1600,7 +1603,7 @@
     <t xml:space="preserve">「カテゴリが1件も登録されていないため、イベントを作成できません」と出て、設定画面への案内が示される</t>
   </si>
   <si>
-    <t xml:space="preserve">ID: D-12 ／ 分類のないイベントを作らせないため</t>
+    <t xml:space="preserve">ID: D-12 ／ 分類のないイベントを作らせないため ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">パスコードは4〜16文字の英数字以外を受け付けない</t>
@@ -1612,7 +1615,7 @@
     <t xml:space="preserve">「パスコードは4〜16文字の英数字で入力してください」と表示され、変更されない</t>
   </si>
   <si>
-    <t xml:space="preserve">ID: D-33 ／ 下限4文字・上限16文字の1つ外側</t>
+    <t xml:space="preserve">ID: D-33 ／ 下限4文字・上限16文字の1つ外側 ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">・資料・運営体制</t>
@@ -1708,7 +1711,7 @@
     <t xml:space="preserve">キャンセルでは残り、OKで削除される。件数が 2 → 2 → 1 と変わる</t>
   </si>
   <si>
-    <t xml:space="preserve">ID: F-34 ／ 誤って押しても実害が出ないことの確認</t>
+    <t xml:space="preserve">ID: F-34 ／ 誤って押しても実害が出ないことの確認 ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">資料は21件目を登録できない</t>
@@ -1735,7 +1738,7 @@
     <t xml:space="preserve">パネルの表示は元のままで、追加したメンバーは保存されていない</t>
   </si>
   <si>
-    <t xml:space="preserve">ID: F-35</t>
+    <t xml:space="preserve">ID: F-35 ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">・境界値・異常系</t>
@@ -1846,7 +1849,7 @@
     <t xml:space="preserve">いずれも「○○は△文字以内で入力してください」と表示され、保存されない</t>
   </si>
   <si>
-    <t xml:space="preserve">ID: D-11 ／ 参加者情報の編集では入力欄の maxlength で止めている</t>
+    <t xml:space="preserve">ID: D-11 ／ 参加者情報の編集では入力欄の maxlength で止めている ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">メールアドレスと視聴URLの形式が不正だと保存できない</t>
@@ -1861,7 +1864,7 @@
     <t xml:space="preserve">「メールアドレスの形式が正しくありません」「視聴URLの形式が正しくありません」と表示され、先に進めない</t>
   </si>
   <si>
-    <t xml:space="preserve">ID: D-18 / D-31</t>
+    <t xml:space="preserve">ID: D-18 / D-31 ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">正方形の画像でも崩れず表示される</t>
@@ -1876,7 +1879,7 @@
     <t xml:space="preserve">縦横比が保たれ、はみ出しや余白の破綻がない</t>
   </si>
   <si>
-    <t xml:space="preserve">ID: D-15 / D-37 / D-38 ／ 横長の画像（1-9）とあわせて両方で確認する</t>
+    <t xml:space="preserve">ID: D-15 / D-37 / D-38 ／ 横長の画像（1-9）とあわせて両方で確認する ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">画像を含むデータを書き出して読み込むと画像も戻る</t>
@@ -1891,7 +1894,7 @@
     <t xml:space="preserve">カバー画像・組織ロゴ・ヘッダー画像がすべて表示される</t>
   </si>
   <si>
-    <t xml:space="preserve">ID: F-20 ／ 画像は文字列に変換して書き出している</t>
+    <t xml:space="preserve">ID: F-20 ／ 画像は文字列に変換して書き出している ／ AIレビューにより追記</t>
   </si>
   <si>
     <t xml:space="preserve">★ NG項目一覧（試験でNGだった点と対応）</t>
@@ -2760,7 +2763,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2772,7 +2775,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -2783,7 +2786,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -2868,23 +2871,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L8" s="13" t="s">
         <v>87</v>
@@ -2893,10 +2896,10 @@
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -2908,20 +2911,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L9" s="13" t="s">
         <v>87</v>
@@ -2930,10 +2933,10 @@
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -2945,20 +2948,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L10" s="13" t="s">
         <v>87</v>
@@ -2967,10 +2970,10 @@
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -2982,20 +2985,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>87</v>
@@ -3004,10 +3007,10 @@
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -3019,20 +3022,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>87</v>
@@ -3041,10 +3044,10 @@
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -3056,20 +3059,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>87</v>
@@ -3078,10 +3081,10 @@
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -3093,20 +3096,20 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>87</v>
@@ -3115,10 +3118,10 @@
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -3130,20 +3133,20 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>87</v>
@@ -3152,10 +3155,10 @@
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="P15" s="13"/>
     </row>
@@ -3167,20 +3170,20 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>87</v>
@@ -3189,10 +3192,10 @@
         <v>46232</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="P16" s="13"/>
     </row>
@@ -3204,20 +3207,20 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>87</v>
@@ -3226,10 +3229,10 @@
         <v>46232</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P17" s="13"/>
     </row>
@@ -3241,20 +3244,20 @@
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="13" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>87</v>
@@ -3263,12 +3266,14 @@
         <v>46232</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O18" s="13" t="s">
-        <v>512</v>
-      </c>
-      <c r="P18" s="13"/>
+        <v>513</v>
+      </c>
+      <c r="P18" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="19" spans="1:16">
       <c r="B19" s="29"/>
@@ -3278,20 +3283,20 @@
       </c>
       <c r="E19" s="32"/>
       <c r="F19" s="13" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>87</v>
@@ -3300,12 +3305,14 @@
         <v>46232</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O19" s="13" t="s">
-        <v>516</v>
-      </c>
-      <c r="P19" s="13"/>
+        <v>517</v>
+      </c>
+      <c r="P19" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="20" spans="1:16">
       <c r="B20" s="29"/>
@@ -3315,20 +3322,20 @@
       </c>
       <c r="E20" s="32"/>
       <c r="F20" s="13" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G20" s="13"/>
       <c r="H20" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L20" s="13" t="s">
         <v>87</v>
@@ -3337,12 +3344,14 @@
         <v>46232</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O20" s="13" t="s">
-        <v>521</v>
-      </c>
-      <c r="P20" s="13"/>
+        <v>522</v>
+      </c>
+      <c r="P20" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="21" spans="1:16">
       <c r="B21" s="29"/>
@@ -3352,20 +3361,20 @@
       </c>
       <c r="E21" s="32"/>
       <c r="F21" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L21" s="13" t="s">
         <v>87</v>
@@ -3374,12 +3383,14 @@
         <v>46232</v>
       </c>
       <c r="N21" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O21" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="P21" s="13"/>
+        <v>527</v>
+      </c>
+      <c r="P21" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="22" spans="1:16">
       <c r="B22" s="29"/>
@@ -3389,20 +3400,20 @@
       </c>
       <c r="E22" s="32"/>
       <c r="F22" s="13" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>87</v>
@@ -3411,12 +3422,14 @@
         <v>46232</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O22" s="13" t="s">
-        <v>530</v>
-      </c>
-      <c r="P22" s="13"/>
+        <v>531</v>
+      </c>
+      <c r="P22" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3457,7 +3470,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -3469,7 +3482,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -3480,7 +3493,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -3565,23 +3578,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L8" s="13" t="s">
         <v>87</v>
@@ -3590,10 +3603,10 @@
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -3605,20 +3618,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L9" s="13" t="s">
         <v>87</v>
@@ -3627,10 +3640,10 @@
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -3642,20 +3655,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L10" s="13" t="s">
         <v>87</v>
@@ -3664,7 +3677,7 @@
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O10" s="13"/>
       <c r="P10" s="13"/>
@@ -3677,20 +3690,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>87</v>
@@ -3699,10 +3712,10 @@
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -3714,20 +3727,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>87</v>
@@ -3736,10 +3749,10 @@
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -3751,20 +3764,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>87</v>
@@ -3773,12 +3786,14 @@
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>562</v>
-      </c>
-      <c r="P13" s="13"/>
+        <v>563</v>
+      </c>
+      <c r="P13" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="14" spans="1:16">
       <c r="B14" s="29"/>
@@ -3788,20 +3803,20 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>87</v>
@@ -3810,12 +3825,14 @@
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>521</v>
-      </c>
-      <c r="P14" s="13"/>
+        <v>522</v>
+      </c>
+      <c r="P14" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="15" spans="1:16">
       <c r="B15" s="29"/>
@@ -3825,20 +3842,20 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>87</v>
@@ -3847,12 +3864,14 @@
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>571</v>
-      </c>
-      <c r="P15" s="13"/>
+        <v>572</v>
+      </c>
+      <c r="P15" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3893,7 +3912,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -3905,7 +3924,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -3916,7 +3935,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -4001,23 +4020,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L8" s="13" t="s">
         <v>87</v>
@@ -4026,7 +4045,7 @@
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O8" s="13"/>
       <c r="P8" s="13"/>
@@ -4039,20 +4058,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L9" s="13" t="s">
         <v>87</v>
@@ -4061,10 +4080,10 @@
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -4076,20 +4095,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="L10" s="13" t="s">
         <v>87</v>
@@ -4098,10 +4117,10 @@
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -4113,20 +4132,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>87</v>
@@ -4135,10 +4154,10 @@
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -4150,20 +4169,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>87</v>
@@ -4172,10 +4191,10 @@
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -4187,20 +4206,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>87</v>
@@ -4209,10 +4228,10 @@
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -4224,20 +4243,20 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>87</v>
@@ -4246,12 +4265,14 @@
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>608</v>
-      </c>
-      <c r="P14" s="13"/>
+        <v>609</v>
+      </c>
+      <c r="P14" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="15" spans="1:16">
       <c r="B15" s="29"/>
@@ -4261,20 +4282,20 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>87</v>
@@ -4283,12 +4304,14 @@
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>613</v>
-      </c>
-      <c r="P15" s="13"/>
+        <v>614</v>
+      </c>
+      <c r="P15" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="16" spans="1:16">
       <c r="B16" s="29"/>
@@ -4298,20 +4321,20 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>87</v>
@@ -4320,12 +4343,14 @@
         <v>46232</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>618</v>
-      </c>
-      <c r="P16" s="13"/>
+        <v>619</v>
+      </c>
+      <c r="P16" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="17" spans="1:16">
       <c r="B17" s="29"/>
@@ -4335,20 +4360,20 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>87</v>
@@ -4357,12 +4382,14 @@
         <v>46232</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>623</v>
-      </c>
-      <c r="P17" s="13"/>
+        <v>624</v>
+      </c>
+      <c r="P17" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4397,12 +4424,12 @@
   <sheetData>
     <row r="1" spans="1:12" ht="26.5">
       <c r="B1" s="24" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="B2" s="13" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -4410,16 +4437,16 @@
         <v>73</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>17</v>
@@ -4428,10 +4455,10 @@
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
   </sheetData>
@@ -4874,7 +4901,7 @@
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O8" s="13" t="s">
         <v>88</v>
@@ -4911,7 +4938,7 @@
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O9" s="13"/>
       <c r="P9" s="13"/>
@@ -4946,7 +4973,7 @@
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O10" s="13" t="s">
         <v>97</v>
@@ -4983,7 +5010,7 @@
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O11" s="13" t="s">
         <v>101</v>
@@ -5020,7 +5047,7 @@
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O12" s="13" t="s">
         <v>106</v>
@@ -5057,7 +5084,7 @@
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O13" s="13" t="s">
         <v>111</v>
@@ -5094,7 +5121,7 @@
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O14" s="13" t="s">
         <v>115</v>
@@ -5131,7 +5158,7 @@
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O15" s="13" t="s">
         <v>120</v>
@@ -5168,7 +5195,7 @@
         <v>46232</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O16" s="13" t="s">
         <v>125</v>
@@ -5205,7 +5232,7 @@
         <v>46232</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O17" s="13" t="s">
         <v>130</v>
@@ -5242,7 +5269,7 @@
         <v>46232</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O18" s="13" t="s">
         <v>135</v>
@@ -5279,7 +5306,7 @@
         <v>46232</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O19" s="13" t="s">
         <v>139</v>
@@ -5316,7 +5343,7 @@
         <v>46232</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O20" s="13" t="s">
         <v>144</v>
@@ -5353,7 +5380,7 @@
         <v>46232</v>
       </c>
       <c r="N21" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O21" s="13" t="s">
         <v>149</v>
@@ -5390,12 +5417,14 @@
         <v>46232</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O22" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="P22" s="13"/>
+      <c r="P22" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="23" spans="1:16">
       <c r="B23" s="29"/>
@@ -5405,20 +5434,20 @@
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G23" s="13"/>
       <c r="H23" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L23" s="13" t="s">
         <v>87</v>
@@ -5427,12 +5456,14 @@
         <v>46232</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O23" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="P23" s="13"/>
+        <v>159</v>
+      </c>
+      <c r="P23" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="24" spans="1:16">
       <c r="B24" s="29"/>
@@ -5442,20 +5473,20 @@
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G24" s="13"/>
       <c r="H24" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L24" s="13" t="s">
         <v>87</v>
@@ -5464,12 +5495,14 @@
         <v>46232</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O24" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="P24" s="13"/>
+        <v>164</v>
+      </c>
+      <c r="P24" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -5510,7 +5543,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -5522,7 +5555,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -5533,7 +5566,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -5618,23 +5651,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L8" s="13" t="s">
         <v>87</v>
@@ -5643,10 +5676,10 @@
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -5658,20 +5691,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L9" s="13" t="s">
         <v>87</v>
@@ -5680,10 +5713,10 @@
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -5695,20 +5728,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L10" s="13" t="s">
         <v>87</v>
@@ -5717,10 +5750,10 @@
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -5732,20 +5765,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>87</v>
@@ -5754,10 +5787,10 @@
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -5769,20 +5802,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>87</v>
@@ -5791,10 +5824,10 @@
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -5806,20 +5839,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>87</v>
@@ -5828,10 +5861,10 @@
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -5843,20 +5876,20 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>87</v>
@@ -5865,10 +5898,10 @@
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -5880,20 +5913,20 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>87</v>
@@ -5902,10 +5935,10 @@
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P15" s="13"/>
     </row>
@@ -5917,20 +5950,20 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>87</v>
@@ -5939,10 +5972,10 @@
         <v>46232</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P16" s="13"/>
     </row>
@@ -5954,20 +5987,20 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>87</v>
@@ -5976,12 +6009,14 @@
         <v>46232</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="P17" s="13"/>
+        <v>213</v>
+      </c>
+      <c r="P17" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="18" spans="1:16">
       <c r="B18" s="29"/>
@@ -5991,20 +6026,20 @@
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>87</v>
@@ -6013,12 +6048,14 @@
         <v>46232</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O18" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="P18" s="13"/>
+        <v>217</v>
+      </c>
+      <c r="P18" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="19" spans="1:16">
       <c r="B19" s="29"/>
@@ -6028,20 +6065,20 @@
       </c>
       <c r="E19" s="32"/>
       <c r="F19" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>87</v>
@@ -6050,12 +6087,14 @@
         <v>46232</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O19" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="P19" s="13"/>
+        <v>221</v>
+      </c>
+      <c r="P19" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -6096,7 +6135,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -6108,7 +6147,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -6119,7 +6158,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -6204,23 +6243,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L8" s="13" t="s">
         <v>87</v>
@@ -6229,10 +6268,10 @@
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -6244,20 +6283,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L9" s="13" t="s">
         <v>87</v>
@@ -6266,10 +6305,10 @@
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -6281,20 +6320,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L10" s="13" t="s">
         <v>87</v>
@@ -6303,10 +6342,10 @@
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -6318,20 +6357,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>87</v>
@@ -6340,7 +6379,7 @@
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O11" s="13"/>
       <c r="P11" s="13"/>
@@ -6353,20 +6392,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>87</v>
@@ -6375,10 +6414,10 @@
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -6390,20 +6429,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>87</v>
@@ -6412,7 +6451,7 @@
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O13" s="13"/>
       <c r="P13" s="13"/>
@@ -6425,20 +6464,20 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>87</v>
@@ -6447,10 +6486,10 @@
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -6462,20 +6501,20 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
         <v>43</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>87</v>
@@ -6484,10 +6523,10 @@
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P15" s="13"/>
     </row>
@@ -6499,20 +6538,20 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>87</v>
@@ -6521,12 +6560,14 @@
         <v>46232</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="P16" s="13"/>
+        <v>265</v>
+      </c>
+      <c r="P16" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -6567,7 +6608,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -6579,7 +6620,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -6590,7 +6631,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -6675,23 +6716,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L8" s="13" t="s">
         <v>87</v>
@@ -6700,10 +6741,10 @@
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -6715,20 +6756,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L9" s="13" t="s">
         <v>87</v>
@@ -6737,10 +6778,10 @@
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -6752,20 +6793,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L10" s="13" t="s">
         <v>87</v>
@@ -6774,10 +6815,10 @@
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -6789,20 +6830,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>87</v>
@@ -6811,7 +6852,7 @@
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O11" s="13"/>
       <c r="P11" s="13"/>
@@ -6824,20 +6865,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>87</v>
@@ -6846,10 +6887,10 @@
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -6861,20 +6902,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>87</v>
@@ -6883,10 +6924,10 @@
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -6898,20 +6939,20 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>87</v>
@@ -6920,10 +6961,10 @@
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -6935,20 +6976,20 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>87</v>
@@ -6957,10 +6998,10 @@
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P15" s="13"/>
     </row>
@@ -6972,20 +7013,20 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>87</v>
@@ -6994,10 +7035,10 @@
         <v>46232</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P16" s="13"/>
     </row>
@@ -7009,20 +7050,20 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>87</v>
@@ -7031,10 +7072,10 @@
         <v>46232</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P17" s="13"/>
     </row>
@@ -7046,20 +7087,20 @@
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="13" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>87</v>
@@ -7068,12 +7109,14 @@
         <v>46232</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O18" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="P18" s="13"/>
+        <v>319</v>
+      </c>
+      <c r="P18" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="19" spans="1:16">
       <c r="B19" s="29"/>
@@ -7083,20 +7126,20 @@
       </c>
       <c r="E19" s="32"/>
       <c r="F19" s="13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>87</v>
@@ -7105,12 +7148,14 @@
         <v>46232</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O19" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="P19" s="13"/>
+        <v>324</v>
+      </c>
+      <c r="P19" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -7151,7 +7196,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -7163,7 +7208,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -7174,7 +7219,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -7262,20 +7307,20 @@
         <v>56</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L8" s="13" t="s">
         <v>87</v>
@@ -7284,10 +7329,10 @@
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -7299,20 +7344,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L9" s="13" t="s">
         <v>87</v>
@@ -7321,7 +7366,7 @@
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O9" s="13"/>
       <c r="P9" s="13"/>
@@ -7334,20 +7379,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L10" s="13" t="s">
         <v>87</v>
@@ -7356,10 +7401,10 @@
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -7371,20 +7416,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>87</v>
@@ -7393,10 +7438,10 @@
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -7408,20 +7453,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>87</v>
@@ -7430,7 +7475,7 @@
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O12" s="13"/>
       <c r="P12" s="13"/>
@@ -7443,20 +7488,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>87</v>
@@ -7465,10 +7510,10 @@
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -7511,7 +7556,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -7523,7 +7568,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -7534,7 +7579,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -7619,23 +7664,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L8" s="13" t="s">
         <v>87</v>
@@ -7644,10 +7689,10 @@
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -7659,20 +7704,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L9" s="13" t="s">
         <v>87</v>
@@ -7681,10 +7726,10 @@
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -7696,20 +7741,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L10" s="13" t="s">
         <v>87</v>
@@ -7718,10 +7763,10 @@
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -7733,20 +7778,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>87</v>
@@ -7755,10 +7800,10 @@
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -7770,20 +7815,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>87</v>
@@ -7792,10 +7837,10 @@
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -7807,20 +7852,20 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>87</v>
@@ -7829,10 +7874,10 @@
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -7844,20 +7889,20 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>87</v>
@@ -7866,10 +7911,10 @@
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -7881,20 +7926,20 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>87</v>
@@ -7903,10 +7948,10 @@
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P15" s="13"/>
     </row>
@@ -7918,20 +7963,20 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>87</v>
@@ -7940,10 +7985,10 @@
         <v>46232</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P16" s="13"/>
     </row>
@@ -7955,20 +8000,20 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>87</v>
@@ -7977,10 +8022,10 @@
         <v>46232</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P17" s="13"/>
     </row>
@@ -7992,20 +8037,20 @@
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="13" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>87</v>
@@ -8014,10 +8059,10 @@
         <v>46232</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O18" s="13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P18" s="13"/>
     </row>
@@ -8029,20 +8074,20 @@
       </c>
       <c r="E19" s="32"/>
       <c r="F19" s="13" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>87</v>
@@ -8051,10 +8096,10 @@
         <v>46232</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O19" s="13" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P19" s="13"/>
     </row>
@@ -8066,20 +8111,20 @@
       </c>
       <c r="E20" s="32"/>
       <c r="F20" s="13" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G20" s="13"/>
       <c r="H20" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L20" s="13" t="s">
         <v>87</v>
@@ -8088,10 +8133,10 @@
         <v>46232</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O20" s="13" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P20" s="13"/>
     </row>
@@ -8103,20 +8148,20 @@
       </c>
       <c r="E21" s="32"/>
       <c r="F21" s="13" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L21" s="13" t="s">
         <v>87</v>
@@ -8125,12 +8170,14 @@
         <v>46232</v>
       </c>
       <c r="N21" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O21" s="13" t="s">
-        <v>423</v>
-      </c>
-      <c r="P21" s="13"/>
+        <v>424</v>
+      </c>
+      <c r="P21" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="22" spans="1:16">
       <c r="B22" s="29"/>
@@ -8140,20 +8187,20 @@
       </c>
       <c r="E22" s="32"/>
       <c r="F22" s="13" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>87</v>
@@ -8162,12 +8209,14 @@
         <v>46232</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O22" s="13" t="s">
-        <v>428</v>
-      </c>
-      <c r="P22" s="13"/>
+        <v>429</v>
+      </c>
+      <c r="P22" s="13" t="s">
+        <v>154</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -8208,7 +8257,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -8220,7 +8269,7 @@
         <v>68</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -8231,7 +8280,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -8316,23 +8365,23 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L8" s="13" t="s">
         <v>87</v>
@@ -8341,10 +8390,10 @@
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -8356,20 +8405,20 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L9" s="13" t="s">
         <v>87</v>
@@ -8378,10 +8427,10 @@
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -8393,20 +8442,20 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L10" s="13" t="s">
         <v>87</v>
@@ -8415,7 +8464,7 @@
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O10" s="13"/>
       <c r="P10" s="13"/>
@@ -8428,20 +8477,20 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>87</v>
@@ -8450,10 +8499,10 @@
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -8465,20 +8514,20 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>87</v>
@@ -8487,7 +8536,7 @@
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O12" s="13"/>
       <c r="P12" s="13"/>

--- a/結合試験仕様書.xlsx
+++ b/結合試験仕様書.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="641">
   <si>
     <t xml:space="preserve">ACTIO（イベント主催・管理サービス）</t>
   </si>
@@ -31,12 +31,15 @@
     <t xml:space="preserve">対象: index.html（単一ファイル・file:// 起動）</t>
   </si>
   <si>
-    <t xml:space="preserve">試験項目: 全109項目（大項目10）</t>
+    <t xml:space="preserve">試験項目: 全110項目（大項目10）</t>
   </si>
   <si>
     <t xml:space="preserve">動作保証: Google Chrome のみ</t>
   </si>
   <si>
+    <t xml:space="preserve">うち未実施: 1項目（QRコードをカメラで読み取って受付できる）</t>
+  </si>
+  <si>
     <t xml:space="preserve">日本コムシンク株式会社</t>
   </si>
   <si>
@@ -97,10 +100,10 @@
     <t xml:space="preserve">操作後に「こうなっていれば正しい」という状態。</t>
   </si>
   <si>
-    <t xml:space="preserve">結果（〇 / ×）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">〇＝期待どおり動いた。×＝期待どおりにならなかった（不具合）。×はNG項目一覧に転記します。</t>
+    <t xml:space="preserve">結果（〇 / × / 未実施）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">〇＝期待どおり動いた。×＝期待どおりにならなかった（不具合）。×はNG項目一覧に転記します。未実施＝本来やるべき項目だが、今回の期間内では実施できなかったもの。理由は備考に「【今回は未実施】」として記載しています。</t>
   </si>
   <si>
     <t xml:space="preserve">備考</t>
@@ -1123,7 +1126,7 @@
     <t xml:space="preserve">どれを入力しても、該当する参加者だけに絞られる</t>
   </si>
   <si>
-    <t xml:space="preserve">ID: F-15 ／ 当日の受付は、この検索に受付コードを入れて行う</t>
+    <t xml:space="preserve">ID: F-15 ／ 当日の受付は、この検索に受付コードを入れて行う。カメラでQRコードを読み取って受付する方法は今回未実施（この大項目の最後の項目を参照）</t>
   </si>
   <si>
     <t xml:space="preserve">参加者一覧のページを送れる</t>
@@ -1310,6 +1313,24 @@
   </si>
   <si>
     <t xml:space="preserve">ID: F-30 ／ Escape キーで閉じた場合も同じ ／ AIレビューにより追記</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QRコードをカメラで読み取って受付できる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">まだ受付していない参加者がいて、その参加者のマイチケットにQRコードが表示されている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参加者一覧からカメラを起動し、参加者のQRコードを読み取る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">読み取った受付コードから参加者が特定され、状態が「申し込み済み」から「参加確定」に変わり、受付した日時が記録される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未実施</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-24 ／ 【今回は未実施】当日の受付は本来この方法で行うべき項目だが、index.html をダブルクリックして file:// で開く形ではカメラを使う仕組みが動かないため、今回はこの機能の実装まで至らず、試験も実施できていない。今回の受付は、受付コードを検索して「受付」を押す方法で代替している</t>
   </si>
   <si>
     <t xml:space="preserve">・ダッシュボード</t>
@@ -2682,8 +2703,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
-      <c r="A17" s="8"/>
+    <row r="17" spans="1:12" ht="23" customHeight="1">
+      <c r="A17" s="8" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="8"/>
@@ -2720,12 +2743,12 @@
     </row>
     <row r="29" spans="1:12" ht="23" customHeight="1">
       <c r="A29" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="23" customHeight="1">
       <c r="A30" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2763,7 +2786,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2772,10 +2795,10 @@
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -2783,10 +2806,10 @@
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -2794,7 +2817,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -2806,7 +2829,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="27"/>
       <c r="L6" s="25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
@@ -2815,49 +2838,49 @@
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2871,35 +2894,35 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M8" s="2">
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -2911,32 +2934,32 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M9" s="2">
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -2948,32 +2971,32 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M10" s="2">
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -2985,32 +3008,32 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M11" s="2">
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -3022,32 +3045,32 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M12" s="2">
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -3059,32 +3082,32 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M13" s="2">
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -3096,32 +3119,32 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M14" s="2">
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -3133,32 +3156,32 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M15" s="2">
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="P15" s="13"/>
     </row>
@@ -3170,32 +3193,32 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M16" s="2">
         <v>46232</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="P16" s="13"/>
     </row>
@@ -3207,32 +3230,32 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M17" s="2">
         <v>46232</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="P17" s="13"/>
     </row>
@@ -3244,35 +3267,35 @@
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="13" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M18" s="2">
         <v>46232</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O18" s="13" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="P18" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -3283,35 +3306,35 @@
       </c>
       <c r="E19" s="32"/>
       <c r="F19" s="13" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M19" s="2">
         <v>46232</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O19" s="13" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="P19" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -3322,35 +3345,35 @@
       </c>
       <c r="E20" s="32"/>
       <c r="F20" s="13" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="G20" s="13"/>
       <c r="H20" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M20" s="2">
         <v>46232</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O20" s="13" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="P20" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -3361,35 +3384,35 @@
       </c>
       <c r="E21" s="32"/>
       <c r="F21" s="13" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="L21" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M21" s="2">
         <v>46232</v>
       </c>
       <c r="N21" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O21" s="13" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="P21" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -3400,35 +3423,35 @@
       </c>
       <c r="E22" s="32"/>
       <c r="F22" s="13" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M22" s="2">
         <v>46232</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O22" s="13" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="P22" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -3470,7 +3493,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -3479,10 +3502,10 @@
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -3490,10 +3513,10 @@
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -3501,7 +3524,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -3513,7 +3536,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="27"/>
       <c r="L6" s="25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
@@ -3522,49 +3545,49 @@
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -3578,35 +3601,35 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M8" s="2">
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -3618,32 +3641,32 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M9" s="2">
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -3655,29 +3678,29 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M10" s="2">
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O10" s="13"/>
       <c r="P10" s="13"/>
@@ -3690,32 +3713,32 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M11" s="2">
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -3727,32 +3750,32 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M12" s="2">
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -3764,35 +3787,35 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M13" s="2">
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="P13" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -3803,35 +3826,35 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M14" s="2">
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -3842,35 +3865,35 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M15" s="2">
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="P15" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -3912,7 +3935,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -3921,10 +3944,10 @@
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -3932,10 +3955,10 @@
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -3943,7 +3966,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -3955,7 +3978,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="27"/>
       <c r="L6" s="25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
@@ -3964,49 +3987,49 @@
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -4020,32 +4043,32 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M8" s="2">
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O8" s="13"/>
       <c r="P8" s="13"/>
@@ -4058,32 +4081,32 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M9" s="2">
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -4095,32 +4118,32 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M10" s="2">
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -4132,32 +4155,32 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M11" s="2">
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -4169,32 +4192,32 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M12" s="2">
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -4206,32 +4229,32 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M13" s="2">
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -4243,35 +4266,35 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M14" s="2">
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -4282,35 +4305,35 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M15" s="2">
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="P15" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -4321,35 +4344,35 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M16" s="2">
         <v>46232</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -4360,35 +4383,35 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M17" s="2">
         <v>46232</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="P17" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -4424,41 +4447,41 @@
   <sheetData>
     <row r="1" spans="1:12" ht="26.5">
       <c r="B1" s="24" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="B2" s="13" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>
@@ -4478,265 +4501,265 @@
   <sheetData>
     <row r="1" spans="1:12" ht="26.5">
       <c r="B1" s="24" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="B2" s="13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="13"/>
       <c r="C6" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="B7" s="13"/>
       <c r="C7" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="B8" s="13"/>
       <c r="C8" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" s="13"/>
       <c r="C9" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="13"/>
       <c r="C10" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" s="13"/>
       <c r="C11" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="B12" s="13"/>
       <c r="C12" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" s="13"/>
       <c r="C13" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="B14" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="B15" s="13"/>
       <c r="C15" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="B16" s="13"/>
       <c r="C16" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="B17" s="13"/>
       <c r="C17" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="B18" s="13"/>
       <c r="C18" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="B19" s="13"/>
       <c r="C19" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="B20" s="13"/>
       <c r="C20" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="B21" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="B22" s="13"/>
       <c r="C22" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="B23" s="13"/>
       <c r="C23" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="B24" s="13"/>
       <c r="C24" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="B25" s="13"/>
       <c r="C25" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="B26" s="13"/>
       <c r="C26" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="B27" s="13"/>
       <c r="C27" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="B28" s="13"/>
       <c r="C28" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="B29" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="B30" s="13"/>
       <c r="C30" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -4768,7 +4791,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -4777,10 +4800,10 @@
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -4788,10 +4811,10 @@
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -4799,7 +4822,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -4811,7 +4834,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="27"/>
       <c r="L6" s="25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
@@ -4820,49 +4843,49 @@
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -4876,35 +4899,35 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M8" s="2">
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -4916,29 +4939,29 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M9" s="2">
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O9" s="13"/>
       <c r="P9" s="13"/>
@@ -4951,32 +4974,32 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M10" s="2">
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -4988,32 +5011,32 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M11" s="2">
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -5025,32 +5048,32 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M12" s="2">
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -5062,32 +5085,32 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M13" s="2">
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -5099,32 +5122,32 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M14" s="2">
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -5136,32 +5159,32 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M15" s="2">
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P15" s="13"/>
     </row>
@@ -5173,32 +5196,32 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M16" s="2">
         <v>46232</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P16" s="13"/>
     </row>
@@ -5210,32 +5233,32 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M17" s="2">
         <v>46232</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P17" s="13"/>
     </row>
@@ -5247,32 +5270,32 @@
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M18" s="2">
         <v>46232</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O18" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P18" s="13"/>
     </row>
@@ -5284,32 +5307,32 @@
       </c>
       <c r="E19" s="32"/>
       <c r="F19" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M19" s="2">
         <v>46232</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O19" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P19" s="13"/>
     </row>
@@ -5321,32 +5344,32 @@
       </c>
       <c r="E20" s="32"/>
       <c r="F20" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G20" s="13"/>
       <c r="H20" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M20" s="2">
         <v>46232</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O20" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P20" s="13"/>
     </row>
@@ -5358,32 +5381,32 @@
       </c>
       <c r="E21" s="32"/>
       <c r="F21" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L21" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M21" s="2">
         <v>46232</v>
       </c>
       <c r="N21" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O21" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P21" s="13"/>
     </row>
@@ -5395,35 +5418,35 @@
       </c>
       <c r="E22" s="32"/>
       <c r="F22" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M22" s="2">
         <v>46232</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O22" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P22" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -5434,35 +5457,35 @@
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G23" s="13"/>
       <c r="H23" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M23" s="2">
         <v>46232</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O23" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P23" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -5473,35 +5496,35 @@
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G24" s="13"/>
       <c r="H24" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M24" s="2">
         <v>46232</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O24" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P24" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -5543,7 +5566,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -5552,10 +5575,10 @@
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -5563,10 +5586,10 @@
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -5574,7 +5597,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -5586,7 +5609,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="27"/>
       <c r="L6" s="25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
@@ -5595,49 +5618,49 @@
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -5651,35 +5674,35 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M8" s="2">
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -5691,32 +5714,32 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M9" s="2">
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -5728,32 +5751,32 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M10" s="2">
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -5765,32 +5788,32 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M11" s="2">
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -5802,32 +5825,32 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M12" s="2">
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -5839,32 +5862,32 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M13" s="2">
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -5876,32 +5899,32 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M14" s="2">
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -5913,32 +5936,32 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M15" s="2">
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P15" s="13"/>
     </row>
@@ -5950,32 +5973,32 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M16" s="2">
         <v>46232</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P16" s="13"/>
     </row>
@@ -5987,35 +6010,35 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M17" s="2">
         <v>46232</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P17" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -6026,35 +6049,35 @@
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M18" s="2">
         <v>46232</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O18" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P18" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -6065,35 +6088,35 @@
       </c>
       <c r="E19" s="32"/>
       <c r="F19" s="13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M19" s="2">
         <v>46232</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O19" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P19" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -6135,7 +6158,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -6144,10 +6167,10 @@
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -6155,10 +6178,10 @@
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -6166,7 +6189,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -6178,7 +6201,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="27"/>
       <c r="L6" s="25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
@@ -6187,49 +6210,49 @@
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -6243,35 +6266,35 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M8" s="2">
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -6283,32 +6306,32 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M9" s="2">
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -6320,32 +6343,32 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M10" s="2">
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -6357,29 +6380,29 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M11" s="2">
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O11" s="13"/>
       <c r="P11" s="13"/>
@@ -6392,32 +6415,32 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M12" s="2">
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -6429,29 +6452,29 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M13" s="2">
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O13" s="13"/>
       <c r="P13" s="13"/>
@@ -6464,32 +6487,32 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M14" s="2">
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -6501,32 +6524,32 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M15" s="2">
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P15" s="13"/>
     </row>
@@ -6538,35 +6561,35 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M16" s="2">
         <v>46232</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -6608,7 +6631,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -6617,10 +6640,10 @@
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -6628,10 +6651,10 @@
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -6639,7 +6662,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -6651,7 +6674,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="27"/>
       <c r="L6" s="25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
@@ -6660,49 +6683,49 @@
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -6716,35 +6739,35 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M8" s="2">
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -6756,32 +6779,32 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M9" s="2">
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -6793,32 +6816,32 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M10" s="2">
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -6830,29 +6853,29 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M11" s="2">
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O11" s="13"/>
       <c r="P11" s="13"/>
@@ -6865,32 +6888,32 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M12" s="2">
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -6902,32 +6925,32 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M13" s="2">
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -6939,32 +6962,32 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M14" s="2">
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -6976,32 +6999,32 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M15" s="2">
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P15" s="13"/>
     </row>
@@ -7013,32 +7036,32 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M16" s="2">
         <v>46232</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P16" s="13"/>
     </row>
@@ -7050,32 +7073,32 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M17" s="2">
         <v>46232</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P17" s="13"/>
     </row>
@@ -7087,35 +7110,35 @@
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="13" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M18" s="2">
         <v>46232</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O18" s="13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P18" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -7126,35 +7149,35 @@
       </c>
       <c r="E19" s="32"/>
       <c r="F19" s="13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M19" s="2">
         <v>46232</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O19" s="13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P19" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -7196,7 +7219,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -7205,10 +7228,10 @@
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -7216,10 +7239,10 @@
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -7227,7 +7250,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -7239,7 +7262,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="27"/>
       <c r="L6" s="25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
@@ -7248,49 +7271,49 @@
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -7304,35 +7327,35 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M8" s="2">
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -7344,29 +7367,29 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M9" s="2">
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O9" s="13"/>
       <c r="P9" s="13"/>
@@ -7379,32 +7402,32 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M10" s="2">
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -7416,32 +7439,32 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M11" s="2">
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -7453,29 +7476,29 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M12" s="2">
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O12" s="13"/>
       <c r="P12" s="13"/>
@@ -7488,32 +7511,32 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M13" s="2">
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -7534,7 +7557,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="5.9140625" style="17" customWidth="1"/>
@@ -7556,7 +7579,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -7565,10 +7588,10 @@
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -7576,10 +7599,10 @@
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -7587,7 +7610,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -7599,7 +7622,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="27"/>
       <c r="L6" s="25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
@@ -7608,49 +7631,49 @@
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -7664,35 +7687,35 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M8" s="2">
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -7704,32 +7727,32 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M9" s="2">
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -7741,32 +7764,32 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M10" s="2">
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P10" s="13"/>
     </row>
@@ -7778,32 +7801,32 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M11" s="2">
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -7815,32 +7838,32 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M12" s="2">
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P12" s="13"/>
     </row>
@@ -7852,32 +7875,32 @@
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="13" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M13" s="2">
         <v>46232</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P13" s="13"/>
     </row>
@@ -7889,32 +7912,32 @@
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="13" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M14" s="2">
         <v>46232</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P14" s="13"/>
     </row>
@@ -7926,32 +7949,32 @@
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="13" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M15" s="2">
         <v>46232</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P15" s="13"/>
     </row>
@@ -7963,32 +7986,32 @@
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="13" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M16" s="2">
         <v>46232</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P16" s="13"/>
     </row>
@@ -8000,32 +8023,32 @@
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="13" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M17" s="2">
         <v>46232</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P17" s="13"/>
     </row>
@@ -8037,32 +8060,32 @@
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M18" s="2">
         <v>46232</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O18" s="13" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P18" s="13"/>
     </row>
@@ -8074,32 +8097,32 @@
       </c>
       <c r="E19" s="32"/>
       <c r="F19" s="13" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M19" s="2">
         <v>46232</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O19" s="13" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P19" s="13"/>
     </row>
@@ -8111,32 +8134,32 @@
       </c>
       <c r="E20" s="32"/>
       <c r="F20" s="13" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G20" s="13"/>
       <c r="H20" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M20" s="2">
         <v>46232</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O20" s="13" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P20" s="13"/>
     </row>
@@ -8148,35 +8171,35 @@
       </c>
       <c r="E21" s="32"/>
       <c r="F21" s="13" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L21" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M21" s="2">
         <v>46232</v>
       </c>
       <c r="N21" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O21" s="13" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P21" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -8187,36 +8210,71 @@
       </c>
       <c r="E22" s="32"/>
       <c r="F22" s="13" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M22" s="2">
         <v>46232</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O22" s="13" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P22" s="13" t="s">
-        <v>154</v>
-      </c>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="22">
+        <v>16</v>
+      </c>
+      <c r="E23" s="32"/>
+      <c r="F23" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>434</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="M23" s="2"/>
+      <c r="N23" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="O23" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="P23" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -8225,9 +8283,9 @@
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="L6:P6"/>
-    <mergeCell ref="B8:B22"/>
-    <mergeCell ref="C8:C22"/>
-    <mergeCell ref="E8:E22"/>
+    <mergeCell ref="B8:B23"/>
+    <mergeCell ref="C8:C23"/>
+    <mergeCell ref="E8:E23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8257,7 +8315,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.5">
       <c r="A1" s="24" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -8266,10 +8324,10 @@
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
@@ -8277,10 +8335,10 @@
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1">
       <c r="B4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
@@ -8288,7 +8346,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -8300,7 +8358,7 @@
       <c r="J6" s="26"/>
       <c r="K6" s="27"/>
       <c r="L6" s="25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="26"/>
@@ -8309,49 +8367,49 @@
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -8365,35 +8423,35 @@
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M8" s="2">
         <v>46232</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="P8" s="13"/>
     </row>
@@ -8405,32 +8463,32 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="13" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M9" s="2">
         <v>46232</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="P9" s="13"/>
     </row>
@@ -8442,29 +8500,29 @@
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="13" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M10" s="2">
         <v>46232</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O10" s="13"/>
       <c r="P10" s="13"/>
@@ -8477,32 +8535,32 @@
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="13" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M11" s="2">
         <v>46232</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="P11" s="13"/>
     </row>
@@ -8514,29 +8572,29 @@
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="13" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M12" s="2">
         <v>46232</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="O12" s="13"/>
       <c r="P12" s="13"/>

--- a/結合試験仕様書.xlsx
+++ b/結合試験仕様書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mihara\projects\event-management-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65A5256-2349-4317-A3B2-CDE98DA79929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4AD352-5DAF-4912-9229-9AAF2C3BCBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="658">
   <si>
     <t>ACTIO（イベント主催・管理サービス）</t>
   </si>
@@ -1968,10 +1968,6 @@
   </si>
   <si>
     <t>テスト内容</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>NG</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2064,6 +2060,31 @@
       <t>シュウセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG(修正済み)</t>
+    <rPh sb="3" eb="6">
+      <t>シュウセイズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">うち対象外: 1項目（QRコードをカメラで読み取って受付できる）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">結果（〇 / × / 対象外）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">〇＝期待どおり動いた。×＝期待どおりにならなかった（不具合）。×はNG項目一覧に転記します。対象外＝この構成では実現できないため、試験の対象としないもの。理由は備考に「【対象外】」として記載しています。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-15 ／ 当日の受付は、この検索に受付コードを入れて行う。カメラでQRコードを読み取って受付する方法は対象外（この大項目の最後の項目を参照）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">対象外</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: F-24 ／ 【対象外】① index.html をダブルクリックして file:// で開く形はセキュアコンテキストではないため、カメラを起動する仕組み（getUserMedia）が使えない。これはページの開き方による制約であり、PC・スマートフォンのどちらのカメラでも同じ。② 読み取り側の自前実装は画像の二値化・傾きの補正・パターン検出を要し、外部ライブラリを使わない前提では工数に見合わない。受付は明細2の受付コード検索で行う（仕様書 8章・機能一覧「対象外」の一覧と対応）</t>
   </si>
 </sst>
 </file>
@@ -2166,7 +2187,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2193,41 +2214,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top/>
       <bottom/>
@@ -2239,7 +2225,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2277,32 +2263,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2313,13 +2273,31 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2661,25 +2639,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="23"/>
+      <c r="A1" s="13"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="23"/>
+      <c r="A2" s="13"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="23"/>
+      <c r="A3" s="13"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="23"/>
+      <c r="A4" s="13"/>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="23"/>
+      <c r="A5" s="13"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="23"/>
+      <c r="A6" s="13"/>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="23"/>
+      <c r="A7" s="13"/>
     </row>
     <row r="8" spans="1:1" ht="23" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="7" t="s">
@@ -2687,13 +2665,13 @@
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="23"/>
+      <c r="A9" s="13"/>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="23"/>
+      <c r="A10" s="13"/>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="23"/>
+      <c r="A11" s="13"/>
     </row>
     <row r="12" spans="1:1" ht="23" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="6" t="s">
@@ -2701,68 +2679,68 @@
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="23"/>
+      <c r="A13" s="13"/>
     </row>
     <row r="14" spans="1:1" ht="23" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="13" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="23" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="13" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="23" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="13" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="23" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="23" t="s">
-        <v>5</v>
+      <c r="A17" s="13" t="s">
+        <v>652</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="23"/>
+      <c r="A18" s="13"/>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="23"/>
+      <c r="A19" s="13"/>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="23"/>
+      <c r="A20" s="13"/>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="23"/>
+      <c r="A21" s="13"/>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="23"/>
+      <c r="A22" s="13"/>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="23"/>
+      <c r="A23" s="13"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="23"/>
+      <c r="A24" s="13"/>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="23"/>
+      <c r="A25" s="13"/>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="23"/>
+      <c r="A26" s="13"/>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="23"/>
+      <c r="A27" s="13"/>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="23"/>
+      <c r="A28" s="13"/>
     </row>
     <row r="29" spans="1:1" ht="23" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="13" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="23" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="13" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2801,56 +2779,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="26.5" x14ac:dyDescent="0.8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="21" t="s">
         <v>463</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="22" t="s">
         <v>464</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="22" t="s">
         <v>465</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="18" t="s">
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="17"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
@@ -2909,7 +2887,7 @@
       <c r="D8" s="11">
         <v>1</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="20" t="s">
         <v>466</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -2928,13 +2906,13 @@
       <c r="K8" s="8" t="s">
         <v>470</v>
       </c>
-      <c r="L8" s="24" t="s">
+      <c r="L8" s="14" t="s">
         <v>88</v>
       </c>
       <c r="M8" s="2">
         <v>46232</v>
       </c>
-      <c r="N8" s="24" t="s">
+      <c r="N8" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O8" s="8" t="s">
@@ -2943,12 +2921,12 @@
       <c r="P8" s="8"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
       <c r="D9" s="11">
         <v>2</v>
       </c>
-      <c r="E9" s="22"/>
+      <c r="E9" s="20"/>
       <c r="F9" s="8" t="s">
         <v>472</v>
       </c>
@@ -2965,13 +2943,13 @@
       <c r="K9" s="8" t="s">
         <v>475</v>
       </c>
-      <c r="L9" s="24" t="s">
+      <c r="L9" s="14" t="s">
         <v>88</v>
       </c>
       <c r="M9" s="2">
         <v>46232</v>
       </c>
-      <c r="N9" s="24" t="s">
+      <c r="N9" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O9" s="8" t="s">
@@ -2980,12 +2958,12 @@
       <c r="P9" s="8"/>
     </row>
     <row r="10" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
       <c r="D10" s="11">
         <v>3</v>
       </c>
-      <c r="E10" s="22"/>
+      <c r="E10" s="20"/>
       <c r="F10" s="8" t="s">
         <v>477</v>
       </c>
@@ -3002,13 +2980,13 @@
       <c r="K10" s="8" t="s">
         <v>480</v>
       </c>
-      <c r="L10" s="24" t="s">
+      <c r="L10" s="14" t="s">
         <v>88</v>
       </c>
       <c r="M10" s="2">
         <v>46233</v>
       </c>
-      <c r="N10" s="24" t="s">
+      <c r="N10" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O10" s="8" t="s">
@@ -3017,12 +2995,12 @@
       <c r="P10" s="8"/>
     </row>
     <row r="11" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
       <c r="D11" s="11">
         <v>4</v>
       </c>
-      <c r="E11" s="22"/>
+      <c r="E11" s="20"/>
       <c r="F11" s="8" t="s">
         <v>482</v>
       </c>
@@ -3039,13 +3017,13 @@
       <c r="K11" s="8" t="s">
         <v>485</v>
       </c>
-      <c r="L11" s="24" t="s">
+      <c r="L11" s="14" t="s">
         <v>88</v>
       </c>
       <c r="M11" s="2">
         <v>46232</v>
       </c>
-      <c r="N11" s="24" t="s">
+      <c r="N11" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O11" s="8" t="s">
@@ -3054,12 +3032,12 @@
       <c r="P11" s="8"/>
     </row>
     <row r="12" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
       <c r="D12" s="11">
         <v>5</v>
       </c>
-      <c r="E12" s="22"/>
+      <c r="E12" s="20"/>
       <c r="F12" s="8" t="s">
         <v>487</v>
       </c>
@@ -3076,13 +3054,13 @@
       <c r="K12" s="8" t="s">
         <v>490</v>
       </c>
-      <c r="L12" s="24" t="s">
+      <c r="L12" s="14" t="s">
         <v>88</v>
       </c>
       <c r="M12" s="2">
         <v>46232</v>
       </c>
-      <c r="N12" s="24" t="s">
+      <c r="N12" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O12" s="8" t="s">
@@ -3091,12 +3069,12 @@
       <c r="P12" s="8"/>
     </row>
     <row r="13" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
       <c r="D13" s="11">
         <v>6</v>
       </c>
-      <c r="E13" s="22"/>
+      <c r="E13" s="20"/>
       <c r="F13" s="8" t="s">
         <v>492</v>
       </c>
@@ -3113,13 +3091,13 @@
       <c r="K13" s="8" t="s">
         <v>495</v>
       </c>
-      <c r="L13" s="24" t="s">
+      <c r="L13" s="14" t="s">
         <v>88</v>
       </c>
       <c r="M13" s="2">
         <v>46232</v>
       </c>
-      <c r="N13" s="24" t="s">
+      <c r="N13" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O13" s="8" t="s">
@@ -3128,12 +3106,12 @@
       <c r="P13" s="8"/>
     </row>
     <row r="14" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
       <c r="D14" s="11">
         <v>7</v>
       </c>
-      <c r="E14" s="22"/>
+      <c r="E14" s="20"/>
       <c r="F14" s="8" t="s">
         <v>497</v>
       </c>
@@ -3150,13 +3128,13 @@
       <c r="K14" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="L14" s="24" t="s">
+      <c r="L14" s="14" t="s">
         <v>88</v>
       </c>
       <c r="M14" s="2">
         <v>46232</v>
       </c>
-      <c r="N14" s="24" t="s">
+      <c r="N14" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O14" s="8" t="s">
@@ -3165,12 +3143,12 @@
       <c r="P14" s="8"/>
     </row>
     <row r="15" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
       <c r="D15" s="11">
         <v>8</v>
       </c>
-      <c r="E15" s="22"/>
+      <c r="E15" s="20"/>
       <c r="F15" s="8" t="s">
         <v>502</v>
       </c>
@@ -3187,13 +3165,13 @@
       <c r="K15" s="8" t="s">
         <v>505</v>
       </c>
-      <c r="L15" s="24" t="s">
+      <c r="L15" s="14" t="s">
         <v>88</v>
       </c>
       <c r="M15" s="2">
         <v>46232</v>
       </c>
-      <c r="N15" s="24" t="s">
+      <c r="N15" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O15" s="8" t="s">
@@ -3202,12 +3180,12 @@
       <c r="P15" s="8"/>
     </row>
     <row r="16" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
       <c r="D16" s="11">
         <v>9</v>
       </c>
-      <c r="E16" s="22"/>
+      <c r="E16" s="20"/>
       <c r="F16" s="8" t="s">
         <v>507</v>
       </c>
@@ -3224,13 +3202,13 @@
       <c r="K16" s="8" t="s">
         <v>510</v>
       </c>
-      <c r="L16" s="24" t="s">
+      <c r="L16" s="14" t="s">
         <v>88</v>
       </c>
       <c r="M16" s="2">
         <v>46232</v>
       </c>
-      <c r="N16" s="24" t="s">
+      <c r="N16" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O16" s="8" t="s">
@@ -3239,12 +3217,12 @@
       <c r="P16" s="8"/>
     </row>
     <row r="17" spans="2:16" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
       <c r="D17" s="11">
         <v>10</v>
       </c>
-      <c r="E17" s="22"/>
+      <c r="E17" s="20"/>
       <c r="F17" s="8" t="s">
         <v>512</v>
       </c>
@@ -3261,13 +3239,13 @@
       <c r="K17" s="8" t="s">
         <v>515</v>
       </c>
-      <c r="L17" s="24" t="s">
+      <c r="L17" s="14" t="s">
         <v>88</v>
       </c>
       <c r="M17" s="2">
         <v>46232</v>
       </c>
-      <c r="N17" s="24" t="s">
+      <c r="N17" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O17" s="8" t="s">
@@ -3276,12 +3254,12 @@
       <c r="P17" s="8"/>
     </row>
     <row r="18" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
       <c r="D18" s="11">
         <v>11</v>
       </c>
-      <c r="E18" s="22"/>
+      <c r="E18" s="20"/>
       <c r="F18" s="8" t="s">
         <v>517</v>
       </c>
@@ -3298,13 +3276,13 @@
       <c r="K18" s="8" t="s">
         <v>519</v>
       </c>
-      <c r="L18" s="24" t="s">
+      <c r="L18" s="14" t="s">
         <v>88</v>
       </c>
       <c r="M18" s="2">
         <v>46233</v>
       </c>
-      <c r="N18" s="24" t="s">
+      <c r="N18" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O18" s="8" t="s">
@@ -3315,12 +3293,12 @@
       </c>
     </row>
     <row r="19" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
       <c r="D19" s="11">
         <v>12</v>
       </c>
-      <c r="E19" s="22"/>
+      <c r="E19" s="20"/>
       <c r="F19" s="8" t="s">
         <v>521</v>
       </c>
@@ -3337,13 +3315,13 @@
       <c r="K19" s="8" t="s">
         <v>523</v>
       </c>
-      <c r="L19" s="24" t="s">
+      <c r="L19" s="14" t="s">
         <v>88</v>
       </c>
       <c r="M19" s="2">
         <v>46232</v>
       </c>
-      <c r="N19" s="24" t="s">
+      <c r="N19" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O19" s="8" t="s">
@@ -3354,12 +3332,12 @@
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
       <c r="D20" s="11">
         <v>13</v>
       </c>
-      <c r="E20" s="22"/>
+      <c r="E20" s="20"/>
       <c r="F20" s="8" t="s">
         <v>525</v>
       </c>
@@ -3376,13 +3354,13 @@
       <c r="K20" s="8" t="s">
         <v>528</v>
       </c>
-      <c r="L20" s="24" t="s">
+      <c r="L20" s="14" t="s">
         <v>88</v>
       </c>
       <c r="M20" s="2">
         <v>46232</v>
       </c>
-      <c r="N20" s="24" t="s">
+      <c r="N20" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O20" s="8" t="s">
@@ -3393,12 +3371,12 @@
       </c>
     </row>
     <row r="21" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
       <c r="D21" s="11">
         <v>14</v>
       </c>
-      <c r="E21" s="22"/>
+      <c r="E21" s="20"/>
       <c r="F21" s="8" t="s">
         <v>530</v>
       </c>
@@ -3415,13 +3393,13 @@
       <c r="K21" s="8" t="s">
         <v>533</v>
       </c>
-      <c r="L21" s="24" t="s">
+      <c r="L21" s="14" t="s">
         <v>88</v>
       </c>
       <c r="M21" s="2">
         <v>46232</v>
       </c>
-      <c r="N21" s="24" t="s">
+      <c r="N21" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O21" s="8" t="s">
@@ -3432,12 +3410,12 @@
       </c>
     </row>
     <row r="22" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
       <c r="D22" s="11">
         <v>15</v>
       </c>
-      <c r="E22" s="22"/>
+      <c r="E22" s="20"/>
       <c r="F22" s="8" t="s">
         <v>535</v>
       </c>
@@ -3454,13 +3432,13 @@
       <c r="K22" s="8" t="s">
         <v>537</v>
       </c>
-      <c r="L22" s="24" t="s">
+      <c r="L22" s="14" t="s">
         <v>88</v>
       </c>
       <c r="M22" s="2">
         <v>46232</v>
       </c>
-      <c r="N22" s="24" t="s">
+      <c r="N22" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O22" s="8" t="s">
@@ -3472,6 +3450,7 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="L6:P6"/>
     <mergeCell ref="B8:B22"/>
     <mergeCell ref="C8:C22"/>
     <mergeCell ref="E8:E22"/>
@@ -3479,7 +3458,6 @@
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="B6:K6"/>
-    <mergeCell ref="L6:P6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3509,56 +3487,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="26.5" x14ac:dyDescent="0.8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="21" t="s">
         <v>539</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="22" t="s">
         <v>540</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="22" t="s">
         <v>541</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="18" t="s">
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25"/>
-      <c r="P6" s="25"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
@@ -3617,7 +3595,7 @@
       <c r="D8" s="11">
         <v>1</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="20" t="s">
         <v>542</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -3636,13 +3614,13 @@
       <c r="K8" s="8" t="s">
         <v>546</v>
       </c>
-      <c r="L8" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M8" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N8" s="24" t="s">
+      <c r="L8" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M8" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N8" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O8" s="8" t="s">
@@ -3656,7 +3634,7 @@
       <c r="D9" s="11">
         <v>2</v>
       </c>
-      <c r="E9" s="21"/>
+      <c r="E9" s="20"/>
       <c r="F9" s="8" t="s">
         <v>548</v>
       </c>
@@ -3673,13 +3651,13 @@
       <c r="K9" s="8" t="s">
         <v>550</v>
       </c>
-      <c r="L9" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M9" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N9" s="24" t="s">
+      <c r="L9" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M9" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N9" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O9" s="8" t="s">
@@ -3693,7 +3671,7 @@
       <c r="D10" s="11">
         <v>3</v>
       </c>
-      <c r="E10" s="21"/>
+      <c r="E10" s="20"/>
       <c r="F10" s="8" t="s">
         <v>552</v>
       </c>
@@ -3710,13 +3688,13 @@
       <c r="K10" s="8" t="s">
         <v>555</v>
       </c>
-      <c r="L10" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M10" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N10" s="24" t="s">
+      <c r="L10" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M10" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N10" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O10" s="8"/>
@@ -3728,7 +3706,7 @@
       <c r="D11" s="11">
         <v>4</v>
       </c>
-      <c r="E11" s="21"/>
+      <c r="E11" s="20"/>
       <c r="F11" s="8" t="s">
         <v>556</v>
       </c>
@@ -3745,13 +3723,13 @@
       <c r="K11" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="L11" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M11" s="26">
+      <c r="L11" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="16">
         <v>46233</v>
       </c>
-      <c r="N11" s="24" t="s">
+      <c r="N11" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O11" s="8" t="s">
@@ -3765,7 +3743,7 @@
       <c r="D12" s="11">
         <v>5</v>
       </c>
-      <c r="E12" s="21"/>
+      <c r="E12" s="20"/>
       <c r="F12" s="8" t="s">
         <v>561</v>
       </c>
@@ -3782,13 +3760,13 @@
       <c r="K12" s="8" t="s">
         <v>564</v>
       </c>
-      <c r="L12" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M12" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N12" s="24" t="s">
+      <c r="L12" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N12" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O12" s="8" t="s">
@@ -3802,7 +3780,7 @@
       <c r="D13" s="11">
         <v>6</v>
       </c>
-      <c r="E13" s="21"/>
+      <c r="E13" s="20"/>
       <c r="F13" s="8" t="s">
         <v>566</v>
       </c>
@@ -3819,13 +3797,13 @@
       <c r="K13" s="8" t="s">
         <v>569</v>
       </c>
-      <c r="L13" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M13" s="26">
+      <c r="L13" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" s="16">
         <v>46233</v>
       </c>
-      <c r="N13" s="24" t="s">
+      <c r="N13" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O13" s="8" t="s">
@@ -3841,7 +3819,7 @@
       <c r="D14" s="11">
         <v>7</v>
       </c>
-      <c r="E14" s="21"/>
+      <c r="E14" s="20"/>
       <c r="F14" s="8" t="s">
         <v>571</v>
       </c>
@@ -3858,13 +3836,13 @@
       <c r="K14" s="8" t="s">
         <v>574</v>
       </c>
-      <c r="L14" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M14" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N14" s="24" t="s">
+      <c r="L14" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M14" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N14" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O14" s="8" t="s">
@@ -3880,7 +3858,7 @@
       <c r="D15" s="11">
         <v>8</v>
       </c>
-      <c r="E15" s="21"/>
+      <c r="E15" s="20"/>
       <c r="F15" s="8" t="s">
         <v>575</v>
       </c>
@@ -3897,13 +3875,13 @@
       <c r="K15" s="8" t="s">
         <v>578</v>
       </c>
-      <c r="L15" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M15" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N15" s="24" t="s">
+      <c r="L15" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M15" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N15" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O15" s="8" t="s">
@@ -3915,6 +3893,7 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="L6:P6"/>
     <mergeCell ref="B8:B15"/>
     <mergeCell ref="C8:C15"/>
     <mergeCell ref="E8:E15"/>
@@ -3922,7 +3901,6 @@
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="B6:K6"/>
-    <mergeCell ref="L6:P6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3952,56 +3930,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="26.5" x14ac:dyDescent="0.8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="21" t="s">
         <v>580</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="22" t="s">
         <v>581</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="22" t="s">
         <v>582</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="23" t="s">
         <v>640</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="18" t="s">
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25"/>
-      <c r="P6" s="25"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
@@ -4060,7 +4038,7 @@
       <c r="D8" s="11">
         <v>1</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="20" t="s">
         <v>583</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -4097,7 +4075,7 @@
       <c r="D9" s="11">
         <v>2</v>
       </c>
-      <c r="E9" s="21"/>
+      <c r="E9" s="20"/>
       <c r="F9" s="8" t="s">
         <v>587</v>
       </c>
@@ -4134,7 +4112,7 @@
       <c r="D10" s="11">
         <v>3</v>
       </c>
-      <c r="E10" s="21"/>
+      <c r="E10" s="20"/>
       <c r="F10" s="8" t="s">
         <v>592</v>
       </c>
@@ -4149,7 +4127,7 @@
         <v>594</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="L10" s="8" t="s">
         <v>88</v>
@@ -4158,10 +4136,10 @@
         <v>46233</v>
       </c>
       <c r="N10" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="O10" s="8" t="s">
         <v>641</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>642</v>
       </c>
       <c r="P10" s="8"/>
     </row>
@@ -4171,7 +4149,7 @@
       <c r="D11" s="11">
         <v>4</v>
       </c>
-      <c r="E11" s="21"/>
+      <c r="E11" s="20"/>
       <c r="F11" s="8" t="s">
         <v>596</v>
       </c>
@@ -4208,7 +4186,7 @@
       <c r="D12" s="11">
         <v>5</v>
       </c>
-      <c r="E12" s="21"/>
+      <c r="E12" s="20"/>
       <c r="F12" s="8" t="s">
         <v>601</v>
       </c>
@@ -4245,7 +4223,7 @@
       <c r="D13" s="11">
         <v>6</v>
       </c>
-      <c r="E13" s="21"/>
+      <c r="E13" s="20"/>
       <c r="F13" s="8" t="s">
         <v>606</v>
       </c>
@@ -4282,7 +4260,7 @@
       <c r="D14" s="11">
         <v>7</v>
       </c>
-      <c r="E14" s="21"/>
+      <c r="E14" s="20"/>
       <c r="F14" s="8" t="s">
         <v>611</v>
       </c>
@@ -4321,7 +4299,7 @@
       <c r="D15" s="11">
         <v>8</v>
       </c>
-      <c r="E15" s="21"/>
+      <c r="E15" s="20"/>
       <c r="F15" s="8" t="s">
         <v>616</v>
       </c>
@@ -4360,7 +4338,7 @@
       <c r="D16" s="11">
         <v>9</v>
       </c>
-      <c r="E16" s="21"/>
+      <c r="E16" s="20"/>
       <c r="F16" s="8" t="s">
         <v>621</v>
       </c>
@@ -4399,7 +4377,7 @@
       <c r="D17" s="11">
         <v>10</v>
       </c>
-      <c r="E17" s="21"/>
+      <c r="E17" s="20"/>
       <c r="F17" s="8" t="s">
         <v>626</v>
       </c>
@@ -4434,6 +4412,7 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="L6:P6"/>
     <mergeCell ref="B8:B17"/>
     <mergeCell ref="C8:C17"/>
     <mergeCell ref="E8:E17"/>
@@ -4441,7 +4420,6 @@
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="B6:K6"/>
-    <mergeCell ref="L6:P6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4469,15 +4447,15 @@
       </c>
     </row>
     <row r="2" spans="2:10" ht="306" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="24" t="s">
         <v>632</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="3" t="s">
@@ -4509,32 +4487,32 @@
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="29">
+      <c r="B5" s="15">
         <v>1</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="15" t="s">
+        <v>644</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>645</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="E5" s="15">
+        <v>3</v>
+      </c>
+      <c r="F5" s="15" t="s">
         <v>646</v>
       </c>
-      <c r="E5" s="29">
-        <v>3</v>
-      </c>
-      <c r="F5" s="29" t="s">
+      <c r="G5" s="15" t="s">
         <v>647</v>
       </c>
-      <c r="G5" s="29" t="s">
-        <v>648</v>
-      </c>
-      <c r="H5" s="29" t="s">
+      <c r="H5" s="15" t="s">
         <v>595</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="15" t="s">
+        <v>649</v>
+      </c>
+      <c r="J5" s="15" t="s">
         <v>650</v>
-      </c>
-      <c r="J5" s="29" t="s">
-        <v>651</v>
       </c>
     </row>
   </sheetData>
@@ -4636,10 +4614,10 @@
     <row r="11" spans="2:4" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="8"/>
       <c r="C11" s="8" t="s">
-        <v>26</v>
+        <v>653</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>27</v>
+        <v>654</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -4848,56 +4826,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="26.5" x14ac:dyDescent="0.8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="18" t="s">
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25"/>
-      <c r="P6" s="25"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
@@ -4956,7 +4934,7 @@
       <c r="D8" s="11">
         <v>1</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="20" t="s">
         <v>83</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -4975,13 +4953,13 @@
       <c r="K8" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="L8" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M8" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N8" s="24" t="s">
+      <c r="L8" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M8" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N8" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O8" s="8" t="s">
@@ -4995,7 +4973,7 @@
       <c r="D9" s="11">
         <v>2</v>
       </c>
-      <c r="E9" s="21"/>
+      <c r="E9" s="20"/>
       <c r="F9" s="8" t="s">
         <v>90</v>
       </c>
@@ -5012,13 +4990,13 @@
       <c r="K9" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="L9" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M9" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N9" s="24" t="s">
+      <c r="L9" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M9" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N9" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O9" s="8"/>
@@ -5030,7 +5008,7 @@
       <c r="D10" s="11">
         <v>3</v>
       </c>
-      <c r="E10" s="21"/>
+      <c r="E10" s="20"/>
       <c r="F10" s="8" t="s">
         <v>94</v>
       </c>
@@ -5047,13 +5025,13 @@
       <c r="K10" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="L10" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M10" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N10" s="24" t="s">
+      <c r="L10" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M10" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N10" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O10" s="8" t="s">
@@ -5067,7 +5045,7 @@
       <c r="D11" s="11">
         <v>4</v>
       </c>
-      <c r="E11" s="21"/>
+      <c r="E11" s="20"/>
       <c r="F11" s="8" t="s">
         <v>99</v>
       </c>
@@ -5084,13 +5062,13 @@
       <c r="K11" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L11" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M11" s="26">
+      <c r="L11" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="16">
         <v>46233</v>
       </c>
-      <c r="N11" s="24" t="s">
+      <c r="N11" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O11" s="8" t="s">
@@ -5104,7 +5082,7 @@
       <c r="D12" s="11">
         <v>5</v>
       </c>
-      <c r="E12" s="21"/>
+      <c r="E12" s="20"/>
       <c r="F12" s="8" t="s">
         <v>103</v>
       </c>
@@ -5121,13 +5099,13 @@
       <c r="K12" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="L12" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M12" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N12" s="24" t="s">
+      <c r="L12" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N12" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O12" s="8" t="s">
@@ -5141,7 +5119,7 @@
       <c r="D13" s="11">
         <v>6</v>
       </c>
-      <c r="E13" s="21"/>
+      <c r="E13" s="20"/>
       <c r="F13" s="8" t="s">
         <v>108</v>
       </c>
@@ -5158,13 +5136,13 @@
       <c r="K13" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="L13" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M13" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N13" s="24" t="s">
+      <c r="L13" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N13" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O13" s="8" t="s">
@@ -5178,7 +5156,7 @@
       <c r="D14" s="11">
         <v>7</v>
       </c>
-      <c r="E14" s="21"/>
+      <c r="E14" s="20"/>
       <c r="F14" s="8" t="s">
         <v>113</v>
       </c>
@@ -5195,13 +5173,13 @@
       <c r="K14" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="L14" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M14" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N14" s="24" t="s">
+      <c r="L14" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M14" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N14" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O14" s="8" t="s">
@@ -5215,7 +5193,7 @@
       <c r="D15" s="11">
         <v>8</v>
       </c>
-      <c r="E15" s="21"/>
+      <c r="E15" s="20"/>
       <c r="F15" s="8" t="s">
         <v>117</v>
       </c>
@@ -5232,13 +5210,13 @@
       <c r="K15" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="L15" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M15" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N15" s="24" t="s">
+      <c r="L15" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M15" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N15" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O15" s="8" t="s">
@@ -5252,7 +5230,7 @@
       <c r="D16" s="11">
         <v>9</v>
       </c>
-      <c r="E16" s="21"/>
+      <c r="E16" s="20"/>
       <c r="F16" s="8" t="s">
         <v>122</v>
       </c>
@@ -5269,13 +5247,13 @@
       <c r="K16" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="L16" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M16" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N16" s="24" t="s">
+      <c r="L16" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M16" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N16" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O16" s="8" t="s">
@@ -5289,7 +5267,7 @@
       <c r="D17" s="11">
         <v>10</v>
       </c>
-      <c r="E17" s="21"/>
+      <c r="E17" s="20"/>
       <c r="F17" s="8" t="s">
         <v>127</v>
       </c>
@@ -5306,13 +5284,13 @@
       <c r="K17" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="L17" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M17" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N17" s="24" t="s">
+      <c r="L17" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M17" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N17" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O17" s="8" t="s">
@@ -5326,7 +5304,7 @@
       <c r="D18" s="11">
         <v>11</v>
       </c>
-      <c r="E18" s="21"/>
+      <c r="E18" s="20"/>
       <c r="F18" s="8" t="s">
         <v>132</v>
       </c>
@@ -5343,13 +5321,13 @@
       <c r="K18" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="L18" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M18" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N18" s="24" t="s">
+      <c r="L18" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M18" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N18" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O18" s="8" t="s">
@@ -5363,7 +5341,7 @@
       <c r="D19" s="11">
         <v>12</v>
       </c>
-      <c r="E19" s="21"/>
+      <c r="E19" s="20"/>
       <c r="F19" s="8" t="s">
         <v>137</v>
       </c>
@@ -5380,13 +5358,13 @@
       <c r="K19" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="L19" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M19" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N19" s="24" t="s">
+      <c r="L19" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M19" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N19" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O19" s="8" t="s">
@@ -5400,7 +5378,7 @@
       <c r="D20" s="11">
         <v>13</v>
       </c>
-      <c r="E20" s="21"/>
+      <c r="E20" s="20"/>
       <c r="F20" s="8" t="s">
         <v>141</v>
       </c>
@@ -5417,13 +5395,13 @@
       <c r="K20" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="L20" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M20" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N20" s="24" t="s">
+      <c r="L20" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M20" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N20" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O20" s="8" t="s">
@@ -5437,7 +5415,7 @@
       <c r="D21" s="11">
         <v>14</v>
       </c>
-      <c r="E21" s="21"/>
+      <c r="E21" s="20"/>
       <c r="F21" s="8" t="s">
         <v>146</v>
       </c>
@@ -5454,13 +5432,13 @@
       <c r="K21" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="L21" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M21" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N21" s="24" t="s">
+      <c r="L21" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M21" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N21" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O21" s="8" t="s">
@@ -5474,7 +5452,7 @@
       <c r="D22" s="11">
         <v>15</v>
       </c>
-      <c r="E22" s="21"/>
+      <c r="E22" s="20"/>
       <c r="F22" s="8" t="s">
         <v>151</v>
       </c>
@@ -5491,13 +5469,13 @@
       <c r="K22" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="L22" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M22" s="26">
+      <c r="L22" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M22" s="16">
         <v>46233</v>
       </c>
-      <c r="N22" s="24" t="s">
+      <c r="N22" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O22" s="8" t="s">
@@ -5513,7 +5491,7 @@
       <c r="D23" s="11">
         <v>16</v>
       </c>
-      <c r="E23" s="21"/>
+      <c r="E23" s="20"/>
       <c r="F23" s="8" t="s">
         <v>156</v>
       </c>
@@ -5530,13 +5508,13 @@
       <c r="K23" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="L23" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M23" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N23" s="24" t="s">
+      <c r="L23" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M23" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N23" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O23" s="8" t="s">
@@ -5552,7 +5530,7 @@
       <c r="D24" s="11">
         <v>17</v>
       </c>
-      <c r="E24" s="21"/>
+      <c r="E24" s="20"/>
       <c r="F24" s="8" t="s">
         <v>161</v>
       </c>
@@ -5569,13 +5547,13 @@
       <c r="K24" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="L24" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M24" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N24" s="24" t="s">
+      <c r="L24" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M24" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N24" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O24" s="8" t="s">
@@ -5587,6 +5565,7 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="L6:P6"/>
     <mergeCell ref="B8:B24"/>
     <mergeCell ref="C8:C24"/>
     <mergeCell ref="E8:E24"/>
@@ -5594,7 +5573,6 @@
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="B6:K6"/>
-    <mergeCell ref="L6:P6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5624,56 +5602,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="26.5" x14ac:dyDescent="0.8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="18" t="s">
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25"/>
-      <c r="P6" s="25"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
@@ -5732,7 +5710,7 @@
       <c r="D8" s="11">
         <v>1</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="20" t="s">
         <v>169</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -5751,13 +5729,13 @@
       <c r="K8" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="L8" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M8" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N8" s="24" t="s">
+      <c r="L8" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M8" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N8" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O8" s="8" t="s">
@@ -5771,7 +5749,7 @@
       <c r="D9" s="11">
         <v>2</v>
       </c>
-      <c r="E9" s="21"/>
+      <c r="E9" s="20"/>
       <c r="F9" s="8" t="s">
         <v>175</v>
       </c>
@@ -5788,13 +5766,13 @@
       <c r="K9" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="L9" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M9" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N9" s="24" t="s">
+      <c r="L9" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M9" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N9" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O9" s="8" t="s">
@@ -5808,7 +5786,7 @@
       <c r="D10" s="11">
         <v>3</v>
       </c>
-      <c r="E10" s="21"/>
+      <c r="E10" s="20"/>
       <c r="F10" s="8" t="s">
         <v>179</v>
       </c>
@@ -5825,13 +5803,13 @@
       <c r="K10" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="L10" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M10" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N10" s="24" t="s">
+      <c r="L10" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M10" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N10" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O10" s="8" t="s">
@@ -5845,7 +5823,7 @@
       <c r="D11" s="11">
         <v>4</v>
       </c>
-      <c r="E11" s="21"/>
+      <c r="E11" s="20"/>
       <c r="F11" s="8" t="s">
         <v>182</v>
       </c>
@@ -5862,13 +5840,13 @@
       <c r="K11" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="L11" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M11" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N11" s="24" t="s">
+      <c r="L11" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N11" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O11" s="8" t="s">
@@ -5882,7 +5860,7 @@
       <c r="D12" s="11">
         <v>5</v>
       </c>
-      <c r="E12" s="21"/>
+      <c r="E12" s="20"/>
       <c r="F12" s="8" t="s">
         <v>187</v>
       </c>
@@ -5899,13 +5877,13 @@
       <c r="K12" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="L12" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M12" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N12" s="24" t="s">
+      <c r="L12" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N12" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O12" s="8" t="s">
@@ -5919,7 +5897,7 @@
       <c r="D13" s="11">
         <v>6</v>
       </c>
-      <c r="E13" s="21"/>
+      <c r="E13" s="20"/>
       <c r="F13" s="8" t="s">
         <v>191</v>
       </c>
@@ -5936,13 +5914,13 @@
       <c r="K13" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="L13" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M13" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N13" s="24" t="s">
+      <c r="L13" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N13" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O13" s="8" t="s">
@@ -5956,7 +5934,7 @@
       <c r="D14" s="11">
         <v>7</v>
       </c>
-      <c r="E14" s="21"/>
+      <c r="E14" s="20"/>
       <c r="F14" s="8" t="s">
         <v>196</v>
       </c>
@@ -5973,13 +5951,13 @@
       <c r="K14" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="L14" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M14" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N14" s="24" t="s">
+      <c r="L14" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M14" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N14" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O14" s="8" t="s">
@@ -5993,7 +5971,7 @@
       <c r="D15" s="11">
         <v>8</v>
       </c>
-      <c r="E15" s="21"/>
+      <c r="E15" s="20"/>
       <c r="F15" s="8" t="s">
         <v>200</v>
       </c>
@@ -6010,13 +5988,13 @@
       <c r="K15" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="L15" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M15" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N15" s="24" t="s">
+      <c r="L15" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M15" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N15" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O15" s="8" t="s">
@@ -6030,7 +6008,7 @@
       <c r="D16" s="11">
         <v>9</v>
       </c>
-      <c r="E16" s="21"/>
+      <c r="E16" s="20"/>
       <c r="F16" s="8" t="s">
         <v>205</v>
       </c>
@@ -6047,13 +6025,13 @@
       <c r="K16" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="L16" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M16" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N16" s="24" t="s">
+      <c r="L16" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M16" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N16" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O16" s="8" t="s">
@@ -6067,7 +6045,7 @@
       <c r="D17" s="11">
         <v>10</v>
       </c>
-      <c r="E17" s="21"/>
+      <c r="E17" s="20"/>
       <c r="F17" s="8" t="s">
         <v>210</v>
       </c>
@@ -6084,13 +6062,13 @@
       <c r="K17" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="L17" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M17" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N17" s="24" t="s">
+      <c r="L17" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M17" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N17" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O17" s="8" t="s">
@@ -6106,7 +6084,7 @@
       <c r="D18" s="11">
         <v>11</v>
       </c>
-      <c r="E18" s="21"/>
+      <c r="E18" s="20"/>
       <c r="F18" s="8" t="s">
         <v>215</v>
       </c>
@@ -6123,13 +6101,13 @@
       <c r="K18" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="L18" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M18" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N18" s="24" t="s">
+      <c r="L18" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M18" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N18" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O18" s="8" t="s">
@@ -6145,7 +6123,7 @@
       <c r="D19" s="11">
         <v>12</v>
       </c>
-      <c r="E19" s="21"/>
+      <c r="E19" s="20"/>
       <c r="F19" s="8" t="s">
         <v>219</v>
       </c>
@@ -6162,13 +6140,13 @@
       <c r="K19" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="L19" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M19" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N19" s="24" t="s">
+      <c r="L19" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M19" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N19" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O19" s="8" t="s">
@@ -6180,6 +6158,7 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="L6:P6"/>
     <mergeCell ref="B8:B19"/>
     <mergeCell ref="C8:C19"/>
     <mergeCell ref="E8:E19"/>
@@ -6187,7 +6166,6 @@
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="B6:K6"/>
-    <mergeCell ref="L6:P6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6217,56 +6195,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="26.5" x14ac:dyDescent="0.8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="22" t="s">
         <v>225</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="18" t="s">
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25"/>
-      <c r="P6" s="25"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
@@ -6325,7 +6303,7 @@
       <c r="D8" s="11">
         <v>1</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="20" t="s">
         <v>226</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -6341,16 +6319,16 @@
       <c r="J8" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="K8" s="24" t="s">
+      <c r="K8" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="L8" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M8" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N8" s="24" t="s">
+      <c r="L8" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M8" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N8" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O8" s="8" t="s">
@@ -6364,7 +6342,7 @@
       <c r="D9" s="11">
         <v>2</v>
       </c>
-      <c r="E9" s="21"/>
+      <c r="E9" s="20"/>
       <c r="F9" s="8" t="s">
         <v>232</v>
       </c>
@@ -6378,16 +6356,16 @@
       <c r="J9" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="K9" s="24" t="s">
+      <c r="K9" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="L9" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M9" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N9" s="24" t="s">
+      <c r="L9" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M9" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N9" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O9" s="8" t="s">
@@ -6401,7 +6379,7 @@
       <c r="D10" s="11">
         <v>3</v>
       </c>
-      <c r="E10" s="21"/>
+      <c r="E10" s="20"/>
       <c r="F10" s="8" t="s">
         <v>237</v>
       </c>
@@ -6415,16 +6393,16 @@
       <c r="J10" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="K10" s="24" t="s">
+      <c r="K10" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="L10" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M10" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N10" s="24" t="s">
+      <c r="L10" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M10" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N10" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O10" s="8" t="s">
@@ -6438,7 +6416,7 @@
       <c r="D11" s="11">
         <v>4</v>
       </c>
-      <c r="E11" s="21"/>
+      <c r="E11" s="20"/>
       <c r="F11" s="8" t="s">
         <v>242</v>
       </c>
@@ -6452,16 +6430,16 @@
       <c r="J11" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="K11" s="24" t="s">
+      <c r="K11" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="L11" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M11" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N11" s="24" t="s">
+      <c r="L11" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N11" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O11" s="8"/>
@@ -6473,7 +6451,7 @@
       <c r="D12" s="11">
         <v>5</v>
       </c>
-      <c r="E12" s="21"/>
+      <c r="E12" s="20"/>
       <c r="F12" s="8" t="s">
         <v>246</v>
       </c>
@@ -6487,16 +6465,16 @@
       <c r="J12" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="K12" s="24" t="s">
+      <c r="K12" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="L12" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M12" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N12" s="24" t="s">
+      <c r="L12" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N12" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O12" s="8" t="s">
@@ -6510,7 +6488,7 @@
       <c r="D13" s="11">
         <v>6</v>
       </c>
-      <c r="E13" s="21"/>
+      <c r="E13" s="20"/>
       <c r="F13" s="8" t="s">
         <v>250</v>
       </c>
@@ -6524,16 +6502,16 @@
       <c r="J13" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="K13" s="24" t="s">
+      <c r="K13" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="L13" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M13" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N13" s="24" t="s">
+      <c r="L13" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N13" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O13" s="8"/>
@@ -6545,7 +6523,7 @@
       <c r="D14" s="11">
         <v>7</v>
       </c>
-      <c r="E14" s="21"/>
+      <c r="E14" s="20"/>
       <c r="F14" s="8" t="s">
         <v>253</v>
       </c>
@@ -6559,16 +6537,16 @@
       <c r="J14" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="K14" s="24" t="s">
+      <c r="K14" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="L14" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M14" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N14" s="24" t="s">
+      <c r="L14" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M14" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N14" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O14" s="8" t="s">
@@ -6582,7 +6560,7 @@
       <c r="D15" s="11">
         <v>8</v>
       </c>
-      <c r="E15" s="21"/>
+      <c r="E15" s="20"/>
       <c r="F15" s="8" t="s">
         <v>258</v>
       </c>
@@ -6596,16 +6574,16 @@
       <c r="J15" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="K15" s="24" t="s">
+      <c r="K15" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="L15" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M15" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N15" s="24" t="s">
+      <c r="L15" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M15" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N15" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O15" s="8" t="s">
@@ -6619,7 +6597,7 @@
       <c r="D16" s="11">
         <v>9</v>
       </c>
-      <c r="E16" s="21"/>
+      <c r="E16" s="20"/>
       <c r="F16" s="8" t="s">
         <v>263</v>
       </c>
@@ -6633,16 +6611,16 @@
       <c r="J16" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="K16" s="24" t="s">
+      <c r="K16" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="L16" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M16" s="26">
+      <c r="L16" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M16" s="16">
         <v>46233</v>
       </c>
-      <c r="N16" s="24" t="s">
+      <c r="N16" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O16" s="8" t="s">
@@ -6654,6 +6632,7 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="L6:P6"/>
     <mergeCell ref="B8:B16"/>
     <mergeCell ref="C8:C16"/>
     <mergeCell ref="E8:E16"/>
@@ -6661,7 +6640,6 @@
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="B6:K6"/>
-    <mergeCell ref="L6:P6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6691,56 +6669,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="26.5" x14ac:dyDescent="0.8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="22" t="s">
         <v>268</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="22" t="s">
         <v>225</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="18" t="s">
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25"/>
-      <c r="P6" s="25"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
@@ -6799,7 +6777,7 @@
       <c r="D8" s="11">
         <v>1</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="20" t="s">
         <v>269</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -6818,13 +6796,13 @@
       <c r="K8" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="L8" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M8" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N8" s="24" t="s">
+      <c r="L8" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M8" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N8" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O8" s="8" t="s">
@@ -6838,7 +6816,7 @@
       <c r="D9" s="11">
         <v>2</v>
       </c>
-      <c r="E9" s="21"/>
+      <c r="E9" s="20"/>
       <c r="F9" s="8" t="s">
         <v>275</v>
       </c>
@@ -6855,13 +6833,13 @@
       <c r="K9" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="L9" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M9" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N9" s="24" t="s">
+      <c r="L9" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M9" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N9" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O9" s="8" t="s">
@@ -6875,7 +6853,7 @@
       <c r="D10" s="11">
         <v>3</v>
       </c>
-      <c r="E10" s="21"/>
+      <c r="E10" s="20"/>
       <c r="F10" s="8" t="s">
         <v>280</v>
       </c>
@@ -6892,13 +6870,13 @@
       <c r="K10" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="L10" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M10" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N10" s="24" t="s">
+      <c r="L10" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M10" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N10" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O10" s="8" t="s">
@@ -6912,7 +6890,7 @@
       <c r="D11" s="11">
         <v>4</v>
       </c>
-      <c r="E11" s="21"/>
+      <c r="E11" s="20"/>
       <c r="F11" s="8" t="s">
         <v>284</v>
       </c>
@@ -6929,13 +6907,13 @@
       <c r="K11" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="L11" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M11" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N11" s="24" t="s">
+      <c r="L11" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N11" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O11" s="8"/>
@@ -6947,7 +6925,7 @@
       <c r="D12" s="11">
         <v>5</v>
       </c>
-      <c r="E12" s="21"/>
+      <c r="E12" s="20"/>
       <c r="F12" s="8" t="s">
         <v>288</v>
       </c>
@@ -6964,13 +6942,13 @@
       <c r="K12" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="L12" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M12" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N12" s="24" t="s">
+      <c r="L12" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N12" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O12" s="8" t="s">
@@ -6984,7 +6962,7 @@
       <c r="D13" s="11">
         <v>6</v>
       </c>
-      <c r="E13" s="21"/>
+      <c r="E13" s="20"/>
       <c r="F13" s="8" t="s">
         <v>293</v>
       </c>
@@ -7001,13 +6979,13 @@
       <c r="K13" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="L13" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M13" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N13" s="24" t="s">
+      <c r="L13" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N13" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O13" s="8" t="s">
@@ -7021,7 +6999,7 @@
       <c r="D14" s="11">
         <v>7</v>
       </c>
-      <c r="E14" s="21"/>
+      <c r="E14" s="20"/>
       <c r="F14" s="8" t="s">
         <v>297</v>
       </c>
@@ -7038,13 +7016,13 @@
       <c r="K14" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="L14" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M14" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N14" s="24" t="s">
+      <c r="L14" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M14" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N14" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O14" s="8" t="s">
@@ -7058,7 +7036,7 @@
       <c r="D15" s="11">
         <v>8</v>
       </c>
-      <c r="E15" s="21"/>
+      <c r="E15" s="20"/>
       <c r="F15" s="8" t="s">
         <v>302</v>
       </c>
@@ -7075,13 +7053,13 @@
       <c r="K15" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="L15" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M15" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N15" s="24" t="s">
+      <c r="L15" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M15" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N15" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O15" s="8" t="s">
@@ -7095,7 +7073,7 @@
       <c r="D16" s="11">
         <v>9</v>
       </c>
-      <c r="E16" s="21"/>
+      <c r="E16" s="20"/>
       <c r="F16" s="8" t="s">
         <v>307</v>
       </c>
@@ -7112,13 +7090,13 @@
       <c r="K16" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="L16" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M16" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N16" s="24" t="s">
+      <c r="L16" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M16" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N16" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O16" s="8" t="s">
@@ -7132,7 +7110,7 @@
       <c r="D17" s="11">
         <v>10</v>
       </c>
-      <c r="E17" s="21"/>
+      <c r="E17" s="20"/>
       <c r="F17" s="8" t="s">
         <v>311</v>
       </c>
@@ -7149,13 +7127,13 @@
       <c r="K17" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="L17" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M17" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N17" s="24" t="s">
+      <c r="L17" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M17" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N17" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O17" s="8" t="s">
@@ -7169,7 +7147,7 @@
       <c r="D18" s="11">
         <v>11</v>
       </c>
-      <c r="E18" s="21"/>
+      <c r="E18" s="20"/>
       <c r="F18" s="8" t="s">
         <v>316</v>
       </c>
@@ -7186,13 +7164,13 @@
       <c r="K18" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="L18" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M18" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N18" s="24" t="s">
+      <c r="L18" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M18" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N18" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O18" s="8" t="s">
@@ -7208,7 +7186,7 @@
       <c r="D19" s="11">
         <v>12</v>
       </c>
-      <c r="E19" s="21"/>
+      <c r="E19" s="20"/>
       <c r="F19" s="8" t="s">
         <v>321</v>
       </c>
@@ -7225,13 +7203,13 @@
       <c r="K19" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="L19" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M19" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N19" s="24" t="s">
+      <c r="L19" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M19" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N19" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O19" s="8" t="s">
@@ -7243,6 +7221,7 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="L6:P6"/>
     <mergeCell ref="B8:B19"/>
     <mergeCell ref="C8:C19"/>
     <mergeCell ref="E8:E19"/>
@@ -7250,7 +7229,6 @@
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="B6:K6"/>
-    <mergeCell ref="L6:P6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7280,56 +7258,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="26.5" x14ac:dyDescent="0.8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="22" t="s">
         <v>327</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="22" t="s">
         <v>328</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="18" t="s">
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25"/>
-      <c r="P6" s="25"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
@@ -7388,7 +7366,7 @@
       <c r="D8" s="11">
         <v>1</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="20" t="s">
         <v>57</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -7407,13 +7385,13 @@
       <c r="K8" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="L8" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M8" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N8" s="24" t="s">
+      <c r="L8" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M8" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N8" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O8" s="8" t="s">
@@ -7427,7 +7405,7 @@
       <c r="D9" s="11">
         <v>2</v>
       </c>
-      <c r="E9" s="21"/>
+      <c r="E9" s="20"/>
       <c r="F9" s="8" t="s">
         <v>334</v>
       </c>
@@ -7444,13 +7422,13 @@
       <c r="K9" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="L9" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M9" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N9" s="24" t="s">
+      <c r="L9" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M9" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N9" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O9" s="8"/>
@@ -7462,7 +7440,7 @@
       <c r="D10" s="11">
         <v>3</v>
       </c>
-      <c r="E10" s="21"/>
+      <c r="E10" s="20"/>
       <c r="F10" s="8" t="s">
         <v>337</v>
       </c>
@@ -7479,13 +7457,13 @@
       <c r="K10" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="L10" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M10" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N10" s="24" t="s">
+      <c r="L10" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M10" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N10" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O10" s="8" t="s">
@@ -7499,7 +7477,7 @@
       <c r="D11" s="11">
         <v>4</v>
       </c>
-      <c r="E11" s="21"/>
+      <c r="E11" s="20"/>
       <c r="F11" s="8" t="s">
         <v>342</v>
       </c>
@@ -7516,13 +7494,13 @@
       <c r="K11" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="L11" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M11" s="26">
+      <c r="L11" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="16">
         <v>46233</v>
       </c>
-      <c r="N11" s="24" t="s">
+      <c r="N11" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O11" s="8" t="s">
@@ -7536,7 +7514,7 @@
       <c r="D12" s="11">
         <v>5</v>
       </c>
-      <c r="E12" s="21"/>
+      <c r="E12" s="20"/>
       <c r="F12" s="8" t="s">
         <v>347</v>
       </c>
@@ -7553,13 +7531,13 @@
       <c r="K12" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="L12" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M12" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N12" s="24" t="s">
+      <c r="L12" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N12" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O12" s="8"/>
@@ -7571,7 +7549,7 @@
       <c r="D13" s="11">
         <v>6</v>
       </c>
-      <c r="E13" s="21"/>
+      <c r="E13" s="20"/>
       <c r="F13" s="8" t="s">
         <v>351</v>
       </c>
@@ -7588,13 +7566,13 @@
       <c r="K13" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="L13" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M13" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N13" s="24" t="s">
+      <c r="L13" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N13" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O13" s="8" t="s">
@@ -7604,6 +7582,7 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="L6:P6"/>
     <mergeCell ref="B8:B13"/>
     <mergeCell ref="C8:C13"/>
     <mergeCell ref="E8:E13"/>
@@ -7611,7 +7590,6 @@
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="B6:K6"/>
-    <mergeCell ref="L6:P6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7641,56 +7619,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="26.5" x14ac:dyDescent="0.8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="21" t="s">
         <v>355</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="22" t="s">
         <v>356</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="22" t="s">
         <v>357</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="18" t="s">
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25"/>
-      <c r="P6" s="25"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
@@ -7749,7 +7727,7 @@
       <c r="D8" s="11">
         <v>1</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="20" t="s">
         <v>358</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -7788,7 +7766,7 @@
       <c r="D9" s="11">
         <v>2</v>
       </c>
-      <c r="E9" s="21"/>
+      <c r="E9" s="20"/>
       <c r="F9" s="8" t="s">
         <v>364</v>
       </c>
@@ -7815,7 +7793,7 @@
         <v>639</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>368</v>
+        <v>655</v>
       </c>
       <c r="P9" s="8"/>
     </row>
@@ -7825,7 +7803,7 @@
       <c r="D10" s="11">
         <v>3</v>
       </c>
-      <c r="E10" s="21"/>
+      <c r="E10" s="20"/>
       <c r="F10" s="8" t="s">
         <v>369</v>
       </c>
@@ -7862,7 +7840,7 @@
       <c r="D11" s="11">
         <v>4</v>
       </c>
-      <c r="E11" s="21"/>
+      <c r="E11" s="20"/>
       <c r="F11" s="8" t="s">
         <v>374</v>
       </c>
@@ -7899,7 +7877,7 @@
       <c r="D12" s="11">
         <v>5</v>
       </c>
-      <c r="E12" s="21"/>
+      <c r="E12" s="20"/>
       <c r="F12" s="8" t="s">
         <v>379</v>
       </c>
@@ -7936,7 +7914,7 @@
       <c r="D13" s="11">
         <v>6</v>
       </c>
-      <c r="E13" s="21"/>
+      <c r="E13" s="20"/>
       <c r="F13" s="8" t="s">
         <v>384</v>
       </c>
@@ -7953,13 +7931,13 @@
       <c r="K13" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="L13" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M13" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N13" s="24" t="s">
+      <c r="L13" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N13" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O13" s="8" t="s">
@@ -7973,7 +7951,7 @@
       <c r="D14" s="11">
         <v>7</v>
       </c>
-      <c r="E14" s="21"/>
+      <c r="E14" s="20"/>
       <c r="F14" s="8" t="s">
         <v>389</v>
       </c>
@@ -7990,13 +7968,13 @@
       <c r="K14" s="8" t="s">
         <v>392</v>
       </c>
-      <c r="L14" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M14" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N14" s="24" t="s">
+      <c r="L14" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M14" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N14" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O14" s="8" t="s">
@@ -8010,7 +7988,7 @@
       <c r="D15" s="11">
         <v>8</v>
       </c>
-      <c r="E15" s="21"/>
+      <c r="E15" s="20"/>
       <c r="F15" s="8" t="s">
         <v>394</v>
       </c>
@@ -8027,13 +8005,13 @@
       <c r="K15" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="L15" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M15" s="26">
+      <c r="L15" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M15" s="16">
         <v>46233</v>
       </c>
-      <c r="N15" s="24" t="s">
+      <c r="N15" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O15" s="8" t="s">
@@ -8047,7 +8025,7 @@
       <c r="D16" s="11">
         <v>9</v>
       </c>
-      <c r="E16" s="21"/>
+      <c r="E16" s="20"/>
       <c r="F16" s="8" t="s">
         <v>399</v>
       </c>
@@ -8064,13 +8042,13 @@
       <c r="K16" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="L16" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M16" s="26">
+      <c r="L16" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M16" s="16">
         <v>46233</v>
       </c>
-      <c r="N16" s="24" t="s">
+      <c r="N16" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O16" s="8" t="s">
@@ -8084,7 +8062,7 @@
       <c r="D17" s="11">
         <v>10</v>
       </c>
-      <c r="E17" s="21"/>
+      <c r="E17" s="20"/>
       <c r="F17" s="8" t="s">
         <v>404</v>
       </c>
@@ -8101,13 +8079,13 @@
       <c r="K17" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="L17" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M17" s="26">
+      <c r="L17" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M17" s="16">
         <v>46233</v>
       </c>
-      <c r="N17" s="24" t="s">
+      <c r="N17" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O17" s="8" t="s">
@@ -8121,7 +8099,7 @@
       <c r="D18" s="11">
         <v>11</v>
       </c>
-      <c r="E18" s="21"/>
+      <c r="E18" s="20"/>
       <c r="F18" s="8" t="s">
         <v>408</v>
       </c>
@@ -8138,13 +8116,13 @@
       <c r="K18" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="L18" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M18" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N18" s="24" t="s">
+      <c r="L18" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M18" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N18" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O18" s="8" t="s">
@@ -8158,7 +8136,7 @@
       <c r="D19" s="11">
         <v>12</v>
       </c>
-      <c r="E19" s="21"/>
+      <c r="E19" s="20"/>
       <c r="F19" s="8" t="s">
         <v>413</v>
       </c>
@@ -8175,13 +8153,13 @@
       <c r="K19" s="8" t="s">
         <v>415</v>
       </c>
-      <c r="L19" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M19" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N19" s="24" t="s">
+      <c r="L19" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M19" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N19" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O19" s="8" t="s">
@@ -8195,7 +8173,7 @@
       <c r="D20" s="11">
         <v>13</v>
       </c>
-      <c r="E20" s="21"/>
+      <c r="E20" s="20"/>
       <c r="F20" s="8" t="s">
         <v>417</v>
       </c>
@@ -8212,13 +8190,13 @@
       <c r="K20" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="L20" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M20" s="26">
+      <c r="L20" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M20" s="16">
         <v>46233</v>
       </c>
-      <c r="N20" s="24" t="s">
+      <c r="N20" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O20" s="8" t="s">
@@ -8232,7 +8210,7 @@
       <c r="D21" s="11">
         <v>14</v>
       </c>
-      <c r="E21" s="21"/>
+      <c r="E21" s="20"/>
       <c r="F21" s="8" t="s">
         <v>422</v>
       </c>
@@ -8249,13 +8227,13 @@
       <c r="K21" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="L21" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M21" s="26">
+      <c r="L21" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M21" s="16">
         <v>46233</v>
       </c>
-      <c r="N21" s="24" t="s">
+      <c r="N21" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O21" s="8" t="s">
@@ -8271,7 +8249,7 @@
       <c r="D22" s="11">
         <v>15</v>
       </c>
-      <c r="E22" s="21"/>
+      <c r="E22" s="20"/>
       <c r="F22" s="8" t="s">
         <v>426</v>
       </c>
@@ -8288,13 +8266,13 @@
       <c r="K22" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="L22" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M22" s="26">
+      <c r="L22" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M22" s="16">
         <v>46233</v>
       </c>
-      <c r="N22" s="24" t="s">
+      <c r="N22" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O22" s="8" t="s">
@@ -8310,7 +8288,7 @@
       <c r="D23" s="11">
         <v>16</v>
       </c>
-      <c r="E23" s="21"/>
+      <c r="E23" s="20"/>
       <c r="F23" s="8" t="s">
         <v>431</v>
       </c>
@@ -8327,22 +8305,23 @@
       <c r="K23" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="L23" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M23" s="26" t="s">
-        <v>644</v>
-      </c>
-      <c r="N23" s="24" t="s">
-        <v>435</v>
+      <c r="L23" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>643</v>
+      </c>
+      <c r="N23" s="14" t="s">
+        <v>656</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>436</v>
+        <v>657</v>
       </c>
       <c r="P23" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="L6:P6"/>
     <mergeCell ref="B8:B23"/>
     <mergeCell ref="C8:C23"/>
     <mergeCell ref="E8:E23"/>
@@ -8350,7 +8329,6 @@
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="B6:K6"/>
-    <mergeCell ref="L6:P6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8380,56 +8358,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="26.5" x14ac:dyDescent="0.8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="21" t="s">
         <v>437</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
     </row>
     <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="22" t="s">
         <v>438</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
     </row>
     <row r="4" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="22" t="s">
         <v>439</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="18" t="s">
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25"/>
-      <c r="P6" s="25"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
@@ -8488,7 +8466,7 @@
       <c r="D8" s="11">
         <v>1</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="20" t="s">
         <v>440</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -8507,13 +8485,13 @@
       <c r="K8" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="L8" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M8" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N8" s="24" t="s">
+      <c r="L8" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M8" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N8" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O8" s="8" t="s">
@@ -8527,7 +8505,7 @@
       <c r="D9" s="11">
         <v>2</v>
       </c>
-      <c r="E9" s="21"/>
+      <c r="E9" s="20"/>
       <c r="F9" s="8" t="s">
         <v>446</v>
       </c>
@@ -8544,13 +8522,13 @@
       <c r="K9" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="L9" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M9" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N9" s="24" t="s">
+      <c r="L9" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M9" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N9" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O9" s="8" t="s">
@@ -8564,7 +8542,7 @@
       <c r="D10" s="11">
         <v>3</v>
       </c>
-      <c r="E10" s="21"/>
+      <c r="E10" s="20"/>
       <c r="F10" s="8" t="s">
         <v>450</v>
       </c>
@@ -8581,13 +8559,13 @@
       <c r="K10" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="L10" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M10" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N10" s="24" t="s">
+      <c r="L10" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M10" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N10" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O10" s="8"/>
@@ -8599,7 +8577,7 @@
       <c r="D11" s="11">
         <v>4</v>
       </c>
-      <c r="E11" s="21"/>
+      <c r="E11" s="20"/>
       <c r="F11" s="8" t="s">
         <v>454</v>
       </c>
@@ -8616,13 +8594,13 @@
       <c r="K11" s="8" t="s">
         <v>457</v>
       </c>
-      <c r="L11" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M11" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N11" s="24" t="s">
+      <c r="L11" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N11" s="14" t="s">
         <v>639</v>
       </c>
       <c r="O11" s="8" t="s">
@@ -8636,7 +8614,7 @@
       <c r="D12" s="11">
         <v>5</v>
       </c>
-      <c r="E12" s="21"/>
+      <c r="E12" s="20"/>
       <c r="F12" s="8" t="s">
         <v>459</v>
       </c>
@@ -8653,20 +8631,21 @@
       <c r="K12" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="L12" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M12" s="26">
-        <v>46232</v>
-      </c>
-      <c r="N12" s="24" t="s">
-        <v>643</v>
+      <c r="L12" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="16">
+        <v>46232</v>
+      </c>
+      <c r="N12" s="14" t="s">
+        <v>642</v>
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="L6:P6"/>
     <mergeCell ref="B8:B12"/>
     <mergeCell ref="C8:C12"/>
     <mergeCell ref="E8:E12"/>
@@ -8674,7 +8653,6 @@
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="B6:K6"/>
-    <mergeCell ref="L6:P6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/結合試験仕様書.xlsx
+++ b/結合試験仕様書.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="748">
   <si>
     <t>ACTIO（イベント主催・管理サービス）</t>
   </si>
@@ -2085,6 +2085,294 @@
   </si>
   <si>
     <t xml:space="preserve">ID: F-24 ／ 【対象外】① index.html をダブルクリックして file:// で開く形はセキュアコンテキストではないため、カメラを起動する仕組み（getUserMedia）が使えない。これはページの開き方による制約であり、PC・スマートフォンのどちらのカメラでも同じ。② 読み取り側の自前実装は画像の二値化・傾きの補正・パターン検出を要し、外部ライブラリを使わない前提では工数に見合わない。受付は明細2の受付コード検索で行う（仕様書 8章・機能一覧「対象外」の一覧と対応）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">上限を1文字超える文字列を用意する（貼り付けで入れる）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベント作成画面でイベント名101文字・説明文2001文字・会場名201文字、申込フォームで氏名51文字・メールアドレス255文字、カテゴリ管理でカテゴリ名31文字を入れようとする</t>
+  </si>
+  <si>
+    <t xml:space="preserve">いずれも入力欄が上限で受け付けを止め、超える分は入力できない（イベント名100・説明文2000・会場名200・氏名50・メールアドレス254・カテゴリ名30）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID: D-11 ／ すべての入力欄が maxlength で上限超えの入力を止めるため、保存時のエラー表示には到達しない ／ AIレビューにより追記</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エビデンス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/1-01_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/1-02a_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/1-04_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/1-05a_final.png
+試験エビデンス/1-05b_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/1-06_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/1-07_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/1-08_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/1-10_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/1-11_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/1-12_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/1-14_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/1-17_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/2-01_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/2-02_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/2-03_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/2-04_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/2-05_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/2-06_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/2-07_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/2-08_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/2-09_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/2-10_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/2-11a_final.png
+試験エビデンス/2-11b_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/2-12a_final.png
+試験エビデンス/2-12b_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/3-01_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/3-02_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/3-03_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/3-04a_final.png
+試験エビデンス/3-04b_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/3-05_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/3-06_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/3-07_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/3-08_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/4-01_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/4-02_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/4-03_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/4-04_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/4-05_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/4-06_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/4-07_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/4-08_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/4-09_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/4-10_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/4-11_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/4-12_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/5-01_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/5-02_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/5-03_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/5-05_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/5-06_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/6-01_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/6-02_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/6-03_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/6-04_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/6-05_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/6-06_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/6-07_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/6-11_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/6-12_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/7-01_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/7-02_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/7-04_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/7-05_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/8-04a_final.png
+試験エビデンス/8-04b_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/8-05a_final.png
+試験エビデンス/8-05b_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/8-06a_final.png
+試験エビデンス/8-06b_final.png
+試験エビデンス/8-06c_final.png
+試験エビデンス/8-06d_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/8-07_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/8-08_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/8-09a_final.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/8-12_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/8-13a_final.png
+試験エビデンス/8-13b_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/8-15_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/9-01_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/9-02_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/9-03a_final.png
+試験エビデンス/9-03b_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/9-04_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/9-05_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/9-06a_final.png
+試験エビデンス/9-06b_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/9-07a_final.png
+試験エビデンス/9-07b_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/9-08_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/10-02a_final.png
+試験エビデンス/10-02b_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/10-03a_final.png
+試験エビデンス/10-03b_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/10-05_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/10-06a_final.png
+試験エビデンス/10-06b_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/10-08a_final.png
+試験エビデンス/10-08b_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験エビデンス/10-09a_final.png
+試験エビデンス/10-09b_final.png</t>
   </si>
 </sst>
 </file>
@@ -2758,7 +3046,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="5.9140625" style="10" customWidth="1"/>
@@ -2776,9 +3064,10 @@
     <col min="14" max="14" width="13" style="10" customWidth="1"/>
     <col min="15" max="15" width="44.58203125" style="10" customWidth="1"/>
     <col min="16" max="16" width="6.5" style="10" customWidth="1"/>
+    <col min="17" max="17" width="34.6640625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.5" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:17" ht="26.5" x14ac:dyDescent="0.8">
       <c r="A1" s="21" t="s">
         <v>463</v>
       </c>
@@ -2787,7 +3076,7 @@
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
@@ -2798,7 +3087,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
     </row>
-    <row r="4" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
@@ -2809,7 +3098,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="23" t="s">
         <v>72</v>
       </c>
@@ -2830,7 +3119,7 @@
       <c r="O6" s="18"/>
       <c r="P6" s="18"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
         <v>74</v>
       </c>
@@ -2876,8 +3165,11 @@
       <c r="P7" s="9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q7" s="9" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="19">
         <v>8</v>
       </c>
@@ -2919,8 +3211,9 @@
         <v>471</v>
       </c>
       <c r="P8" s="8"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q8" s="8"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
       <c r="D9" s="11">
@@ -2956,8 +3249,9 @@
         <v>476</v>
       </c>
       <c r="P9" s="8"/>
-    </row>
-    <row r="10" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q9" s="8"/>
+    </row>
+    <row r="10" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
       <c r="D10" s="11">
@@ -2993,8 +3287,9 @@
         <v>481</v>
       </c>
       <c r="P10" s="8"/>
-    </row>
-    <row r="11" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q10" s="8"/>
+    </row>
+    <row r="11" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
       <c r="D11" s="11">
@@ -3030,8 +3325,11 @@
         <v>486</v>
       </c>
       <c r="P11" s="8"/>
-    </row>
-    <row r="12" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q11" s="8" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
       <c r="D12" s="11">
@@ -3067,8 +3365,11 @@
         <v>491</v>
       </c>
       <c r="P12" s="8"/>
-    </row>
-    <row r="13" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q12" s="8" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
       <c r="D13" s="11">
@@ -3104,8 +3405,11 @@
         <v>496</v>
       </c>
       <c r="P13" s="8"/>
-    </row>
-    <row r="14" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q13" s="8" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
       <c r="D14" s="11">
@@ -3141,8 +3445,11 @@
         <v>501</v>
       </c>
       <c r="P14" s="8"/>
-    </row>
-    <row r="15" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q14" s="8" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
       <c r="D15" s="11">
@@ -3178,8 +3485,11 @@
         <v>506</v>
       </c>
       <c r="P15" s="8"/>
-    </row>
-    <row r="16" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q15" s="8" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
       <c r="D16" s="11">
@@ -3215,6 +3525,9 @@
         <v>511</v>
       </c>
       <c r="P16" s="8"/>
+      <c r="Q16" s="8" t="s">
+        <v>730</v>
+      </c>
     </row>
     <row r="17" spans="2:16" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="19"/>
@@ -3252,6 +3565,7 @@
         <v>516</v>
       </c>
       <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
     </row>
     <row r="18" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="19"/>
@@ -3291,6 +3605,7 @@
       <c r="P18" s="8" t="s">
         <v>155</v>
       </c>
+      <c r="Q18" s="8"/>
     </row>
     <row r="19" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="19"/>
@@ -3330,6 +3645,9 @@
       <c r="P19" s="8" t="s">
         <v>155</v>
       </c>
+      <c r="Q19" s="8" t="s">
+        <v>731</v>
+      </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="19"/>
@@ -3369,6 +3687,9 @@
       <c r="P20" s="8" t="s">
         <v>155</v>
       </c>
+      <c r="Q20" s="8" t="s">
+        <v>732</v>
+      </c>
     </row>
     <row r="21" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="19"/>
@@ -3408,6 +3729,7 @@
       <c r="P21" s="8" t="s">
         <v>155</v>
       </c>
+      <c r="Q21" s="8"/>
     </row>
     <row r="22" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="19"/>
@@ -3447,10 +3769,13 @@
       <c r="P22" s="8" t="s">
         <v>155</v>
       </c>
+      <c r="Q22" s="8" t="s">
+        <v>733</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="L6:P6"/>
+    <mergeCell ref="L6:Q6"/>
     <mergeCell ref="B8:B22"/>
     <mergeCell ref="C8:C22"/>
     <mergeCell ref="E8:E22"/>
@@ -3466,7 +3791,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="5.9140625" style="10" customWidth="1"/>
@@ -3484,9 +3809,10 @@
     <col min="14" max="14" width="13" style="10" customWidth="1"/>
     <col min="15" max="15" width="44.58203125" style="10" customWidth="1"/>
     <col min="16" max="16" width="6.5" style="10" customWidth="1"/>
+    <col min="17" max="17" width="34.6640625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.5" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:17" ht="26.5" x14ac:dyDescent="0.8">
       <c r="A1" s="21" t="s">
         <v>539</v>
       </c>
@@ -3495,7 +3821,7 @@
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
@@ -3506,7 +3832,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
     </row>
-    <row r="4" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
@@ -3517,7 +3843,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="23" t="s">
         <v>72</v>
       </c>
@@ -3538,7 +3864,7 @@
       <c r="O6" s="18"/>
       <c r="P6" s="18"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
         <v>74</v>
       </c>
@@ -3584,8 +3910,11 @@
       <c r="P7" s="9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q7" s="9" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="19">
         <v>9</v>
       </c>
@@ -3627,8 +3956,11 @@
         <v>547</v>
       </c>
       <c r="P8" s="8"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q8" s="8" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
       <c r="D9" s="11">
@@ -3664,8 +3996,11 @@
         <v>551</v>
       </c>
       <c r="P9" s="8"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q9" s="8" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
       <c r="D10" s="11">
@@ -3699,8 +4034,11 @@
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q10" s="8" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
       <c r="D11" s="11">
@@ -3736,8 +4074,11 @@
         <v>560</v>
       </c>
       <c r="P11" s="8"/>
-    </row>
-    <row r="12" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q11" s="8" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
       <c r="D12" s="11">
@@ -3773,8 +4114,11 @@
         <v>565</v>
       </c>
       <c r="P12" s="8"/>
-    </row>
-    <row r="13" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q12" s="8" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
       <c r="D13" s="11">
@@ -3812,8 +4156,11 @@
       <c r="P13" s="8" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q13" s="8" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
       <c r="D14" s="11">
@@ -3851,8 +4198,11 @@
       <c r="P14" s="8" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q14" s="8" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
       <c r="D15" s="11">
@@ -3890,10 +4240,13 @@
       <c r="P15" s="8" t="s">
         <v>155</v>
       </c>
+      <c r="Q15" s="8" t="s">
+        <v>741</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="L6:P6"/>
+    <mergeCell ref="L6:Q6"/>
     <mergeCell ref="B8:B15"/>
     <mergeCell ref="C8:C15"/>
     <mergeCell ref="E8:E15"/>
@@ -3909,7 +4262,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="5.9140625" style="10" customWidth="1"/>
@@ -3927,9 +4280,10 @@
     <col min="14" max="14" width="13" style="10" customWidth="1"/>
     <col min="15" max="15" width="44.58203125" style="10" customWidth="1"/>
     <col min="16" max="16" width="6.5" style="10" customWidth="1"/>
+    <col min="17" max="17" width="34.6640625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.5" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:17" ht="26.5" x14ac:dyDescent="0.8">
       <c r="A1" s="21" t="s">
         <v>580</v>
       </c>
@@ -3938,7 +4292,7 @@
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
@@ -3949,7 +4303,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
     </row>
-    <row r="4" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
@@ -3960,7 +4314,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="23" t="s">
         <v>640</v>
       </c>
@@ -3981,7 +4335,7 @@
       <c r="O6" s="18"/>
       <c r="P6" s="18"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
         <v>74</v>
       </c>
@@ -4027,8 +4381,11 @@
       <c r="P7" s="9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q7" s="9" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="19">
         <v>10</v>
       </c>
@@ -4068,8 +4425,9 @@
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
-    </row>
-    <row r="9" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q8" s="8"/>
+    </row>
+    <row r="9" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
       <c r="D9" s="11">
@@ -4105,8 +4463,11 @@
         <v>591</v>
       </c>
       <c r="P9" s="8"/>
-    </row>
-    <row r="10" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q9" s="8" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
       <c r="D10" s="11">
@@ -4142,8 +4503,11 @@
         <v>641</v>
       </c>
       <c r="P10" s="8"/>
-    </row>
-    <row r="11" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q10" s="8" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
       <c r="D11" s="11">
@@ -4179,8 +4543,9 @@
         <v>600</v>
       </c>
       <c r="P11" s="8"/>
-    </row>
-    <row r="12" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q11" s="8"/>
+    </row>
+    <row r="12" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
       <c r="D12" s="11">
@@ -4216,8 +4581,11 @@
         <v>605</v>
       </c>
       <c r="P12" s="8"/>
-    </row>
-    <row r="13" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q12" s="8" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
       <c r="D13" s="11">
@@ -4253,8 +4621,11 @@
         <v>610</v>
       </c>
       <c r="P13" s="8"/>
-    </row>
-    <row r="14" spans="1:16" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q13" s="8" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
       <c r="D14" s="11">
@@ -4269,13 +4640,13 @@
         <v>42</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>612</v>
+        <v>658</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>613</v>
+        <v>659</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>614</v>
+        <v>660</v>
       </c>
       <c r="L14" s="8" t="s">
         <v>88</v>
@@ -4287,13 +4658,14 @@
         <v>639</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>615</v>
+        <v>661</v>
       </c>
       <c r="P14" s="8" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q14" s="8"/>
+    </row>
+    <row r="15" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
       <c r="D15" s="11">
@@ -4331,8 +4703,11 @@
       <c r="P15" s="8" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q15" s="8" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
       <c r="D16" s="11">
@@ -4369,6 +4744,9 @@
       </c>
       <c r="P16" s="8" t="s">
         <v>155</v>
+      </c>
+      <c r="Q16" s="8" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
@@ -4409,10 +4787,11 @@
       <c r="P17" s="8" t="s">
         <v>155</v>
       </c>
+      <c r="Q17" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="L6:P6"/>
+    <mergeCell ref="L6:Q6"/>
     <mergeCell ref="B8:B17"/>
     <mergeCell ref="C8:C17"/>
     <mergeCell ref="E8:E17"/>
@@ -4805,7 +5184,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="5.9140625" style="10" customWidth="1"/>
@@ -4823,9 +5202,10 @@
     <col min="14" max="14" width="13" style="10" customWidth="1"/>
     <col min="15" max="15" width="44.58203125" style="10" customWidth="1"/>
     <col min="16" max="16" width="6.5" style="10" customWidth="1"/>
+    <col min="17" max="17" width="34.6640625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.5" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:17" ht="26.5" x14ac:dyDescent="0.8">
       <c r="A1" s="21" t="s">
         <v>68</v>
       </c>
@@ -4834,7 +5214,7 @@
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
@@ -4845,7 +5225,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
     </row>
-    <row r="4" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
@@ -4856,7 +5236,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="23" t="s">
         <v>72</v>
       </c>
@@ -4877,7 +5257,7 @@
       <c r="O6" s="18"/>
       <c r="P6" s="18"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
         <v>74</v>
       </c>
@@ -4923,8 +5303,11 @@
       <c r="P7" s="9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q7" s="9" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="19">
         <v>1</v>
       </c>
@@ -4966,8 +5349,11 @@
         <v>89</v>
       </c>
       <c r="P8" s="8"/>
-    </row>
-    <row r="9" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q8" s="8" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
       <c r="D9" s="11">
@@ -5001,8 +5387,11 @@
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q9" s="8" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
       <c r="D10" s="11">
@@ -5038,8 +5427,9 @@
         <v>98</v>
       </c>
       <c r="P10" s="8"/>
-    </row>
-    <row r="11" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q10" s="8"/>
+    </row>
+    <row r="11" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
       <c r="D11" s="11">
@@ -5075,8 +5465,11 @@
         <v>102</v>
       </c>
       <c r="P11" s="8"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q11" s="8" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
       <c r="D12" s="11">
@@ -5112,8 +5505,11 @@
         <v>107</v>
       </c>
       <c r="P12" s="8"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q12" s="8" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
       <c r="D13" s="11">
@@ -5149,8 +5545,11 @@
         <v>112</v>
       </c>
       <c r="P13" s="8"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q13" s="8" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
       <c r="D14" s="11">
@@ -5186,8 +5585,11 @@
         <v>116</v>
       </c>
       <c r="P14" s="8"/>
-    </row>
-    <row r="15" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q14" s="8" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
       <c r="D15" s="11">
@@ -5223,8 +5625,11 @@
         <v>121</v>
       </c>
       <c r="P15" s="8"/>
-    </row>
-    <row r="16" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q15" s="8" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
       <c r="D16" s="11">
@@ -5260,6 +5665,7 @@
         <v>126</v>
       </c>
       <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="19"/>
@@ -5297,6 +5703,9 @@
         <v>131</v>
       </c>
       <c r="P17" s="8"/>
+      <c r="Q17" s="8" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="18" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="19"/>
@@ -5334,6 +5743,9 @@
         <v>136</v>
       </c>
       <c r="P18" s="8"/>
+      <c r="Q18" s="8" t="s">
+        <v>671</v>
+      </c>
     </row>
     <row r="19" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="19"/>
@@ -5371,6 +5783,9 @@
         <v>140</v>
       </c>
       <c r="P19" s="8"/>
+      <c r="Q19" s="8" t="s">
+        <v>672</v>
+      </c>
     </row>
     <row r="20" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="19"/>
@@ -5408,6 +5823,7 @@
         <v>145</v>
       </c>
       <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
     </row>
     <row r="21" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="19"/>
@@ -5445,6 +5861,9 @@
         <v>150</v>
       </c>
       <c r="P21" s="8"/>
+      <c r="Q21" s="8" t="s">
+        <v>673</v>
+      </c>
     </row>
     <row r="22" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="19"/>
@@ -5484,6 +5903,7 @@
       <c r="P22" s="8" t="s">
         <v>155</v>
       </c>
+      <c r="Q22" s="8"/>
     </row>
     <row r="23" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="19"/>
@@ -5523,6 +5943,7 @@
       <c r="P23" s="8" t="s">
         <v>155</v>
       </c>
+      <c r="Q23" s="8"/>
     </row>
     <row r="24" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="19"/>
@@ -5562,10 +5983,13 @@
       <c r="P24" s="8" t="s">
         <v>155</v>
       </c>
+      <c r="Q24" s="8" t="s">
+        <v>674</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="L6:P6"/>
+    <mergeCell ref="L6:Q6"/>
     <mergeCell ref="B8:B24"/>
     <mergeCell ref="C8:C24"/>
     <mergeCell ref="E8:E24"/>
@@ -5581,7 +6005,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="5.9140625" style="10" customWidth="1"/>
@@ -5599,9 +6023,10 @@
     <col min="14" max="14" width="13" style="10" customWidth="1"/>
     <col min="15" max="15" width="44.58203125" style="10" customWidth="1"/>
     <col min="16" max="16" width="6.5" style="10" customWidth="1"/>
+    <col min="17" max="17" width="34.6640625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.5" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:17" ht="26.5" x14ac:dyDescent="0.8">
       <c r="A1" s="21" t="s">
         <v>166</v>
       </c>
@@ -5610,7 +6035,7 @@
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
@@ -5621,7 +6046,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
     </row>
-    <row r="4" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
@@ -5632,7 +6057,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="23" t="s">
         <v>72</v>
       </c>
@@ -5653,7 +6078,7 @@
       <c r="O6" s="18"/>
       <c r="P6" s="18"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
         <v>74</v>
       </c>
@@ -5699,8 +6124,11 @@
       <c r="P7" s="9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q7" s="9" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="19">
         <v>2</v>
       </c>
@@ -5742,8 +6170,11 @@
         <v>174</v>
       </c>
       <c r="P8" s="8"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q8" s="8" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
       <c r="D9" s="11">
@@ -5779,8 +6210,11 @@
         <v>178</v>
       </c>
       <c r="P9" s="8"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q9" s="8" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
       <c r="D10" s="11">
@@ -5816,8 +6250,11 @@
         <v>181</v>
       </c>
       <c r="P10" s="8"/>
-    </row>
-    <row r="11" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q10" s="8" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
       <c r="D11" s="11">
@@ -5853,8 +6290,11 @@
         <v>186</v>
       </c>
       <c r="P11" s="8"/>
-    </row>
-    <row r="12" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q11" s="8" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
       <c r="D12" s="11">
@@ -5890,8 +6330,11 @@
         <v>190</v>
       </c>
       <c r="P12" s="8"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q12" s="8" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
       <c r="D13" s="11">
@@ -5927,8 +6370,11 @@
         <v>195</v>
       </c>
       <c r="P13" s="8"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q13" s="8" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
       <c r="D14" s="11">
@@ -5964,8 +6410,11 @@
         <v>199</v>
       </c>
       <c r="P14" s="8"/>
-    </row>
-    <row r="15" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q14" s="8" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
       <c r="D15" s="11">
@@ -6001,8 +6450,11 @@
         <v>204</v>
       </c>
       <c r="P15" s="8"/>
-    </row>
-    <row r="16" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q15" s="8" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
       <c r="D16" s="11">
@@ -6038,6 +6490,9 @@
         <v>209</v>
       </c>
       <c r="P16" s="8"/>
+      <c r="Q16" s="8" t="s">
+        <v>683</v>
+      </c>
     </row>
     <row r="17" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="19"/>
@@ -6077,6 +6532,9 @@
       <c r="P17" s="8" t="s">
         <v>155</v>
       </c>
+      <c r="Q17" s="8" t="s">
+        <v>684</v>
+      </c>
     </row>
     <row r="18" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="19"/>
@@ -6116,6 +6574,9 @@
       <c r="P18" s="8" t="s">
         <v>155</v>
       </c>
+      <c r="Q18" s="8" t="s">
+        <v>685</v>
+      </c>
     </row>
     <row r="19" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="19"/>
@@ -6155,10 +6616,13 @@
       <c r="P19" s="8" t="s">
         <v>155</v>
       </c>
+      <c r="Q19" s="8" t="s">
+        <v>686</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="L6:P6"/>
+    <mergeCell ref="L6:Q6"/>
     <mergeCell ref="B8:B19"/>
     <mergeCell ref="C8:C19"/>
     <mergeCell ref="E8:E19"/>
@@ -6174,7 +6638,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="5.9140625" style="10" customWidth="1"/>
@@ -6192,9 +6656,10 @@
     <col min="14" max="14" width="13" style="10" customWidth="1"/>
     <col min="15" max="15" width="44.58203125" style="10" customWidth="1"/>
     <col min="16" max="16" width="6.5" style="10" customWidth="1"/>
+    <col min="17" max="17" width="34.6640625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.5" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:17" ht="26.5" x14ac:dyDescent="0.8">
       <c r="A1" s="21" t="s">
         <v>223</v>
       </c>
@@ -6203,7 +6668,7 @@
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
@@ -6214,7 +6679,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
     </row>
-    <row r="4" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
@@ -6225,7 +6690,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="23" t="s">
         <v>72</v>
       </c>
@@ -6246,7 +6711,7 @@
       <c r="O6" s="18"/>
       <c r="P6" s="18"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
         <v>74</v>
       </c>
@@ -6292,8 +6757,11 @@
       <c r="P7" s="9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q7" s="9" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="19">
         <v>3</v>
       </c>
@@ -6335,8 +6803,11 @@
         <v>231</v>
       </c>
       <c r="P8" s="8"/>
-    </row>
-    <row r="9" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q8" s="8" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
       <c r="D9" s="11">
@@ -6372,8 +6843,11 @@
         <v>236</v>
       </c>
       <c r="P9" s="8"/>
-    </row>
-    <row r="10" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q9" s="8" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
       <c r="D10" s="11">
@@ -6409,8 +6883,11 @@
         <v>241</v>
       </c>
       <c r="P10" s="8"/>
-    </row>
-    <row r="11" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q10" s="8" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
       <c r="D11" s="11">
@@ -6444,8 +6921,11 @@
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
-    </row>
-    <row r="12" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q11" s="8" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
       <c r="D12" s="11">
@@ -6481,8 +6961,11 @@
         <v>249</v>
       </c>
       <c r="P12" s="8"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q12" s="8" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
       <c r="D13" s="11">
@@ -6516,8 +6999,11 @@
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
-    </row>
-    <row r="14" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q13" s="8" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
       <c r="D14" s="11">
@@ -6553,8 +7039,11 @@
         <v>257</v>
       </c>
       <c r="P14" s="8"/>
-    </row>
-    <row r="15" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q14" s="8" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
       <c r="D15" s="11">
@@ -6590,8 +7079,11 @@
         <v>262</v>
       </c>
       <c r="P15" s="8"/>
-    </row>
-    <row r="16" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q15" s="8" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
       <c r="D16" s="11">
@@ -6629,10 +7121,11 @@
       <c r="P16" s="8" t="s">
         <v>155</v>
       </c>
+      <c r="Q16" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="L6:P6"/>
+    <mergeCell ref="L6:Q6"/>
     <mergeCell ref="B8:B16"/>
     <mergeCell ref="C8:C16"/>
     <mergeCell ref="E8:E16"/>
@@ -6648,7 +7141,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="5.9140625" style="10" customWidth="1"/>
@@ -6666,9 +7159,10 @@
     <col min="14" max="14" width="13" style="10" customWidth="1"/>
     <col min="15" max="15" width="44.58203125" style="10" customWidth="1"/>
     <col min="16" max="16" width="6.5" style="10" customWidth="1"/>
+    <col min="17" max="17" width="34.6640625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.5" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:17" ht="26.5" x14ac:dyDescent="0.8">
       <c r="A1" s="21" t="s">
         <v>267</v>
       </c>
@@ -6677,7 +7171,7 @@
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
@@ -6688,7 +7182,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
     </row>
-    <row r="4" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
@@ -6699,7 +7193,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="23" t="s">
         <v>72</v>
       </c>
@@ -6720,7 +7214,7 @@
       <c r="O6" s="18"/>
       <c r="P6" s="18"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
         <v>74</v>
       </c>
@@ -6766,8 +7260,11 @@
       <c r="P7" s="9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q7" s="9" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="19">
         <v>4</v>
       </c>
@@ -6809,8 +7306,11 @@
         <v>274</v>
       </c>
       <c r="P8" s="8"/>
-    </row>
-    <row r="9" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q8" s="8" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
       <c r="D9" s="11">
@@ -6846,8 +7346,11 @@
         <v>279</v>
       </c>
       <c r="P9" s="8"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q9" s="8" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
       <c r="D10" s="11">
@@ -6883,8 +7386,11 @@
         <v>283</v>
       </c>
       <c r="P10" s="8"/>
-    </row>
-    <row r="11" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q10" s="8" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
       <c r="D11" s="11">
@@ -6918,8 +7424,11 @@
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
-    </row>
-    <row r="12" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q11" s="8" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
       <c r="D12" s="11">
@@ -6955,8 +7464,11 @@
         <v>292</v>
       </c>
       <c r="P12" s="8"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q12" s="8" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
       <c r="D13" s="11">
@@ -6992,8 +7504,11 @@
         <v>296</v>
       </c>
       <c r="P13" s="8"/>
-    </row>
-    <row r="14" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q13" s="8" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
       <c r="D14" s="11">
@@ -7029,8 +7544,11 @@
         <v>301</v>
       </c>
       <c r="P14" s="8"/>
-    </row>
-    <row r="15" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q14" s="8" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
       <c r="D15" s="11">
@@ -7066,8 +7584,11 @@
         <v>306</v>
       </c>
       <c r="P15" s="8"/>
-    </row>
-    <row r="16" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q15" s="8" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
       <c r="D16" s="11">
@@ -7103,6 +7624,9 @@
         <v>310</v>
       </c>
       <c r="P16" s="8"/>
+      <c r="Q16" s="8" t="s">
+        <v>703</v>
+      </c>
     </row>
     <row r="17" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="19"/>
@@ -7140,6 +7664,9 @@
         <v>315</v>
       </c>
       <c r="P17" s="8"/>
+      <c r="Q17" s="8" t="s">
+        <v>704</v>
+      </c>
     </row>
     <row r="18" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="19"/>
@@ -7179,6 +7706,9 @@
       <c r="P18" s="8" t="s">
         <v>155</v>
       </c>
+      <c r="Q18" s="8" t="s">
+        <v>705</v>
+      </c>
     </row>
     <row r="19" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="19"/>
@@ -7218,10 +7748,13 @@
       <c r="P19" s="8" t="s">
         <v>155</v>
       </c>
+      <c r="Q19" s="8" t="s">
+        <v>706</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="L6:P6"/>
+    <mergeCell ref="L6:Q6"/>
     <mergeCell ref="B8:B19"/>
     <mergeCell ref="C8:C19"/>
     <mergeCell ref="E8:E19"/>
@@ -7237,7 +7770,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="5.9140625" style="10" customWidth="1"/>
@@ -7255,9 +7788,10 @@
     <col min="14" max="14" width="13" style="10" customWidth="1"/>
     <col min="15" max="15" width="44.58203125" style="10" customWidth="1"/>
     <col min="16" max="16" width="6.5" style="10" customWidth="1"/>
+    <col min="17" max="17" width="34.6640625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.5" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:17" ht="26.5" x14ac:dyDescent="0.8">
       <c r="A1" s="21" t="s">
         <v>326</v>
       </c>
@@ -7266,7 +7800,7 @@
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
@@ -7277,7 +7811,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
     </row>
-    <row r="4" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
@@ -7288,7 +7822,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="23" t="s">
         <v>72</v>
       </c>
@@ -7309,7 +7843,7 @@
       <c r="O6" s="18"/>
       <c r="P6" s="18"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
         <v>74</v>
       </c>
@@ -7355,8 +7889,11 @@
       <c r="P7" s="9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q7" s="9" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="19">
         <v>5</v>
       </c>
@@ -7398,8 +7935,11 @@
         <v>333</v>
       </c>
       <c r="P8" s="8"/>
-    </row>
-    <row r="9" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q8" s="8" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
       <c r="D9" s="11">
@@ -7433,8 +7973,11 @@
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
-    </row>
-    <row r="10" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q9" s="8" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
       <c r="D10" s="11">
@@ -7470,8 +8013,11 @@
         <v>341</v>
       </c>
       <c r="P10" s="8"/>
-    </row>
-    <row r="11" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q10" s="8" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
       <c r="D11" s="11">
@@ -7507,8 +8053,9 @@
         <v>346</v>
       </c>
       <c r="P11" s="8"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q11" s="8"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
       <c r="D12" s="11">
@@ -7542,8 +8089,11 @@
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
-    </row>
-    <row r="13" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q12" s="8" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
       <c r="D13" s="11">
@@ -7579,10 +8129,13 @@
         <v>354</v>
       </c>
       <c r="P13" s="8"/>
+      <c r="Q13" s="8" t="s">
+        <v>711</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="L6:P6"/>
+    <mergeCell ref="L6:Q6"/>
     <mergeCell ref="B8:B13"/>
     <mergeCell ref="C8:C13"/>
     <mergeCell ref="E8:E13"/>
@@ -7598,7 +8151,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="5.9140625" style="10" customWidth="1"/>
@@ -7616,9 +8169,10 @@
     <col min="14" max="14" width="13" style="10" customWidth="1"/>
     <col min="15" max="15" width="44.58203125" style="10" customWidth="1"/>
     <col min="16" max="16" width="6.5" style="10" customWidth="1"/>
+    <col min="17" max="17" width="34.6640625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.5" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:17" ht="26.5" x14ac:dyDescent="0.8">
       <c r="A1" s="21" t="s">
         <v>355</v>
       </c>
@@ -7627,7 +8181,7 @@
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
@@ -7638,7 +8192,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
     </row>
-    <row r="4" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
@@ -7649,7 +8203,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="23" t="s">
         <v>72</v>
       </c>
@@ -7670,7 +8224,7 @@
       <c r="O6" s="18"/>
       <c r="P6" s="18"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
         <v>74</v>
       </c>
@@ -7716,8 +8270,11 @@
       <c r="P7" s="9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q7" s="9" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="19">
         <v>6</v>
       </c>
@@ -7759,8 +8316,11 @@
         <v>363</v>
       </c>
       <c r="P8" s="8"/>
-    </row>
-    <row r="9" spans="1:16" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q8" s="8" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
       <c r="D9" s="11">
@@ -7796,8 +8356,11 @@
         <v>655</v>
       </c>
       <c r="P9" s="8"/>
-    </row>
-    <row r="10" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q9" s="8" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
       <c r="D10" s="11">
@@ -7833,8 +8396,11 @@
         <v>373</v>
       </c>
       <c r="P10" s="8"/>
-    </row>
-    <row r="11" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q10" s="8" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
       <c r="D11" s="11">
@@ -7870,8 +8436,11 @@
         <v>378</v>
       </c>
       <c r="P11" s="8"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q11" s="8" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
       <c r="D12" s="11">
@@ -7907,8 +8476,11 @@
         <v>383</v>
       </c>
       <c r="P12" s="8"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q12" s="8" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
       <c r="D13" s="11">
@@ -7944,8 +8516,11 @@
         <v>388</v>
       </c>
       <c r="P13" s="8"/>
-    </row>
-    <row r="14" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q13" s="8" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
       <c r="D14" s="11">
@@ -7981,8 +8556,11 @@
         <v>393</v>
       </c>
       <c r="P14" s="8"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q14" s="8" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
       <c r="D15" s="11">
@@ -8018,8 +8596,9 @@
         <v>398</v>
       </c>
       <c r="P15" s="8"/>
-    </row>
-    <row r="16" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q15" s="8"/>
+    </row>
+    <row r="16" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
       <c r="D16" s="11">
@@ -8055,6 +8634,7 @@
         <v>403</v>
       </c>
       <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="19"/>
@@ -8092,6 +8672,7 @@
         <v>407</v>
       </c>
       <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="19"/>
@@ -8129,6 +8710,9 @@
         <v>412</v>
       </c>
       <c r="P18" s="8"/>
+      <c r="Q18" s="8" t="s">
+        <v>719</v>
+      </c>
     </row>
     <row r="19" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="19"/>
@@ -8166,6 +8750,9 @@
         <v>416</v>
       </c>
       <c r="P19" s="8"/>
+      <c r="Q19" s="8" t="s">
+        <v>720</v>
+      </c>
     </row>
     <row r="20" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="19"/>
@@ -8203,6 +8790,7 @@
         <v>421</v>
       </c>
       <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
     </row>
     <row r="21" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="19"/>
@@ -8242,6 +8830,7 @@
       <c r="P21" s="8" t="s">
         <v>155</v>
       </c>
+      <c r="Q21" s="8"/>
     </row>
     <row r="22" spans="2:16" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="19"/>
@@ -8281,6 +8870,7 @@
       <c r="P22" s="8" t="s">
         <v>155</v>
       </c>
+      <c r="Q22" s="8"/>
     </row>
     <row r="23" spans="2:16" ht="108" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="19"/>
@@ -8318,10 +8908,11 @@
         <v>657</v>
       </c>
       <c r="P23" s="8"/>
+      <c r="Q23" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="L6:P6"/>
+    <mergeCell ref="L6:Q6"/>
     <mergeCell ref="B8:B23"/>
     <mergeCell ref="C8:C23"/>
     <mergeCell ref="E8:E23"/>
@@ -8337,7 +8928,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="5.9140625" style="10" customWidth="1"/>
@@ -8355,9 +8946,10 @@
     <col min="14" max="14" width="13" style="10" customWidth="1"/>
     <col min="15" max="15" width="44.58203125" style="10" customWidth="1"/>
     <col min="16" max="16" width="6.5" style="10" customWidth="1"/>
+    <col min="17" max="17" width="34.6640625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.5" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:17" ht="26.5" x14ac:dyDescent="0.8">
       <c r="A1" s="21" t="s">
         <v>437</v>
       </c>
@@ -8366,7 +8958,7 @@
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>69</v>
       </c>
@@ -8377,7 +8969,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
     </row>
-    <row r="4" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
@@ -8388,7 +8980,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="23" t="s">
         <v>72</v>
       </c>
@@ -8409,7 +9001,7 @@
       <c r="O6" s="18"/>
       <c r="P6" s="18"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
         <v>74</v>
       </c>
@@ -8455,8 +9047,11 @@
       <c r="P7" s="9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q7" s="9" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="19">
         <v>7</v>
       </c>
@@ -8498,8 +9093,11 @@
         <v>445</v>
       </c>
       <c r="P8" s="8"/>
-    </row>
-    <row r="9" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q8" s="8" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
       <c r="D9" s="11">
@@ -8535,8 +9133,11 @@
         <v>449</v>
       </c>
       <c r="P9" s="8"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q9" s="8" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
       <c r="D10" s="11">
@@ -8570,8 +9171,9 @@
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q10" s="8"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
       <c r="D11" s="11">
@@ -8607,8 +9209,11 @@
         <v>458</v>
       </c>
       <c r="P11" s="8"/>
-    </row>
-    <row r="12" spans="1:16" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q11" s="8" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
       <c r="D12" s="11">
@@ -8642,10 +9247,13 @@
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
+      <c r="Q12" s="8" t="s">
+        <v>724</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="L6:P6"/>
+    <mergeCell ref="L6:Q6"/>
     <mergeCell ref="B8:B12"/>
     <mergeCell ref="C8:C12"/>
     <mergeCell ref="E8:E12"/>
